--- a/fine_tuning/dataset/raw/building_std_queries.xlsx
+++ b/fine_tuning/dataset/raw/building_std_queries.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/julian.slane-holloway/repos/building-energy-standards-data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gonz102\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5237CE34-8584-3349-99F2-82C80B9F32C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BB655F2-98DC-407C-A1BE-46D8721DCEDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32820" yWindow="10640" windowWidth="41960" windowHeight="18360" xr2:uid="{77D55900-27DC-4083-93B9-DD1815E6B0C1}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{77D55900-27DC-4083-93B9-DD1815E6B0C1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="128">
   <si>
     <t>answer</t>
   </si>
@@ -456,12 +456,605 @@
   <si>
     <t>Which space types share the same electric equipment profiles but have different ventilation requirements, and how do their schedule patterns compare?</t>
   </si>
+  <si>
+    <t>What space types have electric equipment loads above 0.7 W/ft² and generate latent heat gains?</t>
+  </si>
+  <si>
+    <t>Which space types have the highest variability in electric equipment loads, and what are their heat gain characteristics?</t>
+  </si>
+  <si>
+    <t>SELECT electric_equipment_space_type_name,
+       electric_equipment_minimum_epd,
+       electric_equipment_maximum_epd,
+       (electric_equipment_maximum_epd - electric_equipment_minimum_epd) as epd_range,
+       electric_equipment_fraction_latent,
+       electric_equipment_fraction_radiant,
+       electric_equipment_fraction_lost
+FROM level_2_electric_equipment
+WHERE electric_equipment_maximum_epd &gt; electric_equipment_minimum_epd
+ORDER BY epd_range DESC;</t>
+  </si>
+  <si>
+    <t>SELECT electric_equipment_space_type_name,
+       electric_equipment_average_epd,
+       electric_equipment_median_epd,
+       electric_equipment_fraction_latent,
+       electric_equipment_fraction_radiant
+FROM level_2_electric_equipment
+WHERE electric_equipment_average_epd &gt; 0.7
+  AND electric_equipment_fraction_latent &gt; 0
+ORDER BY electric_equipment_average_epd DESC;</t>
+  </si>
+  <si>
+    <t>How do illuminance requirements vary between IECC and ASHRAE 90.1 standards for the same space types?</t>
+  </si>
+  <si>
+    <t>Which space types require the highest illuminance levels above 400 Lux across any code version?</t>
+  </si>
+  <si>
+    <t>SELECT lighting_space_type_name,
+       level_3_lighting_code_definition_table,
+       lighting_space_type_target_illuminance_setpoint,
+       level_3_lighting_code_definition_id
+FROM level_2_lighting_space_types
+WHERE lighting_space_type_name IN (
+    SELECT lighting_space_type_name 
+    FROM level_2_lighting_space_types 
+    GROUP BY lighting_space_type_name 
+    HAVING COUNT(DISTINCT level_3_lighting_code_definition_table) &gt; 1
+)
+ORDER BY lighting_space_type_name, level_3_lighting_code_definition_table;</t>
+  </si>
+  <si>
+    <t>SELECT DISTINCT lighting_space_type_name,
+       MAX(lighting_space_type_target_illuminance_setpoint) as max_illuminance,
+       lighting_technology_name,
+       lighting_space_type_target_illuminance_setpoint_unit
+FROM level_2_lighting_space_types
+WHERE lighting_space_type_target_illuminance_setpoint &gt; 400
+GROUP BY lighting_space_type_name, lighting_technology_name, lighting_space_type_target_illuminance_setpoint_unit
+ORDER BY max_illuminance DESC;</t>
+  </si>
+  <si>
+    <t>SELECT natural_gas_equipment_space_type_name,
+       natural_gas_equipment_average_epd,
+       natural_gas_equipment_maximum_epd,
+       natural_gas_equipment_fraction_lost,
+       (natural_gas_equipment_fraction_latent + natural_gas_equipment_fraction_radiant) as useful_heat_fraction
+FROM level_2_natural_gas_equipment
+WHERE natural_gas_equipment_average_epd &gt; 100
+ORDER BY natural_gas_equipment_average_epd DESC;</t>
+  </si>
+  <si>
+    <t>Which space types have the highest natural gas equipment loads and what percentage of their heat is lost rather than contributing to space conditioning?</t>
+  </si>
+  <si>
+    <t>Compare the load variability and heat distribution patterns between kitchen-related spaces and other space types?</t>
+  </si>
+  <si>
+    <t>SELECT natural_gas_equipment_space_type_name,
+       natural_gas_equipment_minimum_epd,
+       natural_gas_equipment_median_epd,
+       natural_gas_equipment_maximum_epd,
+       natural_gas_equipment_fraction_latent,
+       natural_gas_equipment_fraction_radiant,
+       natural_gas_equipment_fraction_lost,
+       CASE 
+         WHEN natural_gas_equipment_space_type_name LIKE '%kitchen%' 
+           OR natural_gas_equipment_space_type_name LIKE '%deli%' 
+           OR natural_gas_equipment_space_type_name LIKE '%bakery%' 
+         THEN 'Food Service' 
+         ELSE 'Other' 
+       END as space_category
+FROM level_2_natural_gas_equipment
+ORDER BY space_category, natural_gas_equipment_average_epd DESC;</t>
+  </si>
+  <si>
+    <t>What are the most commonly referenced ventilation definition IDs across all space types, and which standard tables do they belong to?</t>
+  </si>
+  <si>
+    <t>SELECT level_3_ventilation_definition_id,
+       level_3_ventilation_definition_table,
+       COUNT(*) as space_types_using_this_id,
+       STRING_AGG(ventilation_space_type_name, ', ') as space_types
+FROM level_2_ventilation_space_types
+GROUP BY level_3_ventilation_definition_id, level_3_ventilation_definition_table
+HAVING COUNT(*) &gt; 1
+ORDER BY space_types_using_this_id DESC;</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type,
+       lighting_secondary_space_type,
+       lighting_power_density,
+       automatic_full_off,
+       method,
+       annotation
+FROM level_3_lighting_90_1_2004
+WHERE automatic_full_off = 'REQ'
+  AND lighting_power_density &gt;= 1.2
+ORDER BY lighting_power_density DESC;</t>
+  </si>
+  <si>
+    <t>Which space types have the highest lighting power densities and require automatic full-off controls under 90.1-2004?</t>
+  </si>
+  <si>
+    <t>Compare the lighting power density requirements between CS (Complete System) and SS (Space-by-Space) methods for the same space types?</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type,
+       lighting_secondary_space_type,
+       method,
+       lighting_power_density,
+       automatic_full_off
+FROM level_3_lighting_90_1_2004
+WHERE lighting_primary_space_type IN (
+    SELECT lighting_primary_space_type 
+    FROM level_3_lighting_90_1_2004 
+    GROUP BY lighting_primary_space_type, lighting_secondary_space_type
+    HAVING COUNT(DISTINCT method) &gt; 1
+)
+ORDER BY lighting_primary_space_type, lighting_secondary_space_type, method;</t>
+  </si>
+  <si>
+    <t>Which space types in 90.1-2007 have supplemental lighting allowances or special control requirements?</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type,
+       lighting_secondary_space_type,
+       lighting_power_density,
+       supplemental_lighting_power_density,
+       automatic_full_off,
+       scheduled_shutoff,
+       method,
+       annotation
+FROM level_3_lighting_90_1_2007
+WHERE supplemental_lighting_power_density IS NOT NULL
+   OR automatic_full_off IS NOT NULL
+   OR scheduled_shutoff IS NOT NULL
+ORDER BY lighting_power_density DESC;</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type,
+       lighting_secondary_space_type,
+       method,
+       lighting_power_density,
+       automatic_daylight_responsive_controls_for_sidelighting,
+       automatic_daylight_responsive_controls_for_toplighting,
+       annotation
+FROM level_3_lighting_90_1_2010_prm
+WHERE method = 'BA'
+  AND (automatic_daylight_responsive_controls_for_sidelighting = 'REQ' 
+       OR automatic_daylight_responsive_controls_for_toplighting = 'REQ')
+ORDER BY lighting_power_density DESC;</t>
+  </si>
+  <si>
+    <t>Which space types in the PRM baseline have Building Area (BA) method requirements but still need daylight responsive controls?</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type,
+       lighting_secondary_space_type,
+       lighting_power_density,
+       rcr_threshold,
+       automatic_partial_off,
+       automatic_daylight_responsive_controls_for_sidelighting,
+       automatic_daylight_responsive_controls_for_toplighting,
+       annotation
+FROM level_3_lighting_90_1_2013
+WHERE automatic_partial_off = 'REQ'
+  AND rcr_threshold &lt;= 4
+ORDER BY lighting_power_density DESC;</t>
+  </si>
+  <si>
+    <t>Which space types require both automatic partial-off controls AND have the most stringent RCR thresholds?</t>
+  </si>
+  <si>
+    <t>How do the control requirements (ADD2 vs REQ vs null) vary for facilities serving visually impaired populations compared to general spaces?</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type,
+       lighting_secondary_space_type,
+       lighting_power_density,
+       automatic_partial_off,
+       automatic_full_off,
+       scheduled_shutoff,
+       CASE 
+         WHEN lighting_primary_space_type LIKE '%Visually Impaired%' 
+           OR lighting_secondary_space_type LIKE '%visually impaired%'
+         THEN 'Visually Impaired Facility'
+         ELSE 'General Facility'
+       END as facility_type,
+       annotation
+FROM level_3_lighting_90_1_2013
+WHERE lighting_primary_space_type LIKE '%Visually Impaired%' 
+   OR lighting_secondary_space_type LIKE '%visually impaired%'
+   OR lighting_primary_space_type IN ('Lobby', 'Dormitory Living Quarters')
+ORDER BY facility_type, lighting_power_density DESC;</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type,
+       lighting_secondary_space_type,
+       lighting_power_density,
+       automatic_daylight_responsive_controls_for_sidelighting,
+       automatic_partial_off,
+       automatic_full_off,
+       annotation
+FROM level_3_lighting_90_1_2016
+WHERE (lighting_primary_space_type LIKE '%Sports%' 
+       OR lighting_primary_space_type LIKE '%Religious%'
+       OR lighting_primary_space_type LIKE '%Convention%')
+  AND lighting_power_density &gt; 1.0
+ORDER BY lighting_power_density DESC;</t>
+  </si>
+  <si>
+    <t>Which sports and entertainment venues have the highest lighting power densities, and how do their control requirements compare?</t>
+  </si>
+  <si>
+    <t>How do the lighting power densities for retail spaces compare between different retail categories and sections of the code?</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type,
+       lighting_secondary_space_type,
+       lighting_power_density,
+       rcr_threshold,
+       annotation,
+       CASE 
+         WHEN annotation LIKE '%Section 9.6.2%' THEN 'Additional Allowances'
+         WHEN annotation LIKE '%Table 9.6.1%' THEN 'Standard Requirements'
+         ELSE 'Other'
+       END as code_section_type
+FROM level_3_lighting_90_1_2016
+WHERE lighting_primary_space_type LIKE '%Retail%'
+   OR lighting_secondary_space_type LIKE '%Sales%'
+   OR lighting_secondary_space_type LIKE '%Mall%'
+ORDER BY code_section_type, lighting_power_density DESC;</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type,
+       lighting_secondary_space_type,
+       method,
+       lighting_power_density,
+       rcr_threshold,
+       automatic_full_off,
+       automatic_daylight_responsive_controls_for_sidelighting,
+       automatic_daylight_responsive_controls_for_toplighting,
+       annotation
+FROM level_3_lighting_90_1_2010_prm
+WHERE lighting_power_density &gt; 1.0
+  AND automatic_full_off = 'REQ'
+ORDER BY lighting_power_density DESC;</t>
+  </si>
+  <si>
+    <t>Which space types in the 2010 PRM baseline require automatic full-off controls and have lighting power densities above 1.0 W/ft²?</t>
+  </si>
+  <si>
+    <t>Which space types require both automatic partial-off controls AND daylight responsive controls, and how do their lighting power densities compare?</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type,
+       lighting_secondary_space_type,
+       lighting_power_density,
+       rcr_threshold,
+       automatic_partial_off,
+       automatic_daylight_responsive_controls_for_sidelighting,
+       automatic_daylight_responsive_controls_for_toplighting,
+       annotation
+FROM level_3_lighting_90_1_2019
+WHERE automatic_partial_off = 'REQ'
+  AND automatic_daylight_responsive_controls_for_sidelighting = 'REQ'
+ORDER BY lighting_power_density DESC;</t>
+  </si>
+  <si>
+    <t>What are the most energy-intensive laboratory and healthcare spaces, and how do their control requirements differ?</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type,
+       lighting_secondary_space_type,
+       lighting_power_density,
+       automatic_full_off,
+       scheduled_shutoff,
+       rcr_threshold,
+       annotation
+FROM level_3_lighting_90_1_2019
+WHERE (lighting_primary_space_type LIKE '%Laboratory%' 
+       OR lighting_primary_space_type LIKE '%Healthcare%')
+  AND lighting_power_density &gt; 1.0
+ORDER BY lighting_power_density DESC;</t>
+  </si>
+  <si>
+    <t>Which space types have the most restrictive RCR thresholds (≤4) but still allow ADD2 (additional) controls instead of requiring them?</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type,
+       lighting_secondary_space_type,
+       lighting_power_density,
+       rcr_threshold,
+       automatic_full_off,
+       scheduled_shutoff,
+       automatic_daylight_responsive_controls_for_sidelighting,
+       annotation
+FROM level_3_lighting_90_1_2022
+WHERE rcr_threshold &lt;= 4
+  AND (automatic_full_off = 'ADD2' OR scheduled_shutoff = 'ADD2')
+ORDER BY rcr_threshold, lighting_power_density DESC;</t>
+  </si>
+  <si>
+    <t>How do the lighting requirements for facilities serving the visually impaired compare to general facilities in terms of power density and control flexibility?</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type,
+       lighting_secondary_space_type,
+       lighting_power_density,
+       automatic_full_off,
+       scheduled_shutoff,
+       rcr_threshold,
+       CASE 
+         WHEN lighting_primary_space_type LIKE '%Visually Impaired%' 
+         THEN 'Visually Impaired Facility'
+         ELSE 'General Facility'
+       END as facility_type,
+       annotation
+FROM level_3_lighting_90_1_2022
+WHERE lighting_primary_space_type LIKE '%Visually Impaired%'
+   OR lighting_primary_space_type IN ('Conference/Meeting/Multipurpose Rooms', 'Dining Area')
+ORDER BY facility_type, lighting_power_density DESC;</t>
+  </si>
+  <si>
+    <t>Which healthcare facility spaces have the highest lighting power densities, and how do they compare to other high-intensity space types?</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type,
+       lighting_secondary_space_type,
+       lighting_power_density,
+       method,
+       annotation
+FROM level_3_lighting_IECC_2006
+WHERE lighting_primary_space_type = 'Healthcare Facility'
+  AND lighting_power_density &gt;= 1.0
+ORDER BY lighting_power_density DESC;</t>
+  </si>
+  <si>
+    <t>What's the range of lighting power densities for sports and entertainment venues, and how do they vary by facility class or type?</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type,
+       lighting_secondary_space_type,
+       lighting_power_density,
+       method,
+       annotation
+FROM level_3_lighting_IECC_2006
+WHERE (lighting_primary_space_type LIKE '%Sports%' 
+       OR lighting_primary_space_type LIKE '%Audience%'
+       OR lighting_secondary_space_type LIKE '%Class%'
+       OR lighting_secondary_space_type LIKE '%sports arena%')
+ORDER BY lighting_power_density DESC;</t>
+  </si>
+  <si>
+    <t>SELECT ventilation_primary_space_type,
+       ventilation_secondary_space_type,
+       ventilation_rate_occupant,
+       ventilation_rate_area,
+       occupancy_per_area,
+       annotation
+FROM level_3_ventilation_62_1_1999
+WHERE ventilation_rate_occupant = 0
+  AND ventilation_rate_area &gt; 0.3
+ORDER BY ventilation_rate_area DESC;</t>
+  </si>
+  <si>
+    <t>Which space types rely purely on area-based ventilation (no per-person requirements) and have high ventilation rates above 0.3 cfm/ft²?</t>
+  </si>
+  <si>
+    <t>How do the ventilation requirements differ between educational spaces (classrooms vs labs vs auditoriums) in terms of per-person and occupancy assumptions?</t>
+  </si>
+  <si>
+    <t>SELECT ventilation_primary_space_type,
+       ventilation_secondary_space_type,
+       ventilation_rate_occupant,
+       ventilation_rate_area,
+       occupancy_per_area,
+       annotation
+FROM level_3_ventilation_62_1_1999
+WHERE ventilation_primary_space_type = 'Education'
+ORDER BY ventilation_rate_occupant DESC, occupancy_per_area DESC;</t>
+  </si>
+  <si>
+    <t>Which space types are classified as Air Class 2 (higher contamination) and how do their ventilation rates compare to Air Class 1 spaces?</t>
+  </si>
+  <si>
+    <t>SELECT ventilation_primary_space_type,
+       ventilation_secondary_space_type,
+       air_class,
+       ventilation_rate_occupant,
+       ventilation_rate_area,
+       occupancy_per_area,
+       annotation
+FROM level_3_ventilation_62_1_2004
+WHERE air_class = 2
+ORDER BY ventilation_rate_area DESC, ventilation_rate_occupant DESC;</t>
+  </si>
+  <si>
+    <t>How do food service spaces compare in terms of ventilation requirements, and which have the highest per-person ventilation needs?</t>
+  </si>
+  <si>
+    <t>SELECT ventilation_primary_space_type,
+       ventilation_secondary_space_type,
+       ventilation_rate_occupant,
+       ventilation_rate_area,
+       occupancy_per_area,
+       air_class,
+       annotation
+FROM level_3_ventilation_62_1_2004
+WHERE ventilation_primary_space_type = 'Food and Beverage Service'
+ORDER BY ventilation_rate_occupant DESC, ventilation_rate_area DESC;</t>
+  </si>
+  <si>
+    <t>Which space types have both high occupancy density (&gt;100 ppl/1000 ft²) AND require significant per-person ventilation rates?</t>
+  </si>
+  <si>
+    <t>SELECT ventilation_primary_space_type,
+       ventilation_secondary_space_type,
+       ventilation_rate_occupant,
+       ventilation_rate_area,
+       occupancy_per_area,
+       air_class,
+       annotation
+FROM level_3_ventilation_62_1_2007
+WHERE occupancy_per_area &gt; 100
+  AND ventilation_rate_occupant &gt; 5
+ORDER BY occupancy_per_area DESC, ventilation_rate_occupant DESC;</t>
+  </si>
+  <si>
+    <t>How do sports and entertainment venues vary in their ventilation strategies between spectator areas and active play areas?</t>
+  </si>
+  <si>
+    <t>SELECT ventilation_primary_space_type,
+       ventilation_secondary_space_type,
+       ventilation_rate_occupant,
+       ventilation_rate_area,
+       occupancy_per_area,
+       air_class,
+       annotation
+FROM level_3_ventilation_62_1_2007
+WHERE ventilation_primary_space_type = 'Sports and Entertainment'
+ORDER BY ventilation_rate_area DESC, ventilation_rate_occupant DESC;</t>
+  </si>
+  <si>
+    <t>Which insulation materials provide the highest thermal resistance per inch of thickness, and how do their densities compare?</t>
+  </si>
+  <si>
+    <t>SELECT name,
+       material_type,
+       thickness,
+       resistance,
+       (resistance / thickness) as resistance_per_inch,
+       density,
+       conductivity,
+       annotation
+FROM support_materials
+WHERE material_type = 'StandardOpaqueMaterial'
+  AND resistance &gt; 20
+  AND thickness &gt; 0
+ORDER BY resistance_per_inch DESC;</t>
+  </si>
+  <si>
+    <t>SELECT name,
+       thickness,
+       conductivity,
+       resistance,
+       density,
+       specific_heat,
+       annotation
+FROM support_materials
+WHERE name LIKE '%Glass fiber batt%'
+  AND name LIKE '%CEC Default%'
+ORDER BY resistance DESC, thickness;</t>
+  </si>
+  <si>
+    <t>How do the thermal properties of glass fiber batt insulations vary by R-value and thickness across different CEC defaults?</t>
+  </si>
+  <si>
+    <t>How do economizer control strategies differ between data centers and regular buildings across different climate zones?</t>
+  </si>
+  <si>
+    <t>SELECT template,
+       climate_zone,
+       data_center,
+       fixed_dry_bulb_is_allowed,
+       differential_dry_bulb_is_allowed,
+       electronic_enthalpy_is_allowed,
+       differential_enthalpy_is_allowed,
+       dew_point_dry_bulb_is_allowed,
+       heat_recovery_exempted,
+       annotation
+FROM system_requirements_air_economizer_90_1
+WHERE template = '90.1-2010'
+  AND climate_zone IN ('2A', '3A', '4A')
+ORDER BY data_center DESC, climate_zone;</t>
+  </si>
+  <si>
+    <t>What are the high limit shutoff temperatures and enthalpies for different economizer control strategies, and how have they evolved between 90.1-2004 and 90.1-2010?</t>
+  </si>
+  <si>
+    <t>SELECT template,
+       climate_zone,
+       data_center,
+       fixed_dry_bulb_high_limit_shutoff_temp,
+       fixed_enthalpy_high_limit_shutoff_enthalpy,
+       dew_point_dry_bulb_high_limit_shutoff_dew_point_temp,
+       dew_point_dry_bulb_high_limit_shutoff_dry_bulb_temp,
+       annotation
+FROM system_requirements_air_economizer_90_1
+WHERE template IN ('90.1-2004', '90.1-2010')
+  AND climate_zone = '3A'
+ORDER BY template, data_center;</t>
+  </si>
+  <si>
+    <t>SELECT template,
+       climate_zone,
+       under_8000_hours,
+       design_conditions,
+       percent_oa_70_to_80,
+       percent_oa_greater_than_80,
+       energy_recovery_effectiveness,
+       enthalpy_recovery_ratio,
+       sensible_energy_recovery_ratio,
+       annotation
+FROM system_requirements_energy_recovery_90_1
+WHERE percent_oa_greater_than_80 IS NOT NULL
+  AND percent_oa_greater_than_80 &lt; 5000
+ORDER BY percent_oa_greater_than_80, climate_zone;</t>
+  </si>
+  <si>
+    <t>Which climate zones require energy recovery for the smallest outdoor air CFM thresholds, and how do the effectiveness requirements vary?</t>
+  </si>
+  <si>
+    <t>How do energy recovery requirements differ between heating and cooling design conditions for cold climates (zones 6-8)?</t>
+  </si>
+  <si>
+    <t>SELECT template,
+       climate_zone,
+       design_conditions,
+       under_8000_hours,
+       percent_oa_30_to_40,
+       percent_oa_40_to_50,
+       percent_oa_50_to_60,
+       energy_recovery_effectiveness,
+       annotation
+FROM system_requirements_energy_recovery_90_1
+WHERE climate_zone IN ('6A', '6B', '7A', '7B', '8')
+  AND template = '90.1-2013'
+ORDER BY climate_zone, design_conditions;</t>
+  </si>
+  <si>
+    <t>How do the outdoor air percentage thresholds for energy recovery requirements differ between humid (A) and dry (B) climate zones in IECC-2012?</t>
+  </si>
+  <si>
+    <t>SELECT template, climate_zone, design_conditions, percent_oa_30_to_40, percent_oa_40_to_50, percent_oa_50_to_60, percent_oa_60_to_70, percent_oa_70_to_80, percent_oa_greater_than_80, energy_recovery_effectiveness, CASE WHEN climate_zone LIKE '%A' THEN 'Humid' WHEN climate_zone LIKE '%B' THEN 'Dry' ELSE 'Other' END as moisture_regime, annotation FROM system_requirements_energy_recovery_IECC WHERE template = 'IECC-2012' AND climate_zone IN ('1A', '1B', '2A', '2B', '3A', '3B') ORDER BY moisture_regime, climate_zone, design_conditions;</t>
+  </si>
+  <si>
+    <t>Which climate zones completely exempt certain outdoor air percentage ranges from energy recovery requirements, and how have these exemptions evolved from IECC-2009 to IECC-2012?</t>
+  </si>
+  <si>
+    <t>SELECT template, climate_zone, design_conditions, percent_oa_50_to_60, percent_oa_60_to_70, percent_oa_70_to_80, percent_oa_greater_than_80, energy_recovery_effectiveness, annotation FROM system_requirements_energy_recovery_IECC WHERE (percent_oa_50_to_60 IS NULL OR percent_oa_60_to_70 IS NULL OR percent_oa_70_to_80 IS NULL OR percent_oa_greater_than_80 IS NULL) AND template IN ('IECC-2009', 'IECC-2012') ORDER BY template, climate_zone;</t>
+  </si>
+  <si>
+    <t>How do the fan power allowances compare between different filtration levels (MERV 12 vs MERV 13-16 vs HEPA) across different system capacities?</t>
+  </si>
+  <si>
+    <t>SELECT template, air_system_component, minimum_capacity, maximum_capacity, fan_power_allowance, fan_system, annotation FROM system_requirements_fan_power_allowance_90_1 WHERE air_system_component IN ('Filter not higher than MERV 12', 'MERV 13 to MERV 16 filter', 'HEPA filter') ORDER BY minimum_capacity, fan_power_allowance;</t>
+  </si>
+  <si>
+    <t>What are the highest fan power allowances for energy recovery components, and how do they compare between supply and exhaust systems?</t>
+  </si>
+  <si>
+    <t>SELECT template, air_system, air_system_component, fan_system, minimum_capacity, maximum_capacity, fan_power_allowance, annotation FROM system_requirements_fan_power_allowance_90_1 WHERE (air_system_component LIKE '%recovery%' OR air_system_component LIKE '%enthalpy%' OR air_system_component LIKE '%run-around%') AND template = '90.1-2025' ORDER BY fan_power_allowance DESC, air_system;</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -477,13 +1070,46 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="4"/>
+      <color rgb="FF171717"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -498,12 +1124,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -550,8 +1194,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0C8568FE-6704-4958-8B79-579C6A959B01}" name="Table1" displayName="Table1" ref="B1:C32" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2">
-  <autoFilter ref="B1:C32" xr:uid="{0C8568FE-6704-4958-8B79-579C6A959B01}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0C8568FE-6704-4958-8B79-579C6A959B01}" name="Table1" displayName="Table1" ref="B1:C64" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2">
+  <autoFilter ref="B1:C64" xr:uid="{0C8568FE-6704-4958-8B79-579C6A959B01}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{0458D18D-3D29-4D20-8D9F-298C1BBCB325}" name="answer" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{2CB46501-370C-4514-802F-F7A4E1E87BAA}" name="question" dataDxfId="0"/>
@@ -877,16 +1521,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CDBA05A-EE27-4D14-81B9-A7E66315CCFE}">
-  <dimension ref="B1:C49"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="B1:M80"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
-    <col min="2" max="2" width="50.33203125" customWidth="1"/>
-    <col min="3" max="3" width="52.5" customWidth="1"/>
+    <col min="1" max="1" width="8.83984375" customWidth="1"/>
+    <col min="2" max="2" width="50.26171875" customWidth="1"/>
+    <col min="3" max="3" width="52.578125" customWidth="1"/>
     <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:3" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
@@ -894,7 +1538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="2:3" ht="128" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:3" ht="115.2" x14ac:dyDescent="0.55000000000000004">
       <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
@@ -902,7 +1546,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="2:3" ht="160" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:3" ht="144" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
@@ -910,7 +1554,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:3" ht="128" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:3" ht="115.2" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
@@ -918,7 +1562,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="2:3" ht="48" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="1" t="s">
         <v>8</v>
       </c>
@@ -926,7 +1570,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="2:3" ht="48" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="1" t="s">
         <v>11</v>
       </c>
@@ -934,7 +1578,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="2:3" ht="80" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:3" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="1" t="s">
         <v>12</v>
       </c>
@@ -942,7 +1586,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="2:3" ht="144" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:3" ht="144" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" s="1" t="s">
         <v>14</v>
       </c>
@@ -950,7 +1594,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="2:3" ht="48" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" s="1" t="s">
         <v>16</v>
       </c>
@@ -958,7 +1602,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="2:3" ht="240" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:3" ht="216" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" s="1" t="s">
         <v>18</v>
       </c>
@@ -966,7 +1610,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="2:3" ht="256" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:3" ht="230.4" x14ac:dyDescent="0.55000000000000004">
       <c r="B11" s="1" t="s">
         <v>20</v>
       </c>
@@ -974,7 +1618,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="2:3" ht="224" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:3" ht="201.6" x14ac:dyDescent="0.55000000000000004">
       <c r="B12" s="1" t="s">
         <v>23</v>
       </c>
@@ -982,7 +1626,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="2:3" ht="272" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:3" ht="244.8" x14ac:dyDescent="0.55000000000000004">
       <c r="B13" s="1" t="s">
         <v>25</v>
       </c>
@@ -990,7 +1634,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="2:3" ht="256" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:3" ht="244.8" x14ac:dyDescent="0.55000000000000004">
       <c r="B14" s="1" t="s">
         <v>28</v>
       </c>
@@ -998,7 +1642,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="2:3" ht="288" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:3" ht="273.60000000000002" x14ac:dyDescent="0.55000000000000004">
       <c r="B15" s="1" t="s">
         <v>29</v>
       </c>
@@ -1006,7 +1650,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="2:3" ht="256" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:3" ht="244.8" x14ac:dyDescent="0.55000000000000004">
       <c r="B16" s="1" t="s">
         <v>30</v>
       </c>
@@ -1014,7 +1658,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="2:3" ht="304" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:13" ht="302.39999999999998" x14ac:dyDescent="0.55000000000000004">
       <c r="B17" s="1" t="s">
         <v>33</v>
       </c>
@@ -1022,7 +1666,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="2:3" ht="224" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:13" ht="201.6" x14ac:dyDescent="0.55000000000000004">
       <c r="B18" s="1" t="s">
         <v>35</v>
       </c>
@@ -1030,7 +1674,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="2:3" ht="176" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:13" ht="158.4" x14ac:dyDescent="0.55000000000000004">
       <c r="B19" s="1" t="s">
         <v>37</v>
       </c>
@@ -1038,7 +1682,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="2:3" ht="224" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:13" ht="201.6" x14ac:dyDescent="0.55000000000000004">
       <c r="B20" s="1" t="s">
         <v>39</v>
       </c>
@@ -1046,7 +1690,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="2:3" ht="240" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:13" ht="216" x14ac:dyDescent="0.55000000000000004">
       <c r="B21" s="1" t="s">
         <v>41</v>
       </c>
@@ -1054,7 +1698,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="2:3" ht="320" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:13" ht="288" x14ac:dyDescent="0.55000000000000004">
       <c r="B22" s="1" t="s">
         <v>43</v>
       </c>
@@ -1062,7 +1706,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="2:3" ht="256" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:13" ht="230.4" x14ac:dyDescent="0.55000000000000004">
       <c r="B23" s="1" t="s">
         <v>45</v>
       </c>
@@ -1070,7 +1714,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="24" spans="2:3" ht="288" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:13" ht="259.2" x14ac:dyDescent="0.55000000000000004">
       <c r="B24" s="1" t="s">
         <v>47</v>
       </c>
@@ -1078,7 +1722,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="25" spans="2:3" ht="128" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:13" ht="129.6" x14ac:dyDescent="0.55000000000000004">
       <c r="B25" s="1" t="s">
         <v>49</v>
       </c>
@@ -1086,7 +1730,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="2:3" ht="240" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:13" ht="216" x14ac:dyDescent="0.55000000000000004">
       <c r="B26" s="1" t="s">
         <v>50</v>
       </c>
@@ -1094,95 +1738,391 @@
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-    </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-    </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-    </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-    </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-    </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-    </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-    </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-    </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-    </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
-    </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-    </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
-    </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B39" s="1"/>
-      <c r="C39" s="1"/>
-    </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B40" s="1"/>
-      <c r="C40" s="1"/>
-    </row>
-    <row r="41" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B41" s="1"/>
-      <c r="C41" s="1"/>
-    </row>
-    <row r="42" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B42" s="1"/>
-      <c r="C42" s="1"/>
-    </row>
-    <row r="43" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B43" s="1"/>
-      <c r="C43" s="1"/>
-    </row>
-    <row r="44" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B44" s="1"/>
-      <c r="C44" s="1"/>
-    </row>
-    <row r="45" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B45" s="1"/>
-      <c r="C45" s="1"/>
-    </row>
-    <row r="46" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="C46" s="1"/>
-    </row>
-    <row r="47" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="C47" s="1"/>
-    </row>
-    <row r="48" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="C48" s="1"/>
-    </row>
-    <row r="49" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C49" s="1"/>
+    <row r="27" spans="2:13" ht="172.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B27" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" spans="2:13" ht="129.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B28" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="4"/>
+      <c r="L28" s="3"/>
+      <c r="M28" s="3"/>
+    </row>
+    <row r="29" spans="2:13" ht="201.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B29" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="30" spans="2:13" ht="158.4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B30" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G30" s="5"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="6"/>
+      <c r="K30" s="5"/>
+      <c r="L30" s="5"/>
+    </row>
+    <row r="31" spans="2:13" ht="144" x14ac:dyDescent="0.55000000000000004">
+      <c r="B31" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="32" spans="2:13" ht="288" x14ac:dyDescent="0.55000000000000004">
+      <c r="B32" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" ht="144" x14ac:dyDescent="0.55000000000000004">
+      <c r="B33" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" ht="144" x14ac:dyDescent="0.55000000000000004">
+      <c r="B34" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3" ht="216" x14ac:dyDescent="0.55000000000000004">
+      <c r="B35" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3" ht="187.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B36" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3" ht="201.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B37" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="38" spans="2:3" ht="187.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B38" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3" ht="172.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B39" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3" ht="316.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B40" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="41" spans="2:3" ht="187.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B41" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="42" spans="2:3" ht="244.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B42" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="43" spans="2:3" ht="187.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B43" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="44" spans="2:3" ht="172.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B44" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="45" spans="2:3" ht="187.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B45" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="46" spans="2:3" ht="273.60000000000002" x14ac:dyDescent="0.55000000000000004">
+      <c r="B46" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="47" spans="2:3" ht="129.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B47" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="48" spans="2:3" ht="158.4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B48" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="49" spans="2:9" ht="144" x14ac:dyDescent="0.55000000000000004">
+      <c r="B49" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="50" spans="2:9" ht="144" x14ac:dyDescent="0.55000000000000004">
+      <c r="B50" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="51" spans="2:9" ht="158.4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B51" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="52" spans="2:9" ht="172.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B52" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="53" spans="2:9" ht="172.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B53" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="54" spans="2:9" ht="172.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B54" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="55" spans="2:9" ht="187.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B55" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="56" spans="2:9" ht="158.4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B56" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="57" spans="2:9" ht="201.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B57" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="58" spans="2:9" ht="172.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B58" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="59" spans="2:9" ht="201.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B59" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="60" spans="2:9" ht="187.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B60" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="61" spans="2:9" ht="158.4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B61" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="I61" s="8"/>
+    </row>
+    <row r="62" spans="2:9" ht="129.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B62" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="I62" s="8"/>
+    </row>
+    <row r="63" spans="2:9" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B63" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="I63" s="8"/>
+    </row>
+    <row r="64" spans="2:9" ht="115.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B64" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="I64" s="8"/>
+    </row>
+    <row r="65" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B65" s="1"/>
+      <c r="C65" s="1"/>
+    </row>
+    <row r="66" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B66" s="1"/>
+      <c r="C66" s="1"/>
+    </row>
+    <row r="67" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B67" s="1"/>
+      <c r="C67" s="1"/>
+    </row>
+    <row r="68" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B68" s="1"/>
+      <c r="C68" s="1"/>
+    </row>
+    <row r="69" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B69" s="1"/>
+      <c r="C69" s="1"/>
+    </row>
+    <row r="70" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B70" s="1"/>
+      <c r="C70" s="1"/>
+    </row>
+    <row r="71" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B71" s="1"/>
+      <c r="C71" s="1"/>
+    </row>
+    <row r="72" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B72" s="1"/>
+      <c r="C72" s="1"/>
+    </row>
+    <row r="73" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B73" s="1"/>
+      <c r="C73" s="1"/>
+    </row>
+    <row r="74" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B74" s="1"/>
+      <c r="C74" s="1"/>
+    </row>
+    <row r="75" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B75" s="1"/>
+      <c r="C75" s="1"/>
+    </row>
+    <row r="76" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B76" s="1"/>
+      <c r="C76" s="1"/>
+    </row>
+    <row r="77" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="C77" s="1"/>
+    </row>
+    <row r="78" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="C78" s="1"/>
+    </row>
+    <row r="79" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="C79" s="1"/>
+    </row>
+    <row r="80" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="C80" s="1"/>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="E28:F35">
+    <sortCondition ref="F28:F35"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/fine_tuning/dataset/raw/building_std_queries.xlsx
+++ b/fine_tuning/dataset/raw/building_std_queries.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gonz102\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\building_energy_standards_data\fine_tuning\dataset\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BB655F2-98DC-407C-A1BE-46D8721DCEDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A66CC8A7-704E-4E12-A28C-B49D651AF65C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{77D55900-27DC-4083-93B9-DD1815E6B0C1}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1026" uniqueCount="991">
   <si>
     <t>answer</t>
   </si>
@@ -457,9 +457,6 @@
     <t>Which space types share the same electric equipment profiles but have different ventilation requirements, and how do their schedule patterns compare?</t>
   </si>
   <si>
-    <t>What space types have electric equipment loads above 0.7 W/ft² and generate latent heat gains?</t>
-  </si>
-  <si>
     <t>Which space types have the highest variability in electric equipment loads, and what are their heat gain characteristics?</t>
   </si>
   <si>
@@ -724,9 +721,6 @@
 ORDER BY lighting_power_density DESC;</t>
   </si>
   <si>
-    <t>Which space types in the 2010 PRM baseline require automatic full-off controls and have lighting power densities above 1.0 W/ft²?</t>
-  </si>
-  <si>
     <t>Which space types require both automatic partial-off controls AND daylight responsive controls, and how do their lighting power densities compare?</t>
   </si>
   <si>
@@ -759,9 +753,6 @@
        OR lighting_primary_space_type LIKE '%Healthcare%')
   AND lighting_power_density &gt; 1.0
 ORDER BY lighting_power_density DESC;</t>
-  </si>
-  <si>
-    <t>Which space types have the most restrictive RCR thresholds (≤4) but still allow ADD2 (additional) controls instead of requiring them?</t>
   </si>
   <si>
     <t>SELECT lighting_primary_space_type,
@@ -841,9 +832,6 @@
 ORDER BY ventilation_rate_area DESC;</t>
   </si>
   <si>
-    <t>Which space types rely purely on area-based ventilation (no per-person requirements) and have high ventilation rates above 0.3 cfm/ft²?</t>
-  </si>
-  <si>
     <t>How do the ventilation requirements differ between educational spaces (classrooms vs labs vs auditoriums) in terms of per-person and occupancy assumptions?</t>
   </si>
   <si>
@@ -886,9 +874,6 @@
 FROM level_3_ventilation_62_1_2004
 WHERE ventilation_primary_space_type = 'Food and Beverage Service'
 ORDER BY ventilation_rate_occupant DESC, ventilation_rate_area DESC;</t>
-  </si>
-  <si>
-    <t>Which space types have both high occupancy density (&gt;100 ppl/1000 ft²) AND require significant per-person ventilation rates?</t>
   </si>
   <si>
     <t>SELECT ventilation_primary_space_type,
@@ -1049,12 +1034,2616 @@
   <si>
     <t>SELECT template, air_system, air_system_component, fan_system, minimum_capacity, maximum_capacity, fan_power_allowance, annotation FROM system_requirements_fan_power_allowance_90_1 WHERE (air_system_component LIKE '%recovery%' OR air_system_component LIKE '%enthalpy%' OR air_system_component LIKE '%run-around%') AND template = '90.1-2025' ORDER BY fan_power_allowance DESC, air_system;</t>
   </si>
+  <si>
+    <t>SELECT natural_gas_equipment_space_type_name, natural_gas_equipment_average_epd, natural_gas_equipment_fraction_lost FROM level_2_natural_gas_equipment WHERE natural_gas_equipment_average_epd &gt; 100 ORDER BY natural_gas_equipment_average_epd DESC</t>
+  </si>
+  <si>
+    <t>Which space types have the most restrictive RCR thresholds (?4) but still allow ADD2 (additional) controls instead of requiring them?</t>
+  </si>
+  <si>
+    <t>What are the highest fan power allowances for energy recovery components in ASHRAE 90.1-2025, and how do they compare between supply and exhaust systems?</t>
+  </si>
+  <si>
+    <t>Which space types have the highest natural gas equipment loads and what percentage of their heat is lost rather than contributing to space conditioning in ASHRAE 90.1-2019?</t>
+  </si>
+  <si>
+    <t>What space types have electric equipment loads above 0.7 W/ftÂ² and generate latent heat gains?</t>
+  </si>
+  <si>
+    <t>Which space types in the 2010 PRM baseline require automatic full-off controls and have lighting power densities above 1.0 W/ftÂ²?</t>
+  </si>
+  <si>
+    <t>Which space types rely purely on area-based ventilation (no per-person requirements) and have high ventilation rates above 0.3 cfm/ftÂ²?</t>
+  </si>
+  <si>
+    <t>Which space types have both high occupancy density (&gt;100 ppl/1000 ftÂ²) AND require significant per-person ventilation rates?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for buildings in climate zones 4 and 5, specifically for walls and roofs?</t>
+  </si>
+  <si>
+    <t>What are the maximum U-values for walls and roofs in IECC, specifically for residential buildings?</t>
+  </si>
+  <si>
+    <t>How do the lighting power densities compare between retail spaces and warehouses in IECC?</t>
+  </si>
+  <si>
+    <t>How do the envelope requirements for buildings in climate zone 7 compare to those in climate zone 8, specifically for walls and roofs?</t>
+  </si>
+  <si>
+    <t>What are the maximum solar heat gain coefficients for windows in IECC, specifically for residential buildings?</t>
+  </si>
+  <si>
+    <t>Which climate zones have the most stringent envelope requirements for walls in ASHRAE 90.1-2013 standards?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for residential buildings in climate zones 6 and 7 under ASHRAE 90.1-2010 standards?</t>
+  </si>
+  <si>
+    <t>Which equipment types have the highest minimum annual fuel utilization efficiency in ASHRAE 90.1-2019 standards?</t>
+  </si>
+  <si>
+    <t>How do the ventilation rates compare between educational spaces and office spaces in terms of per-person and occupancy assumptions?</t>
+  </si>
+  <si>
+    <t>Which climate zones have the most restrictive envelope requirements for roofs in terms of U-values and solar heat gain coefficients?</t>
+  </si>
+  <si>
+    <t>What are the energy recovery requirements for heating and cooling design conditions in cold climates (zones 6-8) for ASHRAE 90.1-2013?</t>
+  </si>
+  <si>
+    <t>How do the envelope requirements differ between walls and roofs in terms of U-values and solar heat gain coefficients for ASHRAE 90.1-2013?</t>
+  </si>
+  <si>
+    <t>What are the ventilation requirements for educational spaces in terms of per-person and occupancy assumptions for ASHRAE 62.1-1999?</t>
+  </si>
+  <si>
+    <t>Which climate zones have the most lenient envelope requirements for walls in terms of U-values and solar heat gain coefficients for IECC?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for commercial buildings in climate zones 3 and 4, with a focus on roofs and walls?</t>
+  </si>
+  <si>
+    <t>Which space types have the highest lighting power densities in the 2016 ASHRAE 90.1 standard, and what are their control requirements?</t>
+  </si>
+  <si>
+    <t>What are the lighting requirements for sports and entertainment venues in the 2016 ASHRAE 90.1 standard, and how do they compare to other space types?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for buildings in climate zones 5 and 6, with a focus on walls and floors?</t>
+  </si>
+  <si>
+    <t>What are the fan power allowances for energy recovery components in supply and exhaust systems in the 2025 ASHRAE 90.1 standard?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for walls in climate zones 4 and 5 according to ASHRAE 90.1?</t>
+  </si>
+  <si>
+    <t>Which space types have the highest lighting power densities and require automatic partial-off controls according to IECC?</t>
+  </si>
+  <si>
+    <t>What are the fan power allowances for systems with MERV 13-16 filters in ASHRAE 90.1?</t>
+  </si>
+  <si>
+    <t>Which building types have the most stringent envelope requirements for roofs according to ASHRAE 90.1?</t>
+  </si>
+  <si>
+    <t>What are the ventilation rates for spaces with Air Class 2 (higher contamination) according to ASHRAE 62.1-2004?</t>
+  </si>
+  <si>
+    <t>Which sports and entertainment venues have the highest lighting power densities and require automatic daylight responsive controls according to ASHRAE 90.1-2016?</t>
+  </si>
+  <si>
+    <t>Which equipment types have the highest integrated part load values according to ASHRAE 90.1?</t>
+  </si>
+  <si>
+    <t>What are the lighting power densities for office spaces with automatic partial-off controls according to ASHRAE 90.1-2013?</t>
+  </si>
+  <si>
+    <t>What are the maximum permitted assembly U-values for residential exterior walls in Climate Zone 6 according to ASHRAE 90.1-2004?</t>
+  </si>
+  <si>
+    <t>How do the assembly maximum solar heat gain coefficients (SHGC) for commercial skylights differ between Climate Zones 2 and 5 under ASHRAE 90.1-2016?</t>
+  </si>
+  <si>
+    <t>What are the control requirements for laboratory spaces under ASHRAE 90.1-2019?</t>
+  </si>
+  <si>
+    <t>Which space types in the ASHRAE 90.1-2010 standard have lighting power densities above 1.2 W/ftÂ² and require automatic full-off controls?</t>
+  </si>
+  <si>
+    <t>How do the envelope requirements for walls in climate zones 4 and 5 compare to those in climate zone 7 in terms of maximum U-value?</t>
+  </si>
+  <si>
+    <t>Which building categories have electric equipment loads above 0.5 W/ftÂ² and generate latent heat gains in the ASHRAE 90.1-2013 standard?</t>
+  </si>
+  <si>
+    <t>What's the performance difference between standard and high-efficiency single-package heat pumps for mid-size applications across different rating conditions in the ASHRAE 90.1-2010 standard?</t>
+  </si>
+  <si>
+    <t>Which space types in the ASHRAE 90.1-2013 standard have natural gas equipment loads above 0.2 W/ftÂ² and generate radiant heat gains?</t>
+  </si>
+  <si>
+    <t>How do the envelope requirements for roofs in climate zones 3 and 4 compare to those in climate zone 6 in terms of maximum solar heat gain coefficient?</t>
+  </si>
+  <si>
+    <t>What are the maximum U-values for walls in climate zones 4 and 5 in IECC?</t>
+  </si>
+  <si>
+    <t>How do the control requirements for facilities serving visually impaired populations compare to general spaces in ASHRAE 90.1-2013?</t>
+  </si>
+  <si>
+    <t>What are the most commonly referenced ventilation definition IDs for office spaces in ASHRAE 90.1-2010, and which standard tables do they belong to?</t>
+  </si>
+  <si>
+    <t>What are the minimum part load efficiency requirements for water-cooled screw chillers installed in 2015 or later in IECC?</t>
+  </si>
+  <si>
+    <t>What are the maximum solar heat gain coefficients for roofs in climate zones 6 and 7 in ASHRAE 90.1-2010?</t>
+  </si>
+  <si>
+    <t>How do the control requirements for natural gas equipment compare to electric equipment in ASHRAE 90.1-2013?</t>
+  </si>
+  <si>
+    <t>What are the minimum visible transmittance requirements for windows in climate zones 3 and 4 in IECC?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for roofs in climate zones 4 or 5 under ASHRAE 90.1-2013?</t>
+  </si>
+  <si>
+    <t>What SCOP is required for a 100 kBtu/hr air cooled downflow computer room air conditioner installed in 2010?</t>
+  </si>
+  <si>
+    <t>How do the efficiency requirements differ between enclosed and open motor designs for the same horsepower range under ASHRAE 90.1-2007?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for walls in climate zones 7 or 8 under IECC?</t>
+  </si>
+  <si>
+    <t>Which space types have supplemental lighting allowances or special control requirements under ASHRAE 90.1-2004?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for floors in climate zones 3 or 4 under ASHRAE 90.1-2007?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for commercial buildings in Climate Zone 4 or 5 with roof intended surface type?</t>
+  </si>
+  <si>
+    <t>How do residential buildings in Climate Zone 3 or 4 vary in their envelope requirements for walls with insulation layers?</t>
+  </si>
+  <si>
+    <t>Which ventilation space types in ASHRAE 62.1-2007 have occupancy per area greater than 10 people/1000 ftÂ²?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for educational buildings in Climate Zone 6 or 7 with roof intended surface type and insulation layers?</t>
+  </si>
+  <si>
+    <t>Which lighting space types in ASHRAE 90.1-2010 have target illuminance setpoints greater than 30 fc?</t>
+  </si>
+  <si>
+    <t>How do commercial buildings in Climate Zone 2 or 3 vary in their envelope requirements for walls with skylight framing?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for walls in ASHRAE 90.1-2010, and how do they vary across different climate zones?</t>
+  </si>
+  <si>
+    <t>Which space types in IECC have the highest lighting power densities, and what are their corresponding lighting primary space types?</t>
+  </si>
+  <si>
+    <t>How do the outdoor air percentage thresholds for energy recovery requirements differ between humid and dry climate zones in ASHRAE 90.1-2010?</t>
+  </si>
+  <si>
+    <t>Which building types have the highest ventilation rates in ASHRAE 62.1-2007, and what are their corresponding ventilation primary space types?</t>
+  </si>
+  <si>
+    <t>How do the envelope requirements for roofs vary across different climate zones in IECC, and what are their corresponding standards construction types?</t>
+  </si>
+  <si>
+    <t>What are the lighting power densities for office spaces in ASHRAE 90.1-2010, and how do they compare to other space types?</t>
+  </si>
+  <si>
+    <t>Which climate zones have the most stringent energy recovery requirements in ASHRAE 90.1-2010, and what are their corresponding percent outdoor air thresholds?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for walls in climate zones 4 and 5 in IECC, and how do they vary across different standards construction types?</t>
+  </si>
+  <si>
+    <t>Which space types in the 2010 PRM baseline require automatic daylight responsive controls for sidelighting and have lighting power densities above 1.2 W/ftÂ²?</t>
+  </si>
+  <si>
+    <t>What are the most commonly referenced ventilation definition IDs across all space types in ASHRAE 62.1-2004, and which standard tables do they belong to?</t>
+  </si>
+  <si>
+    <t>Which space types in ASHRAE 90.1-2019 require automatic full-off controls and have lighting power densities above 0.8 W/ftÂ²?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for residential buildings in climate zones 6 or 7 with wall constructions under ASHRAE 90.1-2019?</t>
+  </si>
+  <si>
+    <t>What are the efficiency requirements for any oil-fired furnace between 200,000-300,000 Btu/hr under ASHRAE 90.1-2019 standards?</t>
+  </si>
+  <si>
+    <t>What are the maximum U-values for walls in climate zones 5 or 6, and what standards construction types do they use?</t>
+  </si>
+  <si>
+    <t>Which space types have the highest target illuminance setpoints for retail spaces, and what lighting technologies do they use?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for roofs in IECC, and how do they vary by building category?</t>
+  </si>
+  <si>
+    <t>What are the lighting power densities for sports and entertainment venues in ASHRAE 90.1-2013, and how do they vary by facility class or type?</t>
+  </si>
+  <si>
+    <t>What are the minimum U-values for walls in climate zones 4 and 5 according to ASHRAE 90.1?</t>
+  </si>
+  <si>
+    <t>How do the illuminance requirements for retail spaces vary between ASHRAE 90.1 and IECC?</t>
+  </si>
+  <si>
+    <t>Which construction types have the highest maximum U-values for floors in IECC?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for walls in climate zones 4 and 5 under ASHRAE 90.1-2010?</t>
+  </si>
+  <si>
+    <t>What are the ventilation requirements for spaces with high occupancy density (&gt;100 ppl/1000 ftÂ²) under ASHRAE 62.1-2007?</t>
+  </si>
+  <si>
+    <t>Which support constructions have insulation layers and are intended for exterior walls?</t>
+  </si>
+  <si>
+    <t>How have the envelope requirements evolved over different IECC versions for roofs in climate zone 6?</t>
+  </si>
+  <si>
+    <t>What are the efficiency trade-offs between fan types (Centrifugal vs Propeller/Axial) for cooling towers under ASHRAE 90.1-2010?</t>
+  </si>
+  <si>
+    <t>Which space types have both high occupancy density (&gt;100 ppl/1000 ftÂ²) and require significant per-person ventilation rates under ASHRAE 62.1-2010?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for floors in climate zones 7 and 8 under IECC-2021?</t>
+  </si>
+  <si>
+    <t>What are the maximum U-values allowed for walls in residential buildings under IECC standards in climate zones 7-8?</t>
+  </si>
+  <si>
+    <t>How do the envelope requirements for windows differ between ASHRAE 90.1 and IECC standards for residential buildings in climate zone 5?</t>
+  </si>
+  <si>
+    <t>What are the maximum U-values for walls in climate zones 4 and 5 according to ASHRAE 90.1 standards?</t>
+  </si>
+  <si>
+    <t>How do the fan power allowances compare between different filtration levels across various system capacities in the 90.1 standard?</t>
+  </si>
+  <si>
+    <t>What are the efficiency improvements between different versions of ASHRAE 90.1 standards for air-cooled condensing units?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for roofs in climate zones 6 and 7 according to IECC standards?</t>
+  </si>
+  <si>
+    <t>What are the maximum solar heat gain coefficients for windows in climate zones 3 and 4 according to ASHRAE 90.1 standards?</t>
+  </si>
+  <si>
+    <t>Which space types have the highest variability in electric equipment loads and what are their heat gain characteristics?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for walls in climate zones 5 and 6 according to IECC standards?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for walls in climate zones 4 or 5 according to ASHRAE 90.1-2010?</t>
+  </si>
+  <si>
+    <t>Which space types in the PRM baseline have electric equipment loads above 0.5 W/ftÂ² and generate latent heat gains?</t>
+  </si>
+  <si>
+    <t>How has the efficiency requirement evolved over different IECC versions for high-speed 2-pole motors in the 20-30 HP range?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for roofs in climate zones 7 or 8 according to ASHRAE 90.1-2013?</t>
+  </si>
+  <si>
+    <t>How do the performance characteristics of Single Package Variable Heat Pumps (SPVHP) compare to standard heat pumps for small applications across different rating conditions?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for nonresidential buildings with a climate zone set of 5 or 6 according to ASHRAE 90.1-2010?</t>
+  </si>
+  <si>
+    <t>How do the SEER2 requirements differ between regions for a 2-ton split system heat pump installed under IECC-2021 standards?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for residential buildings with a roof intended surface type in Climate Zone 7 according to IECC-2024?</t>
+  </si>
+  <si>
+    <t>How do the HVAC minimum requirements compare between different equipment types (heat pumps and air conditioners) for a 3-ton split system installed under ASHRAE 90.1-2010 standards?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for nonresidential buildings with an exterior wall intended surface type in Climate Zone 4 according to IECC-2021?</t>
+  </si>
+  <si>
+    <t>How do the fan power allowances for exhaust systems compare between different filtration levels in ASHRAE 90.1-2025?</t>
+  </si>
+  <si>
+    <t>What are the required visible transmittances for skylights in residential buildings according to IECC-2018?</t>
+  </si>
+  <si>
+    <t>What are the maximum allowed U-values for residential exterior walls in Climate Zone 4 according to ASHRAE 90.1-2004?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for roofs in Climate Zone 4 under ASHRAE 90.1-2010 standards?</t>
+  </si>
+  <si>
+    <t>Which space types have the highest electric equipment loads above 0.5 W/ftÂ² and generate radiant heat gains?</t>
+  </si>
+  <si>
+    <t>What are the efficiency requirements for open motor designs in the 1-10 horsepower range under IECC-2018 standards?</t>
+  </si>
+  <si>
+    <t>How do the SEER2 requirements differ between regions for a 2-ton split system heat pump installed under ASHRAE 90.1-2013 standards?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for walls in Climate Zone 5 under IECC-2021 standards?</t>
+  </si>
+  <si>
+    <t>Which space types have the lowest variability in electric equipment loads and generate radiant heat gains?</t>
+  </si>
+  <si>
+    <t>What are the efficiency requirements for enclosed motor designs in the 10-20 horsepower range under ASHRAE 90.1-2010 standards?</t>
+  </si>
+  <si>
+    <t>What are the maximum permitted assembly U-values for residential exterior walls in Climate Zone 3A according to IECC-2015?</t>
+  </si>
+  <si>
+    <t>What are the maximum permitted assembly U-values for non-residential exterior roofs in Climate Zone 5B according to IECC-2018?</t>
+  </si>
+  <si>
+    <t>How do the ventilation requirements differ between residential and commercial buildings in warm climates (zones 1-3) under IECC?</t>
+  </si>
+  <si>
+    <t>Which construction types have the highest thermal transmittance values for walls in cold climates (zones 6-8) under ASHRAE 90.1-2013?</t>
+  </si>
+  <si>
+    <t>What are the energy recovery requirements for heating design conditions in warm climates (zones 1-3) under ASHRAE 90.1-2013?</t>
+  </si>
+  <si>
+    <t>Which construction types have the lowest thermal transmittance values for roofs in warm climates (zones 1-3) under ASHRAE 90.1-2013?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for roofs in climate zones 3 and 4 under ASHRAE 90.1?</t>
+  </si>
+  <si>
+    <t>Which space types have the highest lighting power densities in the IECC baseline and require automatic daylight responsive controls?</t>
+  </si>
+  <si>
+    <t>How do the energy recovery requirements vary for different outdoor air CFM thresholds in climate zones 7 and 8 under ASHRAE 90.1?</t>
+  </si>
+  <si>
+    <t>Which building types have the highest electric equipment loads and generate latent heat gains in the PRM baseline?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for walls in climate zones 3 and 4 under IECC?</t>
+  </si>
+  <si>
+    <t>What are the maximum U-values for walls in climate zones 4 and 5 across different standards (ASHRAE 90.1, IECC)?</t>
+  </si>
+  <si>
+    <t>What are the minimum visible transmittance requirements for windows in climate zones 3 and 4 across different standards?</t>
+  </si>
+  <si>
+    <t>What are the maximum solar heat gain coefficients for skylights in IECC-2012?</t>
+  </si>
+  <si>
+    <t>Which constructions have the highest insulation layer values in ASHRAE 90.1?</t>
+  </si>
+  <si>
+    <t>What are the fan power allowances for different air system components in ASHRAE 90.1-2025, and how do they compare between supply and exhaust systems?</t>
+  </si>
+  <si>
+    <t>Which space types have both high occupancy density (&gt;50 ppl/1000 ftÂ²) AND require significant per-person ventilation rates in ASHRAE 62.1-2007?</t>
+  </si>
+  <si>
+    <t>What are the high limit shutoff temperatures and enthalpies for different economizer control strategies in climate zone 4A, and how have they evolved between ASHRAE 90.1-2004 and ASHRAE 90.1-2010?</t>
+  </si>
+  <si>
+    <t>How do the fan power allowances compare between different filtration levels across different system capacities in ASHRAE 90.1-2025?</t>
+  </si>
+  <si>
+    <t>Which space types require the highest illuminance levels above 400 Lux across any code version in ASHRAE 90.1?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for walls in climate zone 7 or 8, and how do they compare between ASHRAE 90.1-2010 and IECC?</t>
+  </si>
+  <si>
+    <t>How do the envelope requirements for roofs compare between different climate zones in ASHRAE 90.1-2010?</t>
+  </si>
+  <si>
+    <t>What are the highest efficiency requirements for motors in IECC, and which design requires higher efficiency?</t>
+  </si>
+  <si>
+    <t>What are the ventilation requirements for educational spaces in ASHRAE 62.1-2019, and how do they compare between classrooms, labs, and auditoriums?</t>
+  </si>
+  <si>
+    <t>What are the lighting requirements for office spaces in ASHRAE 90.1-2019, and how do they compare between open offices, private offices, and conference rooms?</t>
+  </si>
+  <si>
+    <t>What are the fan power allowances for energy recovery components in ASHRAE 90.1-2025?</t>
+  </si>
+  <si>
+    <t>How do the envelope requirements for walls compare between climate zones 3 and 4 according to IECC?</t>
+  </si>
+  <si>
+    <t>How do the outdoor air percentage thresholds for energy recovery requirements differ between humid (A) and dry (B) climate zones in ASHRAE 90.1-2016?</t>
+  </si>
+  <si>
+    <t>Which construction types have the highest U-values for roofs in climate zone 7 under IECC-2015?</t>
+  </si>
+  <si>
+    <t>How do ground-source VRF systems compare to water-source systems in terms of cooling efficiency requirements under ASHRAE 90.1-2019?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for residential buildings in climate zone 3 under ASHRAE 90.1-2016?</t>
+  </si>
+  <si>
+    <t>What are the maximum U-values for non-residential walls in Climate Zone 5 according to ASHRAE 90.1-2010?</t>
+  </si>
+  <si>
+    <t>What are the minimum projection factors for skylights in non-residential buildings according to IECC?</t>
+  </si>
+  <si>
+    <t>Which equipment types have fan types with minimum performance GPM per HP requirements in ASHRAE 90.1-2013?</t>
+  </si>
+  <si>
+    <t>What are the maximum solar heat gain coefficients for southern facing non-residential glass doors in Climate Zone 7 according to ASHRAE 90.1-2004?</t>
+  </si>
+  <si>
+    <t>How do the U-values for roofs vary between residential and non-residential buildings in Climate Zone 6 according to IECC?</t>
+  </si>
+  <si>
+    <t>Which space types have high ventilation rates above 0.3 cfm/ftÂ² and rely purely on area-based ventilation in ASHRAE 62.1-2010?</t>
+  </si>
+  <si>
+    <t>What are the minimum visible transmittances for skylights in non-residential buildings according to ASHRAE 90.1-2007?</t>
+  </si>
+  <si>
+    <t>Which equipment types have minimum performance BTU per HP requirements in ASHRAE 90.1-2010?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for walls in climate zones 4 and 5, according to ASHRAE 90.1 standards?</t>
+  </si>
+  <si>
+    <t>How do the ventilation strategies differ between spectator areas and active play areas in sports and entertainment venues, according to ASHRAE 62.1-2007 standards?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for roofs in climate zones 6 and 7, according to IECC standards?</t>
+  </si>
+  <si>
+    <t>How do the energy recovery requirements vary between ASHRAE 90.1 and IECC standards for systems with outdoor air CFM thresholds below 5000 hours?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for walls in climate zones 3 and 4, according to ASHRAE 90.1 standards, with a minimum R-value of 10?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for residential buildings in Climate Zone 3A according to IECC-2012, focusing on exterior walls and roofs?</t>
+  </si>
+  <si>
+    <t>How do the economizer control strategies differ between data centers and regular buildings in ASHRAE 90.1-2010 across different climate zones, considering heat recovery and dew point dry bulb control?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for roofs in climate zones 4 and 5 under ASHRAE 90.1 standards?</t>
+  </si>
+  <si>
+    <t>How do the control requirements for lighting vary between general facilities and those serving visually impaired populations in IECC standards?</t>
+  </si>
+  <si>
+    <t>Compare the lighting power density requirements between CS and SS methods for office spaces in ASHRAE 90.1-2004 standards.</t>
+  </si>
+  <si>
+    <t>Which space types have the same electric equipment profiles but different ventilation requirements in IECC standards?</t>
+  </si>
+  <si>
+    <t>How do the envelope requirements for walls in climate zone 7 compare between ASHRAE 90.1 and IECC standards?</t>
+  </si>
+  <si>
+    <t>How do the lighting requirements for facilities serving the visually impaired compare to general facilities in terms of power density and control flexibility in IECC standards?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for floors in climate zones 4 and 5 under IECC standards?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for walls in climate zones 3 and 4 according to ASHRAE 90.1?</t>
+  </si>
+  <si>
+    <t>How do the ventilation rates compare for Air Class 1 and Air Class 2 spaces in ASHRAE 62.1-2004?</t>
+  </si>
+  <si>
+    <t>Which space types have both high occupancy density and require significant per-person ventilation rates in ASHRAE 62.1-2007?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for roofs in climate zone 5 according to ASHRAE 90.1-2010?</t>
+  </si>
+  <si>
+    <t>Which space types require both automatic partial-off controls and have the most stringent RCR thresholds in ASHRAE 90.1-2013?</t>
+  </si>
+  <si>
+    <t>How do the lighting requirements for general facilities compare to facilities serving the visually impaired in terms of power density and control flexibility according to ASHRAE 90.1-2022?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for walls in climate zones 6 and 7 according to IECC?</t>
+  </si>
+  <si>
+    <t>Compare the maximum permitted assembly U-values for roofs in Climate Zone 6 according to ASHRAE 90.1-2010 and IECC 2021</t>
+  </si>
+  <si>
+    <t>Which climate zones have the highest U-values for roofs in ASHRAE 90.1 standards and what are their corresponding solar heat gain coefficients?</t>
+  </si>
+  <si>
+    <t>What are the maximum allowable solar heat gain coefficients for windows in commercial buildings located in climate zones with high cooling loads (4A, 5A) according to IECC standards?</t>
+  </si>
+  <si>
+    <t>Which space types have the highest lighting power densities and require automatic daylight responsive controls for sidelighting in ASHRAE 90.1-2013 standards?</t>
+  </si>
+  <si>
+    <t>Which space types have the highest occupancy densities and require significant per-person ventilation rates in ASHRAE 62.1-2007 standards?</t>
+  </si>
+  <si>
+    <t>What are the maximum allowable U-values for floors in commercial buildings located in climate zones with low cooling loads (2A, 3A) according to ASHRAE 90.1 standards?</t>
+  </si>
+  <si>
+    <t>What are the minimum visible transmittances required for skylights in climate zones with high solar radiation (4A, 5A) according to IECC standards?</t>
+  </si>
+  <si>
+    <t>Which space types have the highest lighting power densities in ASHRAE 90.1-2010, and how do they compare to IECC standards?</t>
+  </si>
+  <si>
+    <t>How do the envelope requirements for roofs in climate zones 7 and 8 compare between ASHRAE 90.1-2010 and IECC standards?</t>
+  </si>
+  <si>
+    <t>What are the maximum solar heat gain coefficients for windows in ASHRAE 90.1-2010, and how do they vary by orientation?</t>
+  </si>
+  <si>
+    <t>Which equipment types have the highest minimum annual fuel utilization efficiencies in ASHRAE 90.1-2025?</t>
+  </si>
+  <si>
+    <t>How do the lighting requirements for general offices compare to those for computer labs in terms of power density and control flexibility?</t>
+  </si>
+  <si>
+    <t>What are the maximum U-values for floors in climate zones 3 and 4 according to IECC standards?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for walls in climate zones 4 and 5 according to ASHRAE 90.1-2013?</t>
+  </si>
+  <si>
+    <t>How do the thermal properties of different insulation materials vary in terms of conductivity and density across various standards?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for roofs in climate zones 6 and 7 according to IECC 2018?</t>
+  </si>
+  <si>
+    <t>How do the level 2 lighting space types vary in terms of target illuminance setpoints and lighting technology across different standards?</t>
+  </si>
+  <si>
+    <t>What are the support constructions for walls with insulation layers in ASHRAE 90.1-2013?</t>
+  </si>
+  <si>
+    <t>What are the maximum U-values for walls in climate zones 4 and 5, according to ASHRAE 90.1-2010?</t>
+  </si>
+  <si>
+    <t>What are the allowed solar heat gain coefficients for skylights in climate zones 3 and 6, according to ASHRAE 90.1-2016?</t>
+  </si>
+  <si>
+    <t>How do the U-values for walls in climate zones 2 and 8 compare between ASHRAE 90.1-2010 and IECC-2009?</t>
+  </si>
+  <si>
+    <t>What are the maximum C-factors for roofs in climate zones 5 and 7, according to ASHRAE 90.1-2013?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for residential buildings in Climate Zone 3A under ASHRAE 90.1-2004?</t>
+  </si>
+  <si>
+    <t>Which level 1 space types have the highest variability in lighting loads?</t>
+  </si>
+  <si>
+    <t>How do the efficiency requirements for high-speed motors differ between ASHRAE 90.1-2007 and IECC?</t>
+  </si>
+  <si>
+    <t>What are the maximum permitted solar heat gain coefficients for skylights in Climate Zone 6 according to IECC?</t>
+  </si>
+  <si>
+    <t>What are the maximum U-values for walls in climate zones 4 and 5, according to ASHRAE 90.1?</t>
+  </si>
+  <si>
+    <t>How do the COP requirements for commercial heat pumps in ASHRAE 90.1 compare to those in IECC, for low outdoor temperatures (17 F)?</t>
+  </si>
+  <si>
+    <t>Which construction types have the highest U-values for roofs in climate zones 7 and 8, according to IECC?</t>
+  </si>
+  <si>
+    <t>What are the minimum SCOP requirements for computer room air conditioners with water-cooled downflow installed between 2010 and 2020?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for walls in ASHRAE 90.1-2016 and IECC standards, including assembly maximum U-values and solar heat gain coefficients?</t>
+  </si>
+  <si>
+    <t>Compare the envelope requirements for walls and roofs in ASHRAE 90.1-2016 and IECC standards, including assembly maximum U-values and solar heat gain coefficients</t>
+  </si>
+  <si>
+    <t>How do the EER and IEER requirements compare between air-cooled and water-cooled unitary air conditioners in the 120,000-240,000 Btu/hr range for units installed after 2015?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for roofs in climate zones 4 and 5 under IECC standards, including assembly U-values and solar heat gain coefficients?</t>
+  </si>
+  <si>
+    <t>How do the heat rejection requirements compare between evaporative condensers and air-cooled condensers in the same fan type under ASHRAE 90.1-2019 standards?</t>
+  </si>
+  <si>
+    <t>What are the minimum efficiency requirements for natural gas boilers with capacities between 200 and 400 kBtu/hr according to IECC?</t>
+  </si>
+  <si>
+    <t>Which construction types have the highest solar heat gain coefficients for roofs in climate zones 6 and 7?</t>
+  </si>
+  <si>
+    <t>What are the minimum efficiency requirements for high-speed 2-pole motors in the 20-30 HP range across different climate zones?</t>
+  </si>
+  <si>
+    <t>What are the maximum U-values for walls in climate zones 4 and 5 under ASHRAE 90.1-2016 standards?</t>
+  </si>
+  <si>
+    <t>How do the efficiency requirements for ground-source VRF systems compare to water-source systems in terms of cooling efficiency under IECC standards?</t>
+  </si>
+  <si>
+    <t>How do the BTU/hr per HP requirements compare between different refrigerants for evaporative condensers with the same fan type under current IECC standards?</t>
+  </si>
+  <si>
+    <t>Which equipment types have a minimum energy efficiency ratio greater than or equal to 10 under ASHRAE 90.1-2022 standards?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for roofs in climate zones 4-6 according to ASHRAE 90.1?</t>
+  </si>
+  <si>
+    <t>What are the efficiency requirements for air-cooled condensing units in ASHRAE 90.1-2010 and IECC?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for walls in climate zones 7 and 8 according to ASHRAE 90.1-2013?</t>
+  </si>
+  <si>
+    <t>How have the COP requirements at low outdoor temperatures evolved over different ASHRAE 90.1 versions for large commercial heat pumps?</t>
+  </si>
+  <si>
+    <t>What are the ventilation requirements for educational spaces in terms of per-person and occupancy assumptions according to ASHRAE 62.1-1999?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for floors in climate zones 4-6 according to IECC?</t>
+  </si>
+  <si>
+    <t>What are the ventilation requirements for office spaces in terms of per-person and occupancy assumptions according to ASHRAE 62.1-1999?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for roofs in climate zones 4-6 according to ASHRAE 90.1-2010?</t>
+  </si>
+  <si>
+    <t>What are the maximum U-values for walls in climate zones 4 and 5 according to ASHRAE 90.1?</t>
+  </si>
+  <si>
+    <t>Which space types have a high lighting power density and require automatic daylight responsive controls for sidelighting in the PRM baseline?</t>
+  </si>
+  <si>
+    <t>What are the minimum seasonal energy efficiency ratios for heat pumps in the Southeastern region across different IECC versions?</t>
+  </si>
+  <si>
+    <t>What are the assembly maximum solar heat gain coefficients for windows in climate zones 6 and 7 according to IECC?</t>
+  </si>
+  <si>
+    <t>What are the maximum U-values for floors in climate zones 3 and 4 according to ASHRAE 90.1 PRM?</t>
+  </si>
+  <si>
+    <t>Which space types in the 2010 PRM baseline require automatic full-off controls and have lighting power densities above 0.5 W/ftÂ²?</t>
+  </si>
+  <si>
+    <t>What are the maximum allowed U-values for walls in climate zones 4-6?</t>
+  </si>
+  <si>
+    <t>What are the required solar heat gain coefficients for windows in climate zones 6-8?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for walls in climate zones 4 or 5, according to ASHRAE 90.1-2010?</t>
+  </si>
+  <si>
+    <t>Which space types have the highest lighting power densities and require automatic partial-off controls in ASHRAE 90.1-2019?</t>
+  </si>
+  <si>
+    <t>What are the ventilation requirements for food service spaces in ASHRAE 62.1-2004?</t>
+  </si>
+  <si>
+    <t>How do the envelope requirements for roofs compare between ASHRAE 90.1-2010 and IECC?</t>
+  </si>
+  <si>
+    <t>Which equipment types have the most restrictive requirements for energy recovery in ASHRAE 90.1-2010?</t>
+  </si>
+  <si>
+    <t>What are the support constructions for walls in ASHRAE 90.1-2010?</t>
+  </si>
+  <si>
+    <t>Which space types have the most restrictive RCR thresholds and require automatic daylight responsive controls in ASHRAE 90.1-2022?</t>
+  </si>
+  <si>
+    <t>How do the envelope requirements for floors compare between ASHRAE 90.1-2010 and IECC?</t>
+  </si>
+  <si>
+    <t>What are the system requirements for air economizers in ASHRAE 90.1-2010?</t>
+  </si>
+  <si>
+    <t>Which space types have the highest ventilation rates per occupant in ASHRAE 62.1-2004?</t>
+  </si>
+  <si>
+    <t>What are the minimum energy efficiency requirements for ground-source VRF systems in ASHRAE 90.1-2016 and later versions?</t>
+  </si>
+  <si>
+    <t>How do the ventilation requirements for food service spaces compare between ASHRAE 62.1-2004 and later versions?</t>
+  </si>
+  <si>
+    <t>What are the maximum U-values allowed for walls in climate zones 4 and 5 in ASHRAE 90.1-2019?</t>
+  </si>
+  <si>
+    <t>Which building types have the highest lighting power density requirements in ASHRAE 90.1-2022?</t>
+  </si>
+  <si>
+    <t>What are the minimum part load efficiency requirements for air-cooled chillers in IECC-2012 and later versions?</t>
+  </si>
+  <si>
+    <t>How do the envelope requirements for residential buildings compare between IECC-2009 and IECC-2012?</t>
+  </si>
+  <si>
+    <t>Which exterior lighting allowance types are available in ASHRAE 90.1-2016 and later versions?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for walls in Climate Zone 4 or 5 across different ASHRAE 90.1 versions?</t>
+  </si>
+  <si>
+    <t>Which building categories have the most stringent envelope requirements in ASHRAE 90.1-2022?</t>
+  </si>
+  <si>
+    <t>What are the maximum solar heat gain coefficients for windows in Climate Zone 7 or 8 across different ASHRAE 90.1 versions?</t>
+  </si>
+  <si>
+    <t>What are the minimum visible transmittance requirements for skylights in IECC?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for residential buildings in Climate Zone 5 according to ASHRAE 90.1-2013?</t>
+  </si>
+  <si>
+    <t>Which construction types have the lowest assembly U-values for exterior walls in Climate Zone 7 according to ASHRAE 90.1-2016?</t>
+  </si>
+  <si>
+    <t>What are the energy recovery requirements for outdoor air CFM thresholds in Climate Zone 3A according to ASHRAE 90.1-2010?</t>
+  </si>
+  <si>
+    <t>Which equipment types have the highest minimum COP heating requirements for single package variable heat pumps in ASHRAE 90.1-2016?</t>
+  </si>
+  <si>
+    <t>What are the exterior lighting requirements for parking lots in 90.1-2007?</t>
+  </si>
+  <si>
+    <t>Which space types have the highest lighting power densities and require automatic daylight responsive controls under 90.1-2010?</t>
+  </si>
+  <si>
+    <t>What are the maximum U-values for walls in climate zones 4 or 5 according to ASHRAE 90.1?</t>
+  </si>
+  <si>
+    <t>Which space types have both high occupancy density (&gt;50 ppl/1000 ftÂ²) and require significant per-person ventilation rates in ASHRAE 62.1-2007?</t>
+  </si>
+  <si>
+    <t>What SCOP is required for a 100 kBtu/hr air cooled upflow computer room air conditioner installed in 2010 according to IECC?</t>
+  </si>
+  <si>
+    <t>What are the allowance types for exterior lighting in ASHRAE 90.1-2013?</t>
+  </si>
+  <si>
+    <t>What are the minimum visible transmittance values for skylights in climate zones 3 or 4 according to ASHRAE 90.1-2010?</t>
+  </si>
+  <si>
+    <t>Which level 2 lighting space types have a target illuminance setpoint greater than 30 fc?</t>
+  </si>
+  <si>
+    <t>What are the maximum solar heat gain coefficients for windows in climate zones 5 or 6 according to IECC?</t>
+  </si>
+  <si>
+    <t>What are the maximum U-values for walls in climate zones 3 and 4, according to ASHRAE 90.1-2010?</t>
+  </si>
+  <si>
+    <t>How do the economizer control strategies differ between data centers and regular buildings in climate zones 2A, 3A, and 4A?</t>
+  </si>
+  <si>
+    <t>What are the thermal properties of glass fiber batt insulations with R-values greater than 10, across different CEC defaults?</t>
+  </si>
+  <si>
+    <t>How do the thermal properties of walls vary by R-value and thickness across different climate zones?</t>
+  </si>
+  <si>
+    <t>What are the maximum solar heat gain coefficients for roofs in climate zones 5 and 6, according to ASHRAE 90.1-2010?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for walls in climate zones 4 and 5 according to ASHRAE 90.1-2010?</t>
+  </si>
+  <si>
+    <t>How do the minimum energy efficiency ratios for air-cooled condensing units differ between ASHRAE 90.1-2004 and IECC standards?</t>
+  </si>
+  <si>
+    <t>What are the thermal transmittance requirements for roofs in climate zone 7 according to IECC?</t>
+  </si>
+  <si>
+    <t>How have the COP requirements for heat pumps at low outdoor temperatures evolved over different ASHRAE 90.1 versions?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for floors in ASHRAE 90.1-2007 and what are their corresponding thermal transmittance values?</t>
+  </si>
+  <si>
+    <t>What are the minimum energy efficiency ratios for water-cooled condensing units in ASHRAE 90.1-2013 and IECC standards?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for walls in climate zones 4-6 under ASHRAE 90.1 standards?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for roofs in climate zones 7-8 under IECC standards?</t>
+  </si>
+  <si>
+    <t>How do the efficiency requirements for oil-fired furnaces vary between ASHRAE 90.1 and IECC standards?</t>
+  </si>
+  <si>
+    <t>Which space types have both high occupancy density (&gt;100 ppl/1000 ftÂ²) AND require significant per-person ventilation rates in IECC-2012?</t>
+  </si>
+  <si>
+    <t>How has the efficiency requirement evolved over different ASHRAE 90.1 versions for high-speed 2-pole motors in the 30-40 HP range?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for roofs in climate zones 4-6 in ASHRAE 90.1-2019?</t>
+  </si>
+  <si>
+    <t>How do the outdoor air percentage thresholds for energy recovery requirements differ between humid (A) and dry (B) climate zones in IECC-2015?</t>
+  </si>
+  <si>
+    <t>What are the highest solar heat gain coefficients for windows in ASHRAE 90.1-2016?</t>
+  </si>
+  <si>
+    <t>What are the maximum permitted assembly U-values for residential exterior walls in Climate Zone 4 according to ASHRAE 90.1-2013?</t>
+  </si>
+  <si>
+    <t>What are the minimum SCOP requirements for water-cooled downflow computer room air conditioners with a capacity of 100 kBtu/hr or more according to ASHRAE 90.1-2004?</t>
+  </si>
+  <si>
+    <t>Which climate zones have the highest minimum projection factors for skylights according to IECC?</t>
+  </si>
+  <si>
+    <t>How do the ventilation requirements for office spaces vary between different ASHRAE standards?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for floors in climate zones 6 and 7 according to ASHRAE 90.1-2010?</t>
+  </si>
+  <si>
+    <t>Which space types have natural gas equipment loads above 10 Btu/hÂ·ftÂ² and generate latent heat gains?</t>
+  </si>
+  <si>
+    <t>What are the insulation materials with a thermal resistance per inch of thickness greater than 2 and a density less than 1.5 lb/ft^3?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for roofs in ASHRAE 90.1-2007 with a maximum U-value of 0.05?</t>
+  </si>
+  <si>
+    <t>Which level 2 lighting space types have a target illuminance setpoint greater than 30 footcandles?</t>
+  </si>
+  <si>
+    <t>What are the level 1 space types that use electric equipment and have a ventilation space type name containing 'Office'?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for walls in climate zones 4 or 5 under ASHRAE 90.1-2019 standards?</t>
+  </si>
+  <si>
+    <t>Which space types have supplemental lighting allowances and special control requirements in 90.1-2019?</t>
+  </si>
+  <si>
+    <t>What are the high limit shutoff temperatures and enthalpies for different economizer control strategies in climate zone 4 under ASHRAE 90.1-2010 standards?</t>
+  </si>
+  <si>
+    <t>How do the envelope requirements for roofs compare between different building categories in IECC standards?</t>
+  </si>
+  <si>
+    <t>What are the most energy-intensive laboratory and healthcare spaces in 90.1-2019, and how do their control requirements differ?</t>
+  </si>
+  <si>
+    <t>What are the HVAC minimum requirements for evaporative condensers with a test fluid of R-448A under ASHRAE 90.1-2019 standards?</t>
+  </si>
+  <si>
+    <t>Which space types have different ventilation requirements but share the same electric equipment profiles in 90.1-2010?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for walls in climate zones 7 or 8 under IECC standards?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for walls in ASHRAE 90.1-2007, specifically in climate zones 4 and 5?</t>
+  </si>
+  <si>
+    <t>Which space types have supplemental lighting allowances or special control requirements in 90.1-2007?</t>
+  </si>
+  <si>
+    <t>What are the ventilation rates for educational spaces (classrooms vs labs vs auditoriums) in terms of per-person and occupancy assumptions?</t>
+  </si>
+  <si>
+    <t>How do the envelope requirements differ between residential and commercial buildings in IECC?</t>
+  </si>
+  <si>
+    <t>What are the thermal bridging requirements for roofs in climate zones 6 and 7 in ASHRAE 90.1-2010?</t>
+  </si>
+  <si>
+    <t>How do the level 2 lighting space types vary in terms of target illuminance setpoints and lighting technologies?</t>
+  </si>
+  <si>
+    <t>What are the maximum U-values for walls in climate zones 4, 5, or 6 under ASHRAE 90.1-2010?</t>
+  </si>
+  <si>
+    <t>What are the most common ventilation space types for level 1 space types with specific electric equipment profiles?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for walls in climate zones 7 or 8 under ASHRAE 90.1-2016?</t>
+  </si>
+  <si>
+    <t>What are the maximum permitted assembly U-values for residential exterior walls in Climate Zone 4A according to IECC?</t>
+  </si>
+  <si>
+    <t>What are the maximum U-values for exterior walls in climate zones with a high cooling load, and what are their corresponding orientations?</t>
+  </si>
+  <si>
+    <t>Which space types have the highest lighting power densities and require automatic daylight responsive controls for sidelighting?</t>
+  </si>
+  <si>
+    <t>What are the minimum thermal resistance values for insulation materials used in building constructions, and what are their corresponding densities?</t>
+  </si>
+  <si>
+    <t>Which space types require both automatic partial-off controls and daylight responsive controls, and how do their lighting power densities compare?</t>
+  </si>
+  <si>
+    <t>Which climate zones have the most stringent requirements for exterior roof constructions, and what are their corresponding U-values?</t>
+  </si>
+  <si>
+    <t>What is the maximum permitted assembly U-value for a residential exterior wall in Climate Zone 3B according to IECC-2015?</t>
+  </si>
+  <si>
+    <t>Which space types in ASHRAE 90.1-2013 have supplemental lighting allowances or special control requirements?</t>
+  </si>
+  <si>
+    <t>Which constructions in the support_constructions table have insulation layers?</t>
+  </si>
+  <si>
+    <t>What is the maximum permitted assembly U-value for a residential exterior roof in Climate Zone 4A according to IECC-2012?</t>
+  </si>
+  <si>
+    <t>Which space types in ASHRAE 90.1-2016 have daylight responsive controls?</t>
+  </si>
+  <si>
+    <t>What are the maximum U-values for exterior walls in climate zones 4 and 5 according to ASHRAE 90.1-2013?</t>
+  </si>
+  <si>
+    <t>Which space types have the highest lighting power density and require automatic daylight responsive controls for sidelighting in ASHRAE 90.1-2019?</t>
+  </si>
+  <si>
+    <t>What are the minimum integrated part load values for water-cooled screw chillers with a capacity between 100 and 200 tons in IECC-2006?</t>
+  </si>
+  <si>
+    <t>Which ventilation space types have high ventilation rates above 0.5 cfm/ftÂ² and do not rely on per-person requirements in ASHRAE 62.1-1999?</t>
+  </si>
+  <si>
+    <t>What are the maximum solar heat gain coefficients for skylights in climate zones 6 and 7 according to ASHRAE 90.1-2013?</t>
+  </si>
+  <si>
+    <t>Which space types have the most stringent RCR thresholds and require automatic partial-off controls in ASHRAE 90.1-2019?</t>
+  </si>
+  <si>
+    <t>What are the minimum visible transmittances for windows in climate zones 3 and 4 according to IECC?</t>
+  </si>
+  <si>
+    <t>Which equipment types have the highest minimum coefficients of performance for heating in ASHRAE 90.1-2013?</t>
+  </si>
+  <si>
+    <t>What are the maximum U-values for floors in climate zones 5 and 6 according to ASHRAE 90.1-2013?</t>
+  </si>
+  <si>
+    <t>What are the maximum U-values for walls in climate zones 4 and 5 under ASHRAE 90.1 standards?</t>
+  </si>
+  <si>
+    <t>How do the EER and IEER requirements compare between air-cooled and water-cooled single package air conditioners in the 150,000-300,000 Btu/hr range for units installed after 2015?</t>
+  </si>
+  <si>
+    <t>What are the lighting power densities for retail spaces in IECC standards, and how do they vary by facility class or type?</t>
+  </si>
+  <si>
+    <t>What are the maximum solar heat gain coefficients for windows in climate zones 6 and 7 under ASHRAE 90.1 standards?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for residential exterior walls in Climate Zone 4A according to IECC-2012?</t>
+  </si>
+  <si>
+    <t>How do the minimum AFUE values differ between natural gas furnaces and electric furnaces in ASHRAE 90.1-2016?</t>
+  </si>
+  <si>
+    <t>What is the minimum annual fuel utilization efficiency required for a 150 kBtu/hr natural gas furnace installed in 2018 according to ASHRAE 90.1-2016?</t>
+  </si>
+  <si>
+    <t>Compare the envelope requirements for residential exterior walls in Climate Zone 4A between IECC-2012 and ASHRAE 90.1-2010?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for walls in ASHRAE 90.1, specifically in climate zones with moderate temperatures?</t>
+  </si>
+  <si>
+    <t>How do the lighting power densities for retail spaces vary between ASHRAE 90.1 and IECC standards?</t>
+  </si>
+  <si>
+    <t>What are the maximum U-values for roofs in IECC, specifically for residential buildings in climate zones with high temperatures?</t>
+  </si>
+  <si>
+    <t>Which support constructions have the most insulation layers, and what are their corresponding material types?</t>
+  </si>
+  <si>
+    <t>What are the minimum visible transmittance values for windows in ASHRAE 90.1, specifically for non-residential buildings in climate zones with low temperatures?</t>
+  </si>
+  <si>
+    <t>Which level 1 space types have the highest lighting power densities, and what are their corresponding ventilation rates?</t>
+  </si>
+  <si>
+    <t>How do the EER and IEER requirements compare between air-cooled and water-cooled condensing units in ASHRAE 90.1-2010 for units installed after 2010?</t>
+  </si>
+  <si>
+    <t>What are the maximum U-values for roofs in climate zones 4 and 5 according to ASHRAE 90.1-2007?</t>
+  </si>
+  <si>
+    <t>What are the most common space types that use level_3_lighting_90_1_2022 and have RCR thresholds above 6?</t>
+  </si>
+  <si>
+    <t>Compare the lighting power density requirements between CS and SS methods for office space types in ASHRAE 90.1-2004 and 90.1-2010?</t>
+  </si>
+  <si>
+    <t>What are the efficiency requirements for high-speed motors in the 20-30 HP range, and what's the efficiency penalty for going to slower motors?</t>
+  </si>
+  <si>
+    <t>What is the maximum permitted assembly U-value for a residential exterior wall in Climate Zone 3 according to IECC-2012?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for roofs in Climate Zone 7 according to IECC-2009?</t>
+  </si>
+  <si>
+    <t>What are the maximum U-values for exterior walls in Climate Zone 5 according to ASHRAE 90.1-2010?</t>
+  </si>
+  <si>
+    <t>How do the ventilation requirements differ between educational spaces (classrooms vs labs) in terms of per-person and occupancy assumptions?</t>
+  </si>
+  <si>
+    <t>What are the exterior lighting requirements for parking garages in 90.1-2013?</t>
+  </si>
+  <si>
+    <t>What is the minimum visible transmittance for skylights in Climate Zone 4 according to IECC?</t>
+  </si>
+  <si>
+    <t>How do the energy recovery requirements differ between heating and cooling design conditions for cold climates (zones 6-8) in ASHRAE 90.1-2007?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for residential buildings in Climate Zone 3A according to ASHRAE 90.1-2004?</t>
+  </si>
+  <si>
+    <t>How do the lighting requirements differ between office spaces (private offices vs open offices) in terms of target illuminance setpoints?</t>
+  </si>
+  <si>
+    <t>What are the maximum U-values for roofs in climate zones 3 and 4 according to ASHRAE 90.1-2010?</t>
+  </si>
+  <si>
+    <t>What are the insulation materials with thermal resistance above 20 and density below 2.0, according to support_materials?</t>
+  </si>
+  <si>
+    <t>Which space types require the highest illuminance levels above 300 Lux across any code version in level_2_lighting_space_types?</t>
+  </si>
+  <si>
+    <t>What are the maximum solar heat gain coefficients for windows in climate zones 5 and 6 according to IECC?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for walls in climate zones 7 and 8 according to ASHRAE 90.1-2010?</t>
+  </si>
+  <si>
+    <t>How do the control requirements vary for facilities serving different occupant types in terms of lighting power density?</t>
+  </si>
+  <si>
+    <t>What's the efficiency trade-off between fan types for cooling towers, and how have the GPM per HP requirements changed across ASHRAE 90.1 versions?</t>
+  </si>
+  <si>
+    <t>How do the lighting power densities compare between retail spaces and office spaces in the PRM baseline?</t>
+  </si>
+  <si>
+    <t>What are the maximum U-values for roofs in climate zones 6 and 7 according to IECC?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for floors in climate zones 3 and 4 according to ASHRAE 90.1-2010?</t>
+  </si>
+  <si>
+    <t>How do the ventilation rates compare between different ventilation space types in ASHRAE 62.1-2007?</t>
+  </si>
+  <si>
+    <t>What are the maximum allowed U-values for walls in climate zones 4 and 5 according to ASHRAE 90.1?</t>
+  </si>
+  <si>
+    <t>What are the minimum EER requirements for air-cooled heat pumps in the 120,000-240,000 Btu/hr range installed after 2015 according to IECC?</t>
+  </si>
+  <si>
+    <t>How do the off-mode power requirements compare between Small Duct High Velocity systems and regular heat pumps in the Southwestern region across different ASHRAE 90.1 versions?</t>
+  </si>
+  <si>
+    <t>What are the maximum allowed SHGC values for windows in climate zones 3 and 4 according to IECC?</t>
+  </si>
+  <si>
+    <t>What are the minimum SEER requirements for air-cooled heat pumps in the 120,000-240,000 Btu/hr range installed after 2010 according to ASHRAE 90.1?</t>
+  </si>
+  <si>
+    <t>How do the U-value requirements compare between walls and roofs in climate zones 5 and 6 according to ASHRAE 90.1-2019?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for roofs in ASHRAE 90.1-2013 across different climate zones?</t>
+  </si>
+  <si>
+    <t>What are the BTU/hr per HP requirements for evaporative condensers with the same fan type under current IECC standards?</t>
+  </si>
+  <si>
+    <t>What's the performance difference between space-constrained and standard heat pumps for small applications across different rating conditions?</t>
+  </si>
+  <si>
+    <t>How have the U-factor requirements for windows evolved over different ASHRAE 90.1 versions for residential buildings?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for walls in climate zones 4 or 5 under ASHRAE 90.1 standards?</t>
+  </si>
+  <si>
+    <t>Which space types require the highest illuminance levels above 300 Lux across any code version?</t>
+  </si>
+  <si>
+    <t>What are the minimum and maximum capacities for air conditioners under IECC standards, and how do they vary by equipment type?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for floors in climate zones 6 or 7 under IECC standards, and how do they vary by building category?</t>
+  </si>
+  <si>
+    <t>What are the minimum U-values for exterior walls in climate zones 4-6 under ASHRAE 90.1-2019 standards?</t>
+  </si>
+  <si>
+    <t>Which climate zones have the most stringent requirements for skylight U-values in ASHRAE 90.1-2022 standards?</t>
+  </si>
+  <si>
+    <t>What are the minimum VT/SHGC requirements for skylights in ASHRAE 90.1-2019 standards for buildings with high occupant density?</t>
+  </si>
+  <si>
+    <t>How do the HVAC efficiency requirements compare between different fuel types for furnaces under current IECC standards?</t>
+  </si>
+  <si>
+    <t>Which space types in ASHRAE 90.1 have the highest maximum U-values for roofs and what are their corresponding solar heat gain coefficients?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for walls in IECC and what are their corresponding U-values?</t>
+  </si>
+  <si>
+    <t>Which space types in ASHRAE 90.1 have the most restrictive RCR thresholds but still allow ADD2 controls instead of requiring them?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for floors in climate zones 6 and 7 according to IECC?</t>
+  </si>
+  <si>
+    <t>Which level 2 electric equipment space types have the highest average EPDs and what are their corresponding median EPDs?</t>
+  </si>
+  <si>
+    <t>What are the support constructions for roofs and walls in ASHRAE 90.1 and what are their corresponding insulation layers?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for walls in climate zones 4 and 5 under ASHRAE 90.1-2022 standards?</t>
+  </si>
+  <si>
+    <t>How have the solar heat gain coefficient (SHGC) requirements changed for windows in IECC-2018 and IECC-2021 standards?</t>
+  </si>
+  <si>
+    <t>What are the maximum U-values allowed for roofs in climate zones 3 and 4 under ASHRAE 90.1-2022 standards?</t>
+  </si>
+  <si>
+    <t>How do the water-source and ground-source VRF systems compare in terms of cooling efficiency requirements under ASHRAE 90.1-2016 standards?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for floors in climate zone 5 under IECC-2021 standards?</t>
+  </si>
+  <si>
+    <t>Compare the U-values and solar heat gain coefficients of windows in climate zones 4, 5, or 6 under ASHRAE 90.1-2010 standards.</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for roofs in climate zone 7 under IECC standards?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for walls in climate zones 4 and 5 under ASHRAE 90.1-2013 standards?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for roofs in climate zones 6 and 7 under ASHRAE 90.1-2013 standards?</t>
+  </si>
+  <si>
+    <t>Which space types require automatic daylight responsive controls for toplighting and have a lighting power density above 1.5 W/ft^2 under ASHRAE 90.1-2019 standards?</t>
+  </si>
+  <si>
+    <t>What are the insulation requirements for roofs in climate zones 3-5 under IECC 2021 standards?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for walls in climate zones 4 or 5 under ASHRAE 90.1-2019?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for floors in climate zones 7 or 8 under ASHRAE 90.1-2013?</t>
+  </si>
+  <si>
+    <t>How do the AFUE requirements for natural gas furnaces vary under different standards and versions?</t>
+  </si>
+  <si>
+    <t>What are the level 1 space types that have electric equipment space type names containing 'Office'?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for roofs in climate zone 4 under ASHRAE 90.1-2019 and IECC?</t>
+  </si>
+  <si>
+    <t>How do the solar heat gain coefficients vary for different assemblies under ASHRAE 90.1-2016?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for walls in ASHRAE 90.1-2016 for climate zones that include zone 4?</t>
+  </si>
+  <si>
+    <t>Which space types in the 2010 PRM baseline have lighting power density requirements greater than 1.2 W/ftÂ² and require daylight responsive controls?</t>
+  </si>
+  <si>
+    <t>What are the minimum efficiency requirements for natural gas furnaces in IECC with a capacity between 100 and 200 kBtu/hr?</t>
+  </si>
+  <si>
+    <t>How do the envelope requirements for roofs compare between ASHRAE 90.1-2016 and IECC for buildings in climate zones that include zone 7?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for floors in IECC for buildings in climate zones that include zone 5?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for walls in climate zones 4 and 5, according to ASHRAE 90.1?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for roofs in cold climates (zones 6-8), according to ASHRAE 90.1?</t>
+  </si>
+  <si>
+    <t>How do the envelope requirements for walls in ASHRAE 90.1 compare to those in IECC?</t>
+  </si>
+  <si>
+    <t>What are the ventilation requirements for spaces with high occupancy rates in ASHRAE 62.1?</t>
+  </si>
+  <si>
+    <t>What are the natural gas equipment requirements for kitchen-related spaces in ASHRAE 90.1?</t>
+  </si>
+  <si>
+    <t>Compare the energy recovery effectiveness for different climate zones in ASHRAE 90.1</t>
+  </si>
+  <si>
+    <t>How do the envelope requirements for roofs vary by climate zone in IECC?</t>
+  </si>
+  <si>
+    <t>What are the lighting space types for office buildings according to ASHRAE 90.1?</t>
+  </si>
+  <si>
+    <t>What are the support constructions for walls in ASHRAE 90.1?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for buildings in climate zones 4 or 5 with a roof intended surface type?</t>
+  </si>
+  <si>
+    <t>How do the BTU/hr per HP requirements compare between different fan types for evaporative condensers under current IECC standards?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for buildings in climate zones 3 or 4 with a wall intended surface type under ASHRAE 90.1-2010 standards?</t>
+  </si>
+  <si>
+    <t>Which space types have both high occupancy density (&gt;100 ppl/1000 ftÂ²) and require significant per-person ventilation rates under ASHRAE 90.1-2010 standards?</t>
+  </si>
+  <si>
+    <t>Which space types in the PRM baseline have Building Area (BA) method requirements but still need daylight responsive controls under ASHRAE 90.1-2010 standards?</t>
+  </si>
+  <si>
+    <t>What are the envelope requirements for buildings in climate zones 5 or 6 with a roof intended surface type under ASHRAE 90.1-2010 standards?</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, building_category, construction FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%4%' OR climate_zone_set LIKE '%5%') AND (intended_surface_type LIKE '%Wall%' OR intended_surface_type LIKE '%Roof%')</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, building_category, assembly_maximum_u_value FROM envelope_requirements_IECC WHERE (intended_surface_type LIKE '%Wall%' OR intended_surface_type LIKE '%Roof%') AND building_category LIKE '%Residential%'</t>
+  </si>
+  <si>
+    <t>SELECT id, lighting_primary_space_type, lighting_power_density FROM level_3_lighting_IECC_2006 WHERE (lighting_primary_space_type LIKE '%Retail%' OR lighting_primary_space_type LIKE '%Warehouse%')</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%7%' OR climate_zone_set LIKE '%8%') AND (intended_surface_type LIKE '%Wall%' OR intended_surface_type LIKE '%Roof%')</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, assembly_maximum_solar_heat_gain_coefficient FROM envelope_requirements_IECC WHERE (intended_surface_type LIKE '%Window%') AND building_category LIKE '%Residential%'</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE intended_surface_type LIKE '%Wall%' AND template = '90.1-2013' ORDER BY assembly_maximum_u_value ASC</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, building_category FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%6%' OR climate_zone_set LIKE '%7%') AND building_category LIKE '%Residential%' AND template = '90.1-2010'</t>
+  </si>
+  <si>
+    <t>SELECT equipment_type, minimum_annual_fuel_utilization_efficiency FROM hvac_minimum_requirements_furnaces_90_1 WHERE template = '90.1-2019' ORDER BY minimum_annual_fuel_utilization_efficiency DESC</t>
+  </si>
+  <si>
+    <t>SELECT ventilation_primary_space_type, ventilation_secondary_space_type, ventilation_rate_occupant, ventilation_rate_area, occupancy_per_area FROM level_3_ventilation_62_1_1999 WHERE (ventilation_primary_space_type LIKE '%Education%' OR ventilation_primary_space_type LIKE '%Office%') ORDER BY ventilation_rate_occupant DESC</t>
+  </si>
+  <si>
+    <t>SELECT climate_zone_set, intended_surface_type, assembly_maximum_u_value, assembly_maximum_solar_heat_gain_coefficient FROM envelope_requirements_90_1 WHERE intended_surface_type LIKE '%Roof%' AND (climate_zone_set LIKE '%7%' OR climate_zone_set LIKE '%8%') ORDER BY assembly_maximum_u_value ASC</t>
+  </si>
+  <si>
+    <t>SELECT template, climate_zone, design_conditions, under_8000_hours, percent_oa_30_to_40, percent_oa_40_to_50, percent_oa_50_to_60, energy_recovery_effectiveness FROM system_requirements_energy_recovery_90_1 WHERE (climate_zone LIKE '%6%' OR climate_zone LIKE '%7%' OR climate_zone LIKE '%8%') AND template = '90.1-2013' ORDER BY climate_zone</t>
+  </si>
+  <si>
+    <t>SELECT template, intended_surface_type, assembly_maximum_u_value, assembly_maximum_solar_heat_gain_coefficient FROM envelope_requirements_90_1 WHERE (intended_surface_type LIKE '%Wall%' OR intended_surface_type LIKE '%Roof%') AND template = '90.1-2013' ORDER BY assembly_maximum_u_value ASC</t>
+  </si>
+  <si>
+    <t>SELECT ventilation_primary_space_type, ventilation_secondary_space_type, ventilation_rate_occupant, ventilation_rate_area, occupancy_per_area FROM level_3_ventilation_62_1_1999 WHERE ventilation_primary_space_type LIKE '%Education%' ORDER BY ventilation_rate_occupant DESC</t>
+  </si>
+  <si>
+    <t>SELECT climate_zone_set, intended_surface_type, assembly_maximum_u_value, assembly_maximum_solar_heat_gain_coefficient FROM envelope_requirements_IECC WHERE intended_surface_type LIKE '%Wall%' AND (climate_zone_set LIKE '%3%' OR climate_zone_set LIKE '%4%') ORDER BY assembly_maximum_u_value DESC</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, building_category, construction FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%3%' OR climate_zone_set LIKE '%4%') AND (intended_surface_type LIKE '%Roof%' OR intended_surface_type LIKE '%Wall%')</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type, lighting_secondary_space_type, lighting_power_density, automatic_daylight_responsive_controls_for_sidelighting, automatic_partial_off, automatic_full_off, annotation FROM level_3_lighting_90_1_2016 WHERE lighting_power_density &gt; 1.0 ORDER BY lighting_power_density DESC</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type, lighting_secondary_space_type, method, lighting_power_density, rcr_threshold, automatic_full_off, annotation FROM level_3_lighting_90_1_2016 WHERE (lighting_primary_space_type LIKE '%Sports%' OR lighting_primary_space_type LIKE '%Entertainment%') ORDER BY lighting_power_density DESC</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, building_category, construction FROM envelope_requirements_IECC WHERE (climate_zone_set LIKE '%5%' OR climate_zone_set LIKE '%6%') AND (intended_surface_type LIKE '%Wall%' OR intended_surface_type LIKE '%Floor%')</t>
+  </si>
+  <si>
+    <t>SELECT template, air_system, air_system_component, fan_system, minimum_capacity, maximum_capacity, fan_power_allowance, annotation FROM system_requirements_fan_power_allowance_90_1 WHERE (air_system_component LIKE '%recovery%' OR air_system_component LIKE '%enthalpy%' OR air_system_component LIKE '%run-around%') AND template = '90.1-2025' ORDER BY fan_power_allowance DESC</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, assembly_maximum_u_value, annotation FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%4%' OR climate_zone_set LIKE '%5%') AND intended_surface_type LIKE '%Wall'</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type, lighting_power_density, automatic_partial_off, annotation FROM level_3_lighting_90_1_2016 WHERE automatic_partial_off = 'REQ' AND lighting_power_density &gt; 1.0 ORDER BY lighting_power_density DESC</t>
+  </si>
+  <si>
+    <t>SELECT template, air_system_component, minimum_capacity, maximum_capacity, fan_power_allowance, annotation FROM system_requirements_fan_power_allowance_90_1 WHERE air_system_component LIKE '%MERV 13 to MERV 16 filter%'</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, assembly_maximum_u_value, annotation FROM envelope_requirements_90_1 WHERE intended_surface_type LIKE '%Roof%' AND assembly_maximum_u_value &lt; 0.05 ORDER BY assembly_maximum_u_value ASC</t>
+  </si>
+  <si>
+    <t>SELECT ventilation_primary_space_type, air_class, ventilation_rate_occupant, ventilation_rate_area, annotation FROM level_3_ventilation_62_1_2004 WHERE air_class = 2 ORDER BY ventilation_rate_area DESC</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type, lighting_power_density, automatic_daylight_responsive_controls_for_sidelighting, annotation FROM level_3_lighting_90_1_2016 WHERE (lighting_primary_space_type LIKE '%Sports%' OR lighting_primary_space_type LIKE '%Religious%' OR lighting_primary_space_type LIKE '%Convention%') AND lighting_power_density &gt; 1.0 AND automatic_daylight_responsive_controls_for_sidelighting = 'REQ' ORDER BY lighting_power_density DESC</t>
+  </si>
+  <si>
+    <t>SELECT template, compressor_type, minimum_capacity, maximum_capacity, minimum_integrated_part_load_value, annotation FROM hvac_minimum_requirements_chillers_90_1 WHERE minimum_integrated_part_load_value &gt; 0.8 ORDER BY minimum_integrated_part_load_value DESC</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type, lighting_power_density, automatic_partial_off, annotation FROM level_3_lighting_90_1_2013 WHERE lighting_primary_space_type LIKE '%Office%' AND automatic_partial_off = 'REQ'</t>
+  </si>
+  <si>
+    <t>SELECT assembly_maximum_u_value, assembly_maximum_u_value_unit FROM envelope_requirements_90_1 WHERE template = '90.1-2004' AND climate_zone_set LIKE '%6%' AND intended_surface_type LIKE '%Wall%' AND standards_construction_type = 'Mass' AND building_category = 'Residential'</t>
+  </si>
+  <si>
+    <t>SELECT template, climate_zone_set, intended_surface_type, assembly_maximum_solar_heat_gain_coefficient FROM envelope_requirements_90_1 WHERE template = '90.1-2016' AND (climate_zone_set LIKE '%2%' OR climate_zone_set LIKE '%5%') AND intended_surface_type LIKE '%Skylight%'</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type, lighting_secondary_space_type, automatic_full_off, scheduled_shutoff FROM level_3_lighting_90_1_2019 WHERE lighting_primary_space_type LIKE '%Laboratory%'</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type, lighting_power_density, automatic_full_off, annotation FROM level_3_lighting_90_1_2010 WHERE lighting_power_density &gt; 1.2 AND automatic_full_off = 'REQ'</t>
+  </si>
+  <si>
+    <t>SELECT intended_surface_type, assembly_maximum_u_value, climate_zone_set FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%4%' OR climate_zone_set LIKE '%5%') AND intended_surface_type LIKE '%Wall'</t>
+  </si>
+  <si>
+    <t>SELECT electric_equipment_space_type_name, electric_equipment_average_epd, electric_equipment_fraction_latent FROM level_2_electric_equipment WHERE electric_equipment_average_epd &gt; 0.5 AND electric_equipment_fraction_latent &gt; 0</t>
+  </si>
+  <si>
+    <t>SELECT template, equipment_type, subcategory, rating_condition, minimum_capacity, maximum_capacity, minimum_coefficient_of_performance_heating FROM hvac_minimum_requirements_heat_pumps_heating_90_1 WHERE ((equipment_type = 'Heat Pumps' AND subcategory = 'Single Package') OR (equipment_type = 'High-Efficiency Heat Pumps')) AND minimum_capacity &lt;= 65000 AND maximum_capacity &gt;= 30000</t>
+  </si>
+  <si>
+    <t>SELECT natural_gas_equipment_space_type_name, natural_gas_equipment_average_epd, natural_gas_equipment_fraction_radiant FROM level_2_natural_gas_equipment WHERE natural_gas_equipment_average_epd &gt; 0.2 AND natural_gas_equipment_fraction_radiant &gt; 0</t>
+  </si>
+  <si>
+    <t>SELECT intended_surface_type, assembly_maximum_solar_heat_gain_coefficient, climate_zone_set FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%3%' OR climate_zone_set LIKE '%4%') AND intended_surface_type LIKE '%Roof'</t>
+  </si>
+  <si>
+    <t>SELECT intended_surface_type, assembly_maximum_u_value FROM envelope_requirements_IECC WHERE (climate_zone_set LIKE '%4%' OR climate_zone_set LIKE '%5%') AND intended_surface_type LIKE '%Wall'</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type, lighting_secondary_space_type, automatic_full_off, scheduled_shutoff FROM level_3_lighting_90_1_2013 WHERE (lighting_primary_space_type LIKE '%Visually Impaired%' OR lighting_secondary_space_type LIKE '%visually impaired%') OR (lighting_primary_space_type IN ('Lobby', 'Dormitory Living Quarters'))</t>
+  </si>
+  <si>
+    <t>SELECT level_3_ventilation_definition_id, level_3_ventilation_definition_table, COUNT(*) as space_types_using_this_id FROM level_2_ventilation_space_types WHERE ventilation_space_type_name LIKE '%Office%' GROUP BY level_3_ventilation_definition_id, level_3_ventilation_definition_table HAVING COUNT(*) &gt; 1</t>
+  </si>
+  <si>
+    <t>SELECT template, cooling_type, compressor_type, minimum_capacity, maximum_capacity, start_date, end_date, minimum_integrated_part_load_value FROM hvac_minimum_requirements_chillers_IECC WHERE template = 'IECC-2015' AND cooling_type = 'WaterCooled' AND compressor_type = 'Rotary Screw' AND start_date &gt;= 2015</t>
+  </si>
+  <si>
+    <t>SELECT intended_surface_type, assembly_maximum_solar_heat_gain_coefficient FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%6%' OR climate_zone_set LIKE '%7%') AND intended_surface_type LIKE '%Roof'</t>
+  </si>
+  <si>
+    <t>SELECT space_type_name, natural_gas_equipment_space_type_name, electric_equipment_space_type_name FROM level_1_space_types WHERE natural_gas_equipment_space_type_name IS NOT NULL OR electric_equipment_space_type_name IS NOT NULL</t>
+  </si>
+  <si>
+    <t>SELECT intended_surface_type, assembly_minimum_visible_transmittance FROM envelope_requirements_IECC WHERE (climate_zone_set LIKE '%3%' OR climate_zone_set LIKE '%4%') AND intended_surface_type LIKE '%Window'</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%4%' OR climate_zone_set LIKE '%5%') AND intended_surface_type LIKE '%Roof%' ORDER BY assembly_maximum_u_value</t>
+  </si>
+  <si>
+    <t>SELECT template, cooling_type, standard_model, rating_condition, minimum_capacity, maximum_capacity, minimum_scop, annotation FROM hvac_minimum_requirements_computer_room_air_conditioners_90_1 WHERE cooling_type LIKE '%AirCooled%' AND minimum_capacity &lt;= 100000 AND maximum_capacity &gt;= 100000 AND template = '90.1-2010' ORDER BY cooling_type, standard_model</t>
+  </si>
+  <si>
+    <t>SELECT template, type, number_of_poles, synchronous_speed, minimum_capacity, maximum_capacity, nominal_full_load_efficiency, annotation FROM hvac_minimum_requirements_motors_90_1 WHERE minimum_capacity &lt;= 25 AND maximum_capacity &gt;= 15 AND template = '90.1-2007' AND type IN ('Enclosed', 'Open') ORDER BY type, number_of_poles, minimum_capacity</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, assembly_maximum_u_value FROM envelope_requirements_IECC WHERE (climate_zone_set LIKE '%7%' OR climate_zone_set LIKE '%8%') AND intended_surface_type LIKE '%Wall%' ORDER BY assembly_maximum_u_value</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type, lighting_secondary_space_type, lighting_power_density, supplemental_lighting_power_density, automatic_full_off, scheduled_shutoff, method, annotation FROM level_3_lighting_90_1_2004 WHERE supplemental_lighting_power_density IS NOT NULL OR automatic_full_off IS NOT NULL OR scheduled_shutoff IS NOT NULL ORDER BY lighting_power_density DESC</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%3%' OR climate_zone_set LIKE '%4%') AND intended_surface_type LIKE '%Floor%' ORDER BY assembly_maximum_u_value</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, building_category, construction FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%4%' OR climate_zone_set LIKE '%5%') AND intended_surface_type LIKE '%Roof%' ORDER BY assembly_maximum_u_value</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, building_category, construction, assembly_maximum_u_value FROM envelope_requirements_IECC WHERE (climate_zone_set LIKE '%3%' OR climate_zone_set LIKE '%4%') AND intended_surface_type LIKE '%Wall%' ORDER BY assembly_maximum_u_value</t>
+  </si>
+  <si>
+    <t>SELECT ventilation_primary_space_type, ventilation_secondary_space_type, air_class, ventilation_rate_occupant, ventilation_rate_area, occupancy_per_area FROM level_3_ventilation_62_1_2007 WHERE occupancy_per_area &gt; 10 ORDER BY ventilation_rate_area DESC</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, building_category, construction FROM envelope_requirements_90_1_prm WHERE (climate_zone_set LIKE '%6%' OR climate_zone_set LIKE '%7%') AND intended_surface_type LIKE '%Roof%' ORDER BY assembly_maximum_u_value</t>
+  </si>
+  <si>
+    <t>SELECT id, lighting_space_type_name, level_3_lighting_code_definition_table, level_3_lighting_code_definition_id, lighting_technology_name, lighting_space_type_target_illuminance_setpoint FROM level_2_lighting_space_types WHERE lighting_space_type_target_illuminance_setpoint &gt; 30 ORDER BY lighting_space_type_target_illuminance_setpoint DESC</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, building_category, construction FROM envelope_requirements_IECC WHERE (climate_zone_set LIKE '%2%' OR climate_zone_set LIKE '%3%') AND intended_surface_type LIKE '%Wall%' ORDER BY assembly_maximum_u_value</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE template LIKE '%90.1-2010%' AND intended_surface_type LIKE '%Wall%' ORDER BY climate_zone_set</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type, lighting_secondary_space_type, lighting_power_density FROM level_3_lighting_IECC_2006 WHERE lighting_power_density &gt;= 1.0 ORDER BY lighting_power_density DESC</t>
+  </si>
+  <si>
+    <t>SELECT template, climate_zone, design_conditions, percent_oa_30_to_40, percent_oa_40_to_50 FROM system_requirements_energy_recovery_90_1 WHERE template LIKE '%90.1-2010%' AND (climate_zone LIKE '%A%' OR climate_zone LIKE '%B%') ORDER BY climate_zone</t>
+  </si>
+  <si>
+    <t>SELECT ventilation_primary_space_type, ventilation_secondary_space_type, ventilation_rate_occupant FROM level_3_ventilation_62_1_2007 WHERE ventilation_rate_occupant &gt;= 10 ORDER BY ventilation_rate_occupant DESC</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type FROM envelope_requirements_IECC WHERE intended_surface_type LIKE '%Roof%' ORDER BY climate_zone_set</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type, lighting_secondary_space_type, lighting_power_density FROM level_3_lighting_IECC_2006 WHERE lighting_primary_space_type LIKE '%Office%' ORDER BY lighting_power_density DESC</t>
+  </si>
+  <si>
+    <t>SELECT template, climate_zone, design_conditions, percent_oa_30_to_40 FROM system_requirements_energy_recovery_90_1 WHERE template LIKE '%90.1-2010%' AND percent_oa_30_to_40 &lt; 5000 ORDER BY percent_oa_30_to_40</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type FROM envelope_requirements_IECC WHERE (climate_zone_set LIKE '%4%' OR climate_zone_set LIKE '%5%') AND intended_surface_type LIKE '%Wall%' ORDER BY standards_construction_type</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type, lighting_secondary_space_type, method, lighting_power_density, rcr_threshold, automatic_daylight_responsive_controls_for_sidelighting FROM level_3_lighting_90_1_2010_prm WHERE lighting_power_density &gt; 1.2 AND automatic_daylight_responsive_controls_for_sidelighting = 'REQ'</t>
+  </si>
+  <si>
+    <t>SELECT level_3_ventilation_definition_id, level_3_ventilation_definition_table, COUNT(*) as space_types_using_this_id FROM level_2_ventilation_space_types GROUP BY level_3_ventilation_definition_id, level_3_ventilation_definition_table HAVING COUNT(*) &gt; 1 ORDER BY space_types_using_this_id DESC</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type, lighting_secondary_space_type, method, lighting_power_density, rcr_threshold, automatic_full_off FROM level_3_lighting_90_1_2019 WHERE lighting_power_density &gt; 0.8 AND automatic_full_off = 'REQ'</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%6%' OR climate_zone_set LIKE '%7%') AND building_category = 'Residential' AND intended_surface_type LIKE '%Wall%'</t>
+  </si>
+  <si>
+    <t>SELECT template, equipment_type, fuel_type, subtype, minimum_capacity, maximum_capacity, minimum_annual_fuel_utilization_efficiency FROM hvac_minimum_requirements_furnaces_90_1 WHERE fuel_type = 'Oil' AND minimum_capacity &lt;= 300000 AND maximum_capacity &gt;= 200000</t>
+  </si>
+  <si>
+    <t>SELECT intended_surface_type, assembly_maximum_u_value, assembly_maximum_u_value_unit, standards_construction_type FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%5%' OR climate_zone_set LIKE '%6%') AND intended_surface_type LIKE '%Wall' ORDER BY assembly_maximum_u_value</t>
+  </si>
+  <si>
+    <t>SELECT DISTINCT lighting_space_type_name, MAX(lighting_space_type_target_illuminance_setpoint) as max_illuminance, lighting_technology_name FROM level_2_lighting_space_types WHERE lighting_space_type_name LIKE '%Retail%' GROUP BY lighting_space_type_name, lighting_technology_name ORDER BY max_illuminance DESC</t>
+  </si>
+  <si>
+    <t>SELECT intended_surface_type, standards_construction_type, building_category, assembly_maximum_u_value, assembly_maximum_u_value_unit FROM envelope_requirements_IECC WHERE intended_surface_type LIKE '%Roof%' ORDER BY building_category</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type, lighting_secondary_space_type, lighting_power_density FROM level_3_lighting_90_1_2013 WHERE (lighting_primary_space_type LIKE '%Sports%' OR lighting_primary_space_type LIKE '%Entertainment%') ORDER BY lighting_power_density DESC</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%4%' OR climate_zone_set LIKE '%5%') AND intended_surface_type LIKE '%Wall'</t>
+  </si>
+  <si>
+    <t>SELECT lighting_space_type_name, level_3_lighting_code_definition_table, lighting_space_type_target_illuminance_setpoint FROM level_2_lighting_space_types WHERE lighting_space_type_name LIKE '%Retail%'</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, assembly_maximum_u_value FROM envelope_requirements_IECC WHERE intended_surface_type LIKE '%Floor%' ORDER BY assembly_maximum_u_value DESC</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%4%' OR climate_zone_set LIKE '%5%') AND intended_surface_type LIKE '%Wall%'</t>
+  </si>
+  <si>
+    <t>SELECT ventilation_primary_space_type, ventilation_secondary_space_type, ventilation_rate_occupant, ventilation_rate_area, occupancy_per_area, air_class, annotation FROM level_3_ventilation_62_1_2007 WHERE occupancy_per_area &gt; 100 AND ventilation_rate_occupant &gt; 5</t>
+  </si>
+  <si>
+    <t>SELECT name, intended_surface_type, standards_construction_type, insulation_layer, material_1, material_2 FROM support_constructions WHERE intended_surface_type LIKE '%Wall%' AND insulation_layer IS NOT NULL</t>
+  </si>
+  <si>
+    <t>SELECT template, climate_zone_set, intended_surface_type, standards_construction_type, assembly_maximum_u_value FROM envelope_requirements_IECC WHERE climate_zone_set LIKE '%6%' AND intended_surface_type LIKE '%Roof%'</t>
+  </si>
+  <si>
+    <t>SELECT template, equipment_type, fan_type, minimum_performance_gpm_per_hp, minimum_performance_btu_per_hr_per_hp, annotation FROM hvac_minimum_requirements_heat_rejection_90_1 WHERE equipment_type LIKE '%Cooling Tower%' AND minimum_performance_gpm_per_hp IS NOT NULL AND fan_type IS NOT NULL</t>
+  </si>
+  <si>
+    <t>SELECT ventilation_primary_space_type, ventilation_secondary_space_type, ventilation_rate_occupant, ventilation_rate_area, occupancy_per_area, air_class, annotation FROM level_3_ventilation_62_1_2010 WHERE occupancy_per_area &gt; 100 AND ventilation_rate_occupant &gt; 5</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, assembly_maximum_u_value FROM envelope_requirements_IECC WHERE (climate_zone_set LIKE '%7%' OR climate_zone_set LIKE '%8%') AND intended_surface_type LIKE '%Floor%' AND template LIKE '%IECC-2021%'</t>
+  </si>
+  <si>
+    <t>SELECT intended_surface_type, standards_construction_type, building_category, assembly_maximum_u_value, assembly_minimum_visible_transmittance FROM envelope_requirements_IECC WHERE (climate_zone_set LIKE '%7%' OR climate_zone_set LIKE '%8%') AND building_category LIKE '%Residential%' AND intended_surface_type LIKE '%Wall'</t>
+  </si>
+  <si>
+    <t>SELECT intended_surface_type, standards_construction_type, building_category, assembly_maximum_u_value, assembly_minimum_visible_transmittance FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%5%') AND building_category LIKE '%Residential%' AND intended_surface_type LIKE '%Window%' AND template IN ('90.1-2016', '90.1-2019', 'IECC-2018')</t>
+  </si>
+  <si>
+    <t>SELECT template, air_system_component, minimum_capacity, maximum_capacity, fan_power_allowance FROM system_requirements_fan_power_allowance_90_1 WHERE air_system_component IN ('Filter not higher than MERV 12', 'MERV 13 to MERV 16 filter') ORDER BY minimum_capacity</t>
+  </si>
+  <si>
+    <t>SELECT template, equipment_type, cooling_type, minimum_capacity, maximum_capacity, minimum_energy_efficiency_ratio FROM hvac_minimum_requirements_unitary_air_conditioners_90_1 WHERE equipment_type = 'Condensing Units' AND cooling_type = 'AirCooled' ORDER BY template</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, assembly_maximum_u_value FROM envelope_requirements_IECC WHERE (climate_zone_set LIKE '%6%' OR climate_zone_set LIKE '%7%') AND intended_surface_type LIKE '%Roof'</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, assembly_maximum_solar_heat_gain_coefficient FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%3%' OR climate_zone_set LIKE '%4%') AND intended_surface_type LIKE '%Window'</t>
+  </si>
+  <si>
+    <t>SELECT electric_equipment_space_type_name, electric_equipment_minimum_epd, electric_equipment_maximum_epd, (electric_equipment_maximum_epd - electric_equipment_minimum_epd) as epd_range FROM level_2_electric_equipment WHERE electric_equipment_maximum_epd &gt; electric_equipment_minimum_epd ORDER BY epd_range DESC</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, assembly_maximum_u_value FROM envelope_requirements_IECC WHERE (climate_zone_set LIKE '%5%' OR climate_zone_set LIKE '%6%') AND intended_surface_type LIKE '%Wall'</t>
+  </si>
+  <si>
+    <t>SELECT electric_equipment_space_type_name, electric_equipment_average_epd, electric_equipment_median_epd, electric_equipment_fraction_latent FROM level_2_electric_equipment WHERE electric_equipment_average_epd &gt; 0.5 AND electric_equipment_fraction_latent &gt; 0</t>
+  </si>
+  <si>
+    <t>SELECT template, number_of_poles, synchronous_speed, type, minimum_capacity, maximum_capacity, nominal_full_load_efficiency FROM hvac_minimum_requirements_motors_IECC WHERE minimum_capacity &lt;= 30 AND maximum_capacity &gt;= 20 AND number_of_poles = 2 ORDER BY template</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, assembly_maximum_u_value FROM envelope_requirements_90_1_prm WHERE (climate_zone_set LIKE '%7%' OR climate_zone_set LIKE '%8%') AND intended_surface_type LIKE '%Roof'</t>
+  </si>
+  <si>
+    <t>SELECT template, equipment_type, subcategory, rating_condition, minimum_capacity, maximum_capacity, minimum_coefficient_of_performance_heating FROM hvac_minimum_requirements_heat_pumps_heating_90_1 WHERE ((equipment_type = 'SPVHP' AND subcategory = 'Nonweatherized Space Constrained') OR (equipment_type = 'Heat Pumps' AND subcategory = 'Single Package')) AND minimum_capacity &lt;= 20000 AND maximum_capacity &gt;= 10000</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, building_category, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%5%' OR climate_zone_set LIKE '%6%') AND building_category = 'Nonresidential' AND template = '90.1-2010'</t>
+  </si>
+  <si>
+    <t>SELECT equipment_type, subcategory, region, minimum_seasonal_energy_efficiency_ratio_2, start_date, end_date FROM hvac_minimum_requirements_heat_pumps_cooling_IECC WHERE equipment_type = 'Heat Pumps' AND subcategory = 'Split System' AND (minimum_capacity &lt;= 24000 AND maximum_capacity &gt;= 24000) AND template = 'IECC-2021'</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, building_category, assembly_maximum_u_value FROM envelope_requirements_IECC WHERE climate_zone_set LIKE '%7%' AND intended_surface_type LIKE '%Roof%' AND building_category = 'Residential' AND template = 'IECC-2024'</t>
+  </si>
+  <si>
+    <t>SELECT equipment_type, subcategory, minimum_seasonal_energy_efficiency_ratio_2, start_date, end_date FROM hvac_minimum_requirements_heat_pumps_cooling_90_1 WHERE (equipment_type = 'Heat Pumps' OR equipment_type = 'Air Conditioners') AND subcategory = 'Split System' AND (minimum_capacity &lt;= 36000 AND maximum_capacity &gt;= 36000) AND template = '90.1-2010'</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, building_category, assembly_maximum_u_value FROM envelope_requirements_IECC WHERE climate_zone_set LIKE '%4%' AND intended_surface_type LIKE '%Wall%' AND building_category = 'Nonresidential' AND template = 'IECC-2021'</t>
+  </si>
+  <si>
+    <t>SELECT template, air_system_component, minimum_capacity, maximum_capacity, fan_power_allowance FROM system_requirements_fan_power_allowance_90_1 WHERE template = '90.1-2025' AND air_system LIKE '%Exhaust%' ORDER BY air_system_component</t>
+  </si>
+  <si>
+    <t>SELECT assembly_minimum_visible_transmittance, climate_zone_set, intended_surface_type FROM envelope_requirements_IECC WHERE template = 'IECC-2018' AND building_category LIKE '%Residential%' AND intended_surface_type LIKE '%Skylight%'</t>
+  </si>
+  <si>
+    <t>SELECT assembly_maximum_u_value, assembly_maximum_u_value_unit, building_category, intended_surface_type FROM envelope_requirements_90_1 WHERE template = '90.1-2004' AND climate_zone_set LIKE '%4%' AND intended_surface_type LIKE '%Wall%' AND building_category LIKE '%Residential'</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE climate_zone_set LIKE '%4%' AND intended_surface_type LIKE '%Roof%' AND template = '90.1-2010'</t>
+  </si>
+  <si>
+    <t>SELECT electric_equipment_space_type_name, electric_equipment_average_epd, electric_equipment_fraction_radiant FROM level_2_electric_equipment WHERE electric_equipment_average_epd &gt; 0.5 AND electric_equipment_fraction_radiant &gt; 0 ORDER BY electric_equipment_average_epd DESC</t>
+  </si>
+  <si>
+    <t>SELECT template, type, number_of_poles, synchronous_speed, minimum_capacity, maximum_capacity, nominal_full_load_efficiency FROM hvac_minimum_requirements_motors_IECC WHERE minimum_capacity &gt;= 1 AND maximum_capacity &lt;= 10 AND type = 'Open' AND template = 'IECC-2018'</t>
+  </si>
+  <si>
+    <t>SELECT template, equipment_type, subcategory, region, minimum_seasonal_energy_efficiency_ratio_2, start_date, end_date FROM hvac_minimum_requirements_heat_pumps_cooling_90_1 WHERE equipment_type = 'Heat Pumps' AND subcategory = 'Split System' AND minimum_capacity &lt;= 24000 AND maximum_capacity &gt;= 24000 AND template = '90.1-2013'</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, assembly_maximum_u_value FROM envelope_requirements_IECC WHERE climate_zone_set LIKE '%5%' AND intended_surface_type LIKE '%Wall%' AND template = 'IECC-2021'</t>
+  </si>
+  <si>
+    <t>SELECT electric_equipment_space_type_name, electric_equipment_minimum_epd, electric_equipment_maximum_epd, (electric_equipment_maximum_epd - electric_equipment_minimum_epd) AS epd_range, electric_equipment_fraction_radiant FROM level_2_electric_equipment WHERE electric_equipment_fraction_radiant &gt; 0 ORDER BY epd_range ASC</t>
+  </si>
+  <si>
+    <t>SELECT template, type, number_of_poles, synchronous_speed, minimum_capacity, maximum_capacity, nominal_full_load_efficiency FROM hvac_minimum_requirements_motors_90_1 WHERE minimum_capacity &gt;= 10 AND maximum_capacity &lt;= 20 AND type = 'Enclosed' AND template = '90.1-2010'</t>
+  </si>
+  <si>
+    <t>SELECT assembly_maximum_u_value, assembly_maximum_u_value_unit FROM envelope_requirements_IECC WHERE template = 'IECC-2015' AND climate_zone_set LIKE '%3%' AND intended_surface_type LIKE '%Wall%' AND building_category LIKE '%Residential'</t>
+  </si>
+  <si>
+    <t>SELECT assembly_maximum_u_value, assembly_maximum_u_value_unit FROM envelope_requirements_IECC WHERE template = 'IECC-2018' AND climate_zone_set LIKE '%5%' AND intended_surface_type LIKE '%Roof%' AND building_category NOT LIKE '%Residential'</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, assembly_maximum_u_value FROM envelope_requirements_IECC WHERE (climate_zone_set LIKE '%1%' OR climate_zone_set LIKE '%2%' OR climate_zone_set LIKE '%3%') AND building_category IN ('Residential', 'Commercial')</t>
+  </si>
+  <si>
+    <t>SELECT standards_construction_type, assembly_maximum_u_value, climate_zone_set FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%6%' OR climate_zone_set LIKE '%7%' OR climate_zone_set LIKE '%8%') AND intended_surface_type LIKE '%Wall%' ORDER BY assembly_maximum_u_value DESC</t>
+  </si>
+  <si>
+    <t>SELECT template, climate_zone, design_conditions, under_8000_hours, percent_oa_30_to_40 FROM system_requirements_energy_recovery_90_1 WHERE (climate_zone LIKE '%1%' OR climate_zone LIKE '%2%' OR climate_zone LIKE '%3%') AND design_conditions = 'Heating'</t>
+  </si>
+  <si>
+    <t>SELECT standards_construction_type, assembly_maximum_u_value, climate_zone_set FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%1%' OR climate_zone_set LIKE '%2%' OR climate_zone_set LIKE '%3%') AND intended_surface_type LIKE '%Roof%' ORDER BY assembly_maximum_u_value ASC</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%3%' OR climate_zone_set LIKE '%4%') AND intended_surface_type LIKE '%Roof'</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type, lighting_secondary_space_type, method, lighting_power_density, automatic_daylight_responsive_controls_for_sidelighting FROM level_3_lighting_90_1_2010_prm WHERE method = 'BA' AND (automatic_daylight_responsive_controls_for_sidelighting = 'REQ' OR automatic_daylight_responsive_controls_for_toplighting = 'REQ') ORDER BY lighting_power_density DESC</t>
+  </si>
+  <si>
+    <t>SELECT template, climate_zone, under_8000_hours, design_conditions, percent_oa_70_to_80, percent_oa_greater_than_80 FROM system_requirements_energy_recovery_90_1 WHERE (climate_zone LIKE '%7%' OR climate_zone LIKE '%8%') ORDER BY percent_oa_greater_than_80</t>
+  </si>
+  <si>
+    <t>SELECT electric_equipment_space_type_name, electric_equipment_average_epd, electric_equipment_median_epd, electric_equipment_fraction_latent FROM level_2_electric_equipment WHERE electric_equipment_average_epd &gt; 0.7 AND electric_equipment_fraction_latent &gt; 0 ORDER BY electric_equipment_average_epd DESC</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, assembly_maximum_u_value FROM envelope_requirements_IECC WHERE (climate_zone_set LIKE '%3%' OR climate_zone_set LIKE '%4%') AND intended_surface_type LIKE '%Wall'</t>
+  </si>
+  <si>
+    <t>SELECT template, climate_zone_set, intended_surface_type, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%4%' OR climate_zone_set LIKE '%5%') AND intended_surface_type LIKE '%Wall'</t>
+  </si>
+  <si>
+    <t>SELECT template, climate_zone_set, intended_surface_type, assembly_minimum_visible_transmittance FROM envelope_requirements_IECC WHERE (climate_zone_set LIKE '%3%' OR climate_zone_set LIKE '%4%') AND intended_surface_type LIKE '%Window'</t>
+  </si>
+  <si>
+    <t>SELECT template, intended_surface_type, assembly_maximum_solar_heat_gain_coefficient FROM envelope_requirements_IECC WHERE template = 'IECC-2012' AND intended_surface_type LIKE '%Skylight%'</t>
+  </si>
+  <si>
+    <t>SELECT name, insulation_layer FROM support_constructions ORDER BY insulation_layer DESC LIMIT 5</t>
+  </si>
+  <si>
+    <t>SELECT template, air_system, air_system_component, fan_system, minimum_capacity, maximum_capacity, fan_power_allowance, annotation FROM system_requirements_fan_power_allowance_90_1 WHERE (air_system LIKE '%supply%' OR air_system LIKE '%exhaust%') AND template = '90.1-2025' ORDER BY fan_power_allowance DESC, air_system;</t>
+  </si>
+  <si>
+    <t>SELECT ventilation_primary_space_type, ventilation_secondary_space_type, ventilation_rate_occupant, ventilation_rate_area, occupancy_per_area, air_class, annotation FROM level_3_ventilation_62_1_2007 WHERE occupancy_per_area &gt; 50 AND ventilation_rate_occupant &gt; 5 ORDER BY occupancy_per_area DESC, ventilation_rate_occupant DESC;</t>
+  </si>
+  <si>
+    <t>SELECT template, climate_zone, data_center, fixed_dry_bulb_high_limit_shutoff_temp, fixed_enthalpy_high_limit_shutoff_enthalpy, dew_point_dry_bulb_high_limit_shutoff_dew_point_temp, dew_point_dry_bulb_high_limit_shutoff_dry_bulb_temp, annotation FROM system_requirements_air_economizer_90_1 WHERE (climate_zone LIKE '%4A%') AND template IN ('90.1-2004', '90.1-2010') ORDER BY template, data_center;</t>
+  </si>
+  <si>
+    <t>SELECT template, air_system_component, minimum_capacity, maximum_capacity, fan_power_allowance, fan_system, annotation FROM system_requirements_fan_power_allowance_90_1 WHERE (air_system_component LIKE '%MERV%') AND template = '90.1-2025' ORDER BY minimum_capacity, fan_power_allowance;</t>
+  </si>
+  <si>
+    <t>SELECT DISTINCT lighting_space_type_name, MAX(lighting_space_type_target_illuminance_setpoint) as max_illuminance, lighting_technology_name, lighting_space_type_target_illuminance_setpoint_unit FROM level_2_lighting_space_types WHERE lighting_space_type_target_illuminance_setpoint &gt; 400 GROUP BY lighting_space_type_name, lighting_technology_name, lighting_space_type_target_illuminance_setpoint_unit ORDER BY max_illuminance DESC;</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, building_category, construction, minimum_percent_of_surface, maximum_percent_of_surface, assembly_maximum_u_value, annotation FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%7%' OR climate_zone_set LIKE '%8%') AND intended_surface_type LIKE '%Wall%' AND template IN ('90.1-2010', 'IECC') ORDER BY climate_zone_set, standards_construction_type;</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, building_category, construction, minimum_percent_of_surface, maximum_percent_of_surface, assembly_maximum_u_value, annotation FROM envelope_requirements_90_1 WHERE intended_surface_type LIKE '%Roof%' AND template = '90.1-2010' ORDER BY climate_zone_set;</t>
+  </si>
+  <si>
+    <t>SELECT id, template, type, number_of_poles, synchronous_speed, minimum_capacity, maximum_capacity, nominal_full_load_efficiency FROM hvac_minimum_requirements_motors_IECC ORDER BY nominal_full_load_efficiency DESC</t>
+  </si>
+  <si>
+    <t>SELECT ventilation_primary_space_type, ventilation_secondary_space_type, ventilation_rate_occupant, ventilation_rate_area, occupancy_per_area FROM level_3_ventilation_62_1_2019 WHERE ventilation_primary_space_type LIKE '%Education%' ORDER BY ventilation_rate_occupant DESC</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type, lighting_secondary_space_type, lighting_power_density, automatic_full_off, scheduled_shutoff FROM level_3_lighting_90_1_2019 WHERE lighting_primary_space_type LIKE '%Office%' ORDER BY lighting_power_density DESC</t>
+  </si>
+  <si>
+    <t>SELECT id, template, air_system, air_system_component, fan_system, minimum_capacity, maximum_capacity, fan_power_allowance FROM system_requirements_fan_power_allowance_90_1 WHERE (air_system_component LIKE '%recovery%' OR air_system_component LIKE '%enthalpy%' OR air_system_component LIKE '%run-around%') AND template = '90.1-2025'</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, building_category, construction, minimum_percent_of_surface, maximum_percent_of_surface FROM envelope_requirements_IECC WHERE (climate_zone_set LIKE '%3%' OR climate_zone_set LIKE '%4%') AND intended_surface_type LIKE '%Wall'</t>
+  </si>
+  <si>
+    <t>SELECT template, climate_zone, design_conditions, percent_oa_30_to_40, percent_oa_40_to_50, percent_oa_50_to_60, percent_oa_60_to_70, percent_oa_70_to_80, percent_oa_greater_than_80, energy_recovery_effectiveness FROM system_requirements_energy_recovery_90_1 WHERE template = '90.1-2016' AND (climate_zone LIKE '%A%' OR climate_zone LIKE '%B%') ORDER BY climate_zone</t>
+  </si>
+  <si>
+    <t>SELECT intended_surface_type, standards_construction_type, assembly_maximum_u_value, assembly_maximum_u_value_unit FROM envelope_requirements_IECC WHERE template = 'IECC-2015' AND climate_zone_set LIKE '%7%' AND intended_surface_type LIKE '%Roof%' ORDER BY assembly_maximum_u_value DESC</t>
+  </si>
+  <si>
+    <t>SELECT template, equipment_type, subcategory, minimum_capacity, maximum_capacity, minimum_energy_efficiency_ratio FROM hvac_minimum_requirements_variable_refrigerant_flow_systems_90_1 WHERE template = '90.1-2019' AND (equipment_type LIKE '%GroundSource%' OR equipment_type LIKE '%WaterSource%') ORDER BY equipment_type</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, building_category, construction FROM envelope_requirements_90_1 WHERE template = '90.1-2016' AND climate_zone_set LIKE '%3%' AND building_category LIKE '%Residential'</t>
+  </si>
+  <si>
+    <t>SELECT assembly_maximum_u_value, building_category, climate_zone_set, intended_surface_type FROM envelope_requirements_90_1 WHERE template = '90.1-2010' AND climate_zone_set LIKE '%5%' AND intended_surface_type LIKE '%Wall%' AND building_category LIKE '%Nonresidential%'</t>
+  </si>
+  <si>
+    <t>SELECT assembly_maximum_f_factor, building_category, intended_surface_type FROM envelope_requirements_IECC WHERE climate_zone_set LIKE '%5%' AND intended_surface_type LIKE '%Skylight%' AND building_category LIKE '%Nonresidential%'</t>
+  </si>
+  <si>
+    <t>SELECT equipment_type, fan_type, minimum_performance_gpm_per_hp FROM hvac_minimum_requirements_heat_rejection_90_1 WHERE template = '90.1-2013' AND minimum_performance_gpm_per_hp IS NOT NULL</t>
+  </si>
+  <si>
+    <t>SELECT assembly_maximum_solar_heat_gain_coefficient, orientation FROM envelope_requirements_90_1 WHERE template = '90.1-2004' AND climate_zone_set LIKE '%7%' AND intended_surface_type LIKE '%GlassDoor%' AND building_category LIKE '%Nonresidential%' AND orientation LIKE '%S%'</t>
+  </si>
+  <si>
+    <t>SELECT assembly_maximum_u_value, building_category FROM envelope_requirements_IECC WHERE climate_zone_set LIKE '%6%' AND intended_surface_type LIKE '%Roof%'</t>
+  </si>
+  <si>
+    <t>SELECT ventilation_primary_space_type, ventilation_rate_area FROM level_3_ventilation_62_1_2010 WHERE ventilation_rate_occupant = 0 AND ventilation_rate_area &gt; 0.3</t>
+  </si>
+  <si>
+    <t>SELECT assembly_minimum_visible_transmittance, building_category FROM envelope_requirements_90_1 WHERE template = '90.1-2007' AND climate_zone_set LIKE '%5%' AND intended_surface_type LIKE '%Skylight%' AND building_category LIKE '%Nonresidential%'</t>
+  </si>
+  <si>
+    <t>SELECT equipment_type, minimum_performance_btu_per_hr_per_hp FROM hvac_minimum_requirements_heat_rejection_90_1 WHERE template = '90.1-2010' AND minimum_performance_btu_per_hr_per_hp IS NOT NULL</t>
+  </si>
+  <si>
+    <t>SELECT ventilation_primary_space_type, ventilation_secondary_space_type, ventilation_rate_occupant, ventilation_rate_area, occupancy_per_area FROM level_3_ventilation_62_1_2007 WHERE ventilation_primary_space_type LIKE '%Sports%' AND (ventilation_secondary_space_type LIKE '%Spectator%' OR ventilation_secondary_space_type LIKE '%Active Play%')</t>
+  </si>
+  <si>
+    <t>SELECT name, thickness, conductivity, resistance, density FROM support_materials WHERE name LIKE '%Glass fiber batt%' AND name LIKE '%CEC Default%' ORDER BY resistance DESC, thickness</t>
+  </si>
+  <si>
+    <t>SELECT template, climate_zone, under_8000_hours, design_conditions, percent_oa_70_to_80, percent_oa_greater_than_80 FROM system_requirements_energy_recovery_90_1 WHERE percent_oa_greater_than_80 IS NOT NULL AND percent_oa_greater_than_80 &lt; 5000</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%3%' OR climate_zone_set LIKE '%4%') AND intended_surface_type LIKE '%Wall' AND assembly_maximum_u_value &lt; 0.1</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, building_category, assembly_maximum_u_value FROM envelope_requirements_IECC WHERE template = 'IECC-2012' AND climate_zone_set LIKE '%3%' AND (intended_surface_type LIKE '%Wall%' OR intended_surface_type LIKE '%Roof%') AND building_category = 'Residential'</t>
+  </si>
+  <si>
+    <t>SELECT template, climate_zone, data_center, fixed_dry_bulb_is_allowed, differential_dry_bulb_is_allowed, electronic_enthalpy_is_allowed, differential_enthalpy_is_allowed, dew_point_dry_bulb_is_allowed, heat_recovery_exempted FROM system_requirements_air_economizer_90_1 WHERE template = '90.1-2010' AND climate_zone LIKE '%4A%' OR climate_zone LIKE '%5A%'</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%4%' OR climate_zone_set LIKE '%5%') AND intended_surface_type LIKE '%Roof%' ORDER BY climate_zone_set</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type, lighting_secondary_space_type, automatic_full_off, scheduled_shutoff FROM level_3_lighting_90_1_2013 WHERE (lighting_primary_space_type LIKE '%Visually Impaired%' OR lighting_secondary_space_type LIKE '%visually impaired%') ORDER BY lighting_primary_space_type</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type, lighting_secondary_space_type, method, lighting_power_density FROM level_3_lighting_90_1_2004 WHERE lighting_primary_space_type LIKE '%Office%' AND method IN ('CS', 'SS') ORDER BY lighting_primary_space_type, method</t>
+  </si>
+  <si>
+    <t>SELECT space_type_name, electric_equipment_space_type_name, ventilation_space_type_name FROM level_1_space_types WHERE electric_equipment_space_type_name IN (SELECT electric_equipment_space_type_name FROM level_1_space_types GROUP BY electric_equipment_space_type_name HAVING COUNT(*) &gt; 1) ORDER BY electric_equipment_space_type_name</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE climate_zone_set LIKE '%7%' AND intended_surface_type LIKE '%Wall%' UNION SELECT id, template, climate_zone_set, intended_surface_type, assembly_maximum_u_value FROM envelope_requirements_IECC WHERE climate_zone_set LIKE '%7%' AND intended_surface_type LIKE '%Wall%' ORDER BY climate_zone_set</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type, lighting_secondary_space_type, lighting_power_density, automatic_full_off, scheduled_shutoff FROM level_3_lighting_90_1_2022 WHERE (lighting_primary_space_type LIKE '%Visually Impaired%' OR lighting_secondary_space_type LIKE '%visually impaired%') ORDER BY lighting_primary_space_type</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, assembly_maximum_u_value FROM envelope_requirements_IECC WHERE (climate_zone_set LIKE '%4%' OR climate_zone_set LIKE '%5%') AND intended_surface_type LIKE '%Floor%' ORDER BY climate_zone_set</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, building_category, construction, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%3%' OR climate_zone_set LIKE '%4%') AND intended_surface_type LIKE '%Wall'</t>
+  </si>
+  <si>
+    <t>SELECT ventilation_primary_space_type, ventilation_secondary_space_type, air_class, ventilation_rate_occupant, ventilation_rate_area, occupancy_per_area, annotation FROM level_3_ventilation_62_1_2004 WHERE air_class IN (1, 2) ORDER BY ventilation_rate_area DESC</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, building_category, construction, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE climate_zone_set LIKE '%5%' AND intended_surface_type LIKE '%Roof'</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type, lighting_secondary_space_type, lighting_power_density, rcr_threshold, automatic_partial_off, annotation FROM level_3_lighting_90_1_2013 WHERE automatic_partial_off = 'REQ' AND rcr_threshold &lt;= 4</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type, lighting_secondary_space_type, lighting_power_density, automatic_full_off, scheduled_shutoff, rcr_threshold, annotation FROM level_3_lighting_90_1_2022 WHERE lighting_primary_space_type LIKE '%Visually Impaired%' OR lighting_primary_space_type IN ('Conference/Meeting/Multipurpose Rooms', 'Dining Area') ORDER BY lighting_power_density DESC</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, building_category, construction, assembly_maximum_u_value FROM envelope_requirements_IECC WHERE (climate_zone_set LIKE '%6%' OR climate_zone_set LIKE '%7%') AND intended_surface_type LIKE '%Wall'</t>
+  </si>
+  <si>
+    <t>SELECT template, climate_zone_set, intended_surface_type, assembly_maximum_u_value, assembly_maximum_u_value_unit FROM envelope_requirements_90_1 WHERE (template = '90.1-2010' OR template = 'IECC-2021') AND climate_zone_set LIKE '%6%' AND intended_surface_type LIKE '%Roof'</t>
+  </si>
+  <si>
+    <t>SELECT climate_zone_set, intended_surface_type, assembly_maximum_u_value, assembly_minimum_visible_transmittance FROM envelope_requirements_90_1 WHERE intended_surface_type LIKE '%Roof%' AND assembly_maximum_u_value &gt; 0.05 ORDER BY assembly_maximum_u_value DESC</t>
+  </si>
+  <si>
+    <t>SELECT template, climate_zone_set, intended_surface_type, assembly_maximum_solar_heat_gain_coefficient FROM envelope_requirements_IECC WHERE (climate_zone_set LIKE '%4A%' OR climate_zone_set LIKE '%5A%') AND intended_surface_type LIKE '%Window%'</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type, lighting_power_density, automatic_daylight_responsive_controls_for_sidelighting FROM level_3_lighting_90_1_2013 WHERE lighting_power_density &gt; 1.5 AND automatic_daylight_responsive_controls_for_sidelighting = 'REQ' ORDER BY lighting_power_density DESC</t>
+  </si>
+  <si>
+    <t>SELECT ventilation_primary_space_type, occupancy_per_area, ventilation_rate_occupant FROM level_3_ventilation_62_1_2007 WHERE occupancy_per_area &gt; 100 AND ventilation_rate_occupant &gt; 5 ORDER BY occupancy_per_area DESC</t>
+  </si>
+  <si>
+    <t>SELECT template, climate_zone_set, intended_surface_type, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%2A%' OR climate_zone_set LIKE '%3A%') AND intended_surface_type LIKE '%Floor%'</t>
+  </si>
+  <si>
+    <t>SELECT template, climate_zone_set, intended_surface_type, assembly_minimum_visible_transmittance FROM envelope_requirements_IECC WHERE (climate_zone_set LIKE '%4A%' OR climate_zone_set LIKE '%5A%') AND intended_surface_type LIKE '%Skylight%'</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type, lighting_power_density, annotation FROM level_3_lighting_90_1_2010 WHERE lighting_power_density &gt; 1.5 ORDER BY lighting_power_density DESC</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, assembly_maximum_u_value, annotation FROM envelope_requirements_IECC WHERE (climate_zone_set LIKE '%7%' OR climate_zone_set LIKE '%8%') AND intended_surface_type LIKE '%Roof'</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, assembly_maximum_solar_heat_gain_coefficient, orientation FROM envelope_requirements_90_1 WHERE template = '90.1-2010' AND intended_surface_type LIKE '%Window%'</t>
+  </si>
+  <si>
+    <t>SELECT fluid_type, minimum_annual_fuel_utilization_efficiency, start_date, end_date FROM hvac_minimum_requirements_boilers_90_1 WHERE template = '90.1-2025' ORDER BY minimum_annual_fuel_utilization_efficiency DESC</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type, lighting_power_density, automatic_full_off, scheduled_shutoff FROM level_3_lighting_IECC_2006 WHERE lighting_primary_space_type IN ('Office', 'Computer Lab') ORDER BY lighting_power_density DESC</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, assembly_maximum_u_value FROM envelope_requirements_IECC WHERE (climate_zone_set LIKE '%3%' OR climate_zone_set LIKE '%4%') AND intended_surface_type LIKE '%Floor'</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, building_category FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%4%' OR climate_zone_set LIKE '%5%') AND intended_surface_type LIKE '%Wall%'</t>
+  </si>
+  <si>
+    <t>SELECT name, conductivity, density, annotation FROM support_materials WHERE name LIKE '%Insulation%' ORDER BY conductivity DESC, density</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type FROM envelope_requirements_IECC WHERE (climate_zone_set LIKE '%6%' OR climate_zone_set LIKE '%7%') AND intended_surface_type LIKE '%Roof%'</t>
+  </si>
+  <si>
+    <t>SELECT id, lighting_space_type_name, level_3_lighting_code_definition_table, lighting_technology_name, lighting_space_type_target_illuminance_setpoint FROM level_2_lighting_space_types WHERE lighting_space_type_name LIKE '%Office%' ORDER BY lighting_space_type_target_illuminance_setpoint DESC</t>
+  </si>
+  <si>
+    <t>SELECT name, intended_surface_type, standards_construction_type, insulation_layer FROM support_constructions WHERE (intended_surface_type LIKE '%Wall%') AND (insulation_layer LIKE '%Insulation%')</t>
+  </si>
+  <si>
+    <t>SELECT template, climate_zone_set, intended_surface_type, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%4%' OR climate_zone_set LIKE '%5%') AND intended_surface_type LIKE '%Wall%' AND template = '90.1-2010'</t>
+  </si>
+  <si>
+    <t>SELECT template, climate_zone_set, intended_surface_type, assembly_maximum_solar_heat_gain_coefficient FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%3%' OR climate_zone_set LIKE '%6%') AND intended_surface_type LIKE '%Skylight%' AND template = '90.1-2016'</t>
+  </si>
+  <si>
+    <t>SELECT template, climate_zone_set, intended_surface_type, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%2%' OR climate_zone_set LIKE '%8%') AND intended_surface_type LIKE '%Wall%' AND (template = '90.1-2010' OR template = 'IECC-2009')</t>
+  </si>
+  <si>
+    <t>SELECT template, climate_zone_set, intended_surface_type, assembly_maximum_c_factor FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%5%' OR climate_zone_set LIKE '%7%') AND intended_surface_type LIKE '%Roof%' AND template = '90.1-2013'</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, building_category, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE template = '90.1-2004' AND climate_zone_set LIKE '%3A%' AND building_category = 'Residential'</t>
+  </si>
+  <si>
+    <t>SELECT id, space_type_name, lighting_space_type_name FROM level_1_space_types WHERE lighting_space_type_name IS NOT NULL ORDER BY lighting_space_type_name DESC</t>
+  </si>
+  <si>
+    <t>SELECT template, number_of_poles, minimum_capacity, maximum_capacity, nominal_full_load_efficiency FROM hvac_minimum_requirements_motors_90_1 WHERE (template = '90.1-2007' OR template LIKE '%IECC%') AND number_of_poles = 2 AND minimum_capacity &gt; 10 ORDER BY template, minimum_capacity</t>
+  </si>
+  <si>
+    <t>SELECT assembly_maximum_solar_heat_gain_coefficient FROM envelope_requirements_IECC WHERE climate_zone_set LIKE '%6%' AND intended_surface_type LIKE '%Skylight%'</t>
+  </si>
+  <si>
+    <t>SELECT template, equipment_type, rating_condition, minimum_coefficient_of_performance_heating FROM hvac_minimum_requirements_heat_pumps_heating_90_1 WHERE rating_condition = '17F db/15F wb outdoor air' UNION SELECT template, equipment_type, rating_condition, minimum_coefficient_of_performance_heating FROM hvac_minimum_requirements_heat_pumps_heating_IECC</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, assembly_maximum_u_value FROM envelope_requirements_IECC WHERE (climate_zone_set LIKE '%7%' OR climate_zone_set LIKE '%8%') AND intended_surface_type LIKE '%Roof' ORDER BY assembly_maximum_u_value DESC</t>
+  </si>
+  <si>
+    <t>SELECT template, cooling_type, standard_model, rating_condition, minimum_capacity, maximum_capacity, minimum_scop FROM hvac_minimum_requirements_computer_room_air_conditioners_90_1 WHERE cooling_type LIKE '%WaterCooled%' AND (template LIKE '%2010%' OR template LIKE '%2013%' OR template LIKE '%2016%') ORDER BY minimum_scop DESC</t>
+  </si>
+  <si>
+    <t>SELECT intended_surface_type, standards_construction_type, building_category, construction, assembly_maximum_u_value, assembly_maximum_solar_heat_gain_coefficient FROM envelope_requirements_90_1 WHERE (intended_surface_type LIKE '%Wall%') AND (template LIKE '%2016%' OR template LIKE '%IECC%') ORDER BY assembly_maximum_u_value DESC</t>
+  </si>
+  <si>
+    <t>SELECT intended_surface_type, standards_construction_type, building_category, construction, assembly_maximum_u_value, assembly_maximum_solar_heat_gain_coefficient FROM envelope_requirements_90_1 WHERE (intended_surface_type LIKE '%Wall%' OR intended_surface_type LIKE '%Roof%') AND (template LIKE '%2016%' OR template LIKE '%IECC%') ORDER BY assembly_maximum_u_value DESC</t>
+  </si>
+  <si>
+    <t>SELECT template, equipment_type, cooling_type, heating_type, subcategory, minimum_capacity, maximum_capacity, minimum_energy_efficiency_ratio AS eer, minimum_integrated_energy_efficiency_ratio AS ieer FROM hvac_minimum_requirements_unitary_air_conditioners_90_1 WHERE equipment_type = 'Air Conditioners' AND (cooling_type LIKE '%AirCooled%' OR cooling_type LIKE '%WaterCooled%') AND minimum_capacity &gt;= 120000 AND maximum_capacity &lt;= 240000 AND start_date &gt; '2015-01-01'</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, building_category, construction, assembly_maximum_u_value, assembly_maximum_solar_heat_gain_coefficient FROM envelope_requirements_IECC WHERE (climate_zone_set LIKE '%4%' OR climate_zone_set LIKE '%5%') AND intended_surface_type LIKE '%Roof%'</t>
+  </si>
+  <si>
+    <t>SELECT template, equipment_type, fan_type, test_fluid, minimum_performance_btu_per_hr_per_hp FROM hvac_minimum_requirements_heat_rejection_90_1 WHERE equipment_type IN ('Evaporative Condenser', 'AirCooled Condenser') AND fan_type = 'Propeller or Axial' ORDER BY equipment_type</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%4%' OR climate_zone_set LIKE '%5%') AND intended_surface_type LIKE '%Wall'</t>
+  </si>
+  <si>
+    <t>SELECT fluid_type, minimum_annual_fuel_utilization_efficiency, minimum_thermal_efficiency, start_date, end_date FROM hvac_minimum_requirements_boilers_IECC WHERE fuel_type = 'NaturalGas' AND minimum_capacity &lt;= 400000 AND maximum_capacity &gt;= 200000</t>
+  </si>
+  <si>
+    <t>SELECT standards_construction_type, assembly_maximum_solar_heat_gain_coefficient FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%6%' OR climate_zone_set LIKE '%7%') AND intended_surface_type LIKE '%Roof' ORDER BY assembly_maximum_solar_heat_gain_coefficient DESC</t>
+  </si>
+  <si>
+    <t>SELECT template, number_of_poles, synchronous_speed, type, minimum_capacity, maximum_capacity, nominal_full_load_efficiency FROM hvac_minimum_requirements_motors_90_1 WHERE minimum_capacity &lt;= 30 AND maximum_capacity &gt;= 20 AND number_of_poles = 2</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%4%' OR climate_zone_set LIKE '%5%') AND template = '90.1-2016' AND intended_surface_type LIKE '%Wall'</t>
+  </si>
+  <si>
+    <t>SELECT template, equipment_type, subcategory, minimum_capacity, maximum_capacity, minimum_energy_efficiency_ratio FROM hvac_minimum_requirements_variable_refrigerant_flow_systems_IECC WHERE (equipment_type = 'GroundSourceCoolingMode' OR equipment_type = 'WaterSourceCoolingMode') AND minimum_capacity &gt; 0</t>
+  </si>
+  <si>
+    <t>SELECT template, equipment_type, fan_type, test_fluid, minimum_performance_btu_per_hr_per_hp FROM hvac_minimum_requirements_heat_rejection_IECC WHERE equipment_type = 'Evaporative Condenser' AND fan_type = 'Propeller or Axial'</t>
+  </si>
+  <si>
+    <t>SELECT template, equipment_type, subcategory, minimum_capacity, maximum_capacity, minimum_energy_efficiency_ratio FROM hvac_minimum_requirements_variable_refrigerant_flow_systems_90_1 WHERE minimum_energy_efficiency_ratio &gt;= 10 AND template = '90.1-2022'</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%4%' OR climate_zone_set LIKE '%5%' OR climate_zone_set LIKE '%6%') AND intended_surface_type LIKE '%Roof%'</t>
+  </si>
+  <si>
+    <t>SELECT template, equipment_type, cooling_type, minimum_capacity, maximum_capacity, minimum_energy_efficiency_ratio FROM hvac_minimum_requirements_unitary_air_conditioners_90_1 WHERE (template = '90.1-2010' OR template LIKE '%IECC%') AND equipment_type = 'Condensing Units' AND cooling_type = 'AirCooled'</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%7%' OR climate_zone_set LIKE '%8%') AND intended_surface_type LIKE '%Wall%' AND template = '90.1-2013'</t>
+  </si>
+  <si>
+    <t>SELECT template, equipment_type, rating_condition, minimum_capacity, maximum_capacity, minimum_coefficient_of_performance_heating FROM hvac_minimum_requirements_heat_pumps_heating_90_1 WHERE rating_condition = '17F db/15F wb outdoor air' AND minimum_capacity &gt;= 135000 AND equipment_type = 'Heat Pumps'</t>
+  </si>
+  <si>
+    <t>SELECT id, ventilation_primary_space_type, ventilation_rate_occupant, ventilation_rate_area, occupancy_per_area FROM level_3_ventilation_62_1_1999 WHERE ventilation_primary_space_type LIKE '%Education%'</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, assembly_maximum_u_value FROM envelope_requirements_IECC WHERE (climate_zone_set LIKE '%4%' OR climate_zone_set LIKE '%5%' OR climate_zone_set LIKE '%6%') AND intended_surface_type LIKE '%Floor%'</t>
+  </si>
+  <si>
+    <t>SELECT id, ventilation_primary_space_type, ventilation_rate_occupant, ventilation_rate_area, occupancy_per_area FROM level_3_ventilation_62_1_1999 WHERE ventilation_primary_space_type LIKE '%Office%'</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%4%' OR climate_zone_set LIKE '%5%' OR climate_zone_set LIKE '%6%') AND intended_surface_type LIKE '%Roof%' AND template = '90.1-2010'</t>
+  </si>
+  <si>
+    <t>SELECT assembly_maximum_u_value, assembly_maximum_u_value_unit, climate_zone_set FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%4%' OR climate_zone_set LIKE '%5%') AND intended_surface_type LIKE '%Wall'</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type, lighting_power_density, automatic_daylight_responsive_controls_for_sidelighting FROM level_3_lighting_90_1_2010_prm WHERE lighting_power_density &gt; 1.2 AND automatic_daylight_responsive_controls_for_sidelighting = 'REQ'</t>
+  </si>
+  <si>
+    <t>SELECT template, equipment_type, region, minimum_seasonal_energy_efficiency_ratio FROM hvac_minimum_requirements_heat_pumps_cooling_IECC WHERE region = 'Southeastern' AND equipment_type LIKE '%Heat Pump%'</t>
+  </si>
+  <si>
+    <t>SELECT assembly_maximum_solar_heat_gain_coefficient, climate_zone_set FROM envelope_requirements_IECC WHERE (climate_zone_set LIKE '%6%' OR climate_zone_set LIKE '%7%') AND intended_surface_type LIKE '%Window'</t>
+  </si>
+  <si>
+    <t>SELECT assembly_maximum_u_value, assembly_maximum_u_value_unit, climate_zone_set FROM envelope_requirements_90_1_prm WHERE (climate_zone_set LIKE '%3%' OR climate_zone_set LIKE '%4%') AND intended_surface_type LIKE '%Floor'</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type, lighting_secondary_space_type, method, lighting_power_density, rcr_threshold, automatic_full_off FROM level_3_lighting_90_1_2010_prm WHERE (lighting_primary_space_type LIKE '%Office%' OR lighting_secondary_space_type LIKE '%Retail%') AND lighting_power_density &gt; 0.5 AND automatic_full_off = 'REQ' ORDER BY lighting_power_density DESC</t>
+  </si>
+  <si>
+    <t>SELECT intended_surface_type, standards_construction_type, building_category, construction, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%4%' OR climate_zone_set LIKE '%5%' OR climate_zone_set LIKE '%6%') AND intended_surface_type LIKE '%Wall' ORDER BY assembly_maximum_u_value DESC</t>
+  </si>
+  <si>
+    <t>SELECT intended_surface_type, standards_construction_type, building_category, construction, assembly_maximum_solar_heat_gain_coefficient FROM envelope_requirements_IECC WHERE (climate_zone_set LIKE '%6%' OR climate_zone_set LIKE '%7%' OR climate_zone_set LIKE '%8%') AND intended_surface_type LIKE '%Window' ORDER BY assembly_maximum_solar_heat_gain_coefficient DESC</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, building_category, construction FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%4%' OR climate_zone_set LIKE '%5%') AND intended_surface_type LIKE '%Wall%'</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type, lighting_secondary_space_type, lighting_power_density, rcr_threshold, automatic_partial_off FROM level_3_lighting_90_1_2019 WHERE automatic_partial_off = 'REQ' ORDER BY lighting_power_density DESC</t>
+  </si>
+  <si>
+    <t>SELECT ventilation_primary_space_type, ventilation_secondary_space_type, ventilation_rate_occupant, ventilation_rate_area, occupancy_per_area FROM level_3_ventilation_62_1_2004 WHERE ventilation_primary_space_type LIKE '%Food%'</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type FROM envelope_requirements_90_1 WHERE intended_surface_type LIKE '%Roof%' UNION SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type FROM envelope_requirements_IECC WHERE intended_surface_type LIKE '%Roof%'</t>
+  </si>
+  <si>
+    <t>SELECT template, climate_zone, under_8000_hours, design_conditions, percent_oa_70_to_80, percent_oa_greater_than_80 FROM system_requirements_energy_recovery_90_1 WHERE percent_oa_greater_than_80 IS NOT NULL ORDER BY percent_oa_greater_than_80</t>
+  </si>
+  <si>
+    <t>SELECT name, intended_surface_type, standards_construction_type FROM support_constructions WHERE intended_surface_type LIKE '%Wall%'</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type, lighting_secondary_space_type, lighting_power_density, rcr_threshold, automatic_daylight_responsive_controls_for_sidelighting FROM level_3_lighting_90_1_2022 WHERE rcr_threshold &lt;= 4 AND automatic_daylight_responsive_controls_for_sidelighting = 'REQ'</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type FROM envelope_requirements_90_1 WHERE intended_surface_type LIKE '%Floor%' UNION SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type FROM envelope_requirements_IECC WHERE intended_surface_type LIKE '%Floor%'</t>
+  </si>
+  <si>
+    <t>SELECT template, climate_zone, data_center, fixed_dry_bulb_high_limit_shutoff_temp FROM system_requirements_air_economizer_90_1 WHERE climate_zone LIKE '%3A%'</t>
+  </si>
+  <si>
+    <t>SELECT ventilation_primary_space_type, ventilation_secondary_space_type, ventilation_rate_occupant FROM level_3_ventilation_62_1_2004 ORDER BY ventilation_rate_occupant DESC</t>
+  </si>
+  <si>
+    <t>SELECT template, equipment_type, subcategory, minimum_capacity, maximum_capacity, minimum_energy_efficiency_ratio, annotation FROM hvac_minimum_requirements_variable_refrigerant_flow_systems_90_1 WHERE equipment_type LIKE '%GroundSource%' AND template IN ('90.1-2016', '90.1-2019', '90.1-2022', '90.1-2025')</t>
+  </si>
+  <si>
+    <t>SELECT ventilation_primary_space_type, ventilation_secondary_space_type, ventilation_rate_occupant, ventilation_rate_area, occupancy_per_area, air_class, annotation FROM level_3_ventilation_62_1_2004 WHERE ventilation_primary_space_type LIKE '%Food%' ORDER BY ventilation_rate_occupant DESC</t>
+  </si>
+  <si>
+    <t>SELECT template, climate_zone_set, intended_surface_type, assembly_maximum_u_value, annotation FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%4%' OR climate_zone_set LIKE '%5%') AND intended_surface_type LIKE '%Wall%' AND template = '90.1-2019'</t>
+  </si>
+  <si>
+    <t>SELECT lighting_space_type_name, level_3_lighting_code_definition_table, lighting_space_type_target_illuminance_setpoint, annotation FROM level_2_lighting_space_types WHERE lighting_space_type_name LIKE '%Office%' ORDER BY lighting_space_type_target_illuminance_setpoint DESC</t>
+  </si>
+  <si>
+    <t>SELECT template, cooling_type, compressor_type, minimum_capacity, maximum_capacity, start_date, end_date, minimum_integrated_part_load_value, annotation FROM hvac_minimum_requirements_chillers_IECC WHERE cooling_type LIKE '%AirCooled%' AND template IN ('IECC-2012', 'IECC-2015', 'IECC-2018')</t>
+  </si>
+  <si>
+    <t>SELECT template, climate_zone_set, intended_surface_type, assembly_maximum_u_value, annotation FROM envelope_requirements_IECC WHERE building_category LIKE '%Residential%' AND (template = 'IECC-2009' OR template = 'IECC-2012') ORDER BY assembly_maximum_u_value</t>
+  </si>
+  <si>
+    <t>SELECT DISTINCT allowance_type FROM exterior_lighting_90_1 WHERE template IN ('90.1-2016', '90.1-2019', '90.1-2022', '90.1-2025') ORDER BY allowance_type</t>
+  </si>
+  <si>
+    <t>SELECT building_category, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE template LIKE '%2022%' ORDER BY assembly_maximum_u_value ASC LIMIT 10</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, assembly_maximum_solar_heat_gain_coefficient FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%7%' OR climate_zone_set LIKE '%8%') AND intended_surface_type LIKE '%Window'</t>
+  </si>
+  <si>
+    <t>SELECT intended_surface_type, assembly_minimum_visible_transmittance FROM envelope_requirements_IECC WHERE intended_surface_type LIKE '%Skylight%'</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, building_category, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE template = '90.1-2013' AND climate_zone_set LIKE '%5%' AND building_category LIKE '%Residential'</t>
+  </si>
+  <si>
+    <t>SELECT standards_construction_type, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE template = '90.1-2016' AND climate_zone_set LIKE '%7%' AND intended_surface_type LIKE '%Wall'</t>
+  </si>
+  <si>
+    <t>SELECT template, climate_zone, under_8000_hours, design_conditions, percent_oa_70_to_80 FROM system_requirements_energy_recovery_90_1 WHERE template = '90.1-2010' AND climate_zone LIKE '%3A%'</t>
+  </si>
+  <si>
+    <t>SELECT equipment_type, subcategory, rating_condition, minimum_coefficient_of_performance_heating FROM hvac_minimum_requirements_heat_pumps_heating_90_1 WHERE template = '90.1-2016' AND equipment_type LIKE '%SPVHP%' ORDER BY minimum_coefficient_of_performance_heating DESC</t>
+  </si>
+  <si>
+    <t>SELECT lighting_zone, allowance_type, allowance, allowance_unit FROM exterior_lighting_90_1 WHERE template LIKE '%90.1-2007%' AND allowance_type LIKE '%parking lot%'</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type, lighting_secondary_space_type, lighting_power_density, automatic_daylight_responsive_controls_for_sidelighting FROM level_3_lighting_90_1_2010 WHERE lighting_power_density &gt;= 1.2 AND automatic_daylight_responsive_controls_for_sidelighting = 'REQ'</t>
+  </si>
+  <si>
+    <t>SELECT ventilation_primary_space_type, ventilation_secondary_space_type, ventilation_rate_occupant, ventilation_rate_area, occupancy_per_area, air_class FROM level_3_ventilation_62_1_2007 WHERE occupancy_per_area &gt; 50 AND ventilation_rate_occupant &gt; 5 ORDER BY occupancy_per_area DESC, ventilation_rate_occupant DESC</t>
+  </si>
+  <si>
+    <t>SELECT template, cooling_type, standard_model, rating_condition, minimum_capacity, maximum_capacity, minimum_scop FROM hvac_minimum_requirements_computer_room_air_conditioners_IECC WHERE cooling_type LIKE '%AirCooled%' AND minimum_capacity &lt;= 100000 AND maximum_capacity &gt;= 100000 AND template = 'IECC-2009' ORDER BY cooling_type, standard_model</t>
+  </si>
+  <si>
+    <t>SELECT DISTINCT allowance_type FROM exterior_lighting_90_1 WHERE template = '90.1-2013' ORDER BY allowance_type</t>
+  </si>
+  <si>
+    <t>SELECT name, thickness, conductivity, resistance, density, specific_heat FROM support_materials WHERE name LIKE '%Glass fiber batt%' AND name LIKE '%CEC Default%' ORDER BY resistance DESC, thickness</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, assembly_minimum_visible_transmittance FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%3%' OR climate_zone_set LIKE '%4%') AND intended_surface_type LIKE '%Skylight'</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, assembly_maximum_solar_heat_gain_coefficient FROM envelope_requirements_IECC WHERE (climate_zone_set LIKE '%5%' OR climate_zone_set LIKE '%6%') AND intended_surface_type LIKE '%Window'</t>
+  </si>
+  <si>
+    <t>SELECT assembly_maximum_u_value, intended_surface_type FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%3%' OR climate_zone_set LIKE '%4%') AND intended_surface_type LIKE '%Wall%'</t>
+  </si>
+  <si>
+    <t>SELECT template, climate_zone, data_center, fixed_dry_bulb_is_allowed FROM system_requirements_air_economizer_90_1 WHERE (climate_zone LIKE '%2A%' OR climate_zone LIKE '%3A%' OR climate_zone LIKE '%4A%') AND template = '90.1-2010'</t>
+  </si>
+  <si>
+    <t>SELECT electric_equipment_space_type_name, electric_equipment_minimum_epd, electric_equipment_maximum_epd FROM level_2_electric_equipment WHERE electric_equipment_maximum_epd &gt; electric_equipment_minimum_epd ORDER BY (electric_equipment_maximum_epd - electric_equipment_minimum_epd) DESC</t>
+  </si>
+  <si>
+    <t>SELECT name, thickness, conductivity, resistance FROM support_materials WHERE name LIKE '%Glass fiber batt%' AND name LIKE '%CEC Default%' AND resistance &gt; 10</t>
+  </si>
+  <si>
+    <t>SELECT intended_surface_type, assembly_maximum_u_value, assembly_maximum_f_factor FROM envelope_requirements_90_1 WHERE intended_surface_type LIKE '%Wall%' AND (climate_zone_set LIKE '%2%' OR climate_zone_set LIKE '%3%' OR climate_zone_set LIKE '%4%')</t>
+  </si>
+  <si>
+    <t>SELECT assembly_maximum_solar_heat_gain_coefficient, intended_surface_type FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%5%' OR climate_zone_set LIKE '%6%') AND intended_surface_type LIKE '%Roof%'</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%4%' OR climate_zone_set LIKE '%5%') AND intended_surface_type LIKE '%Wall%' AND template = '90.1-2010'</t>
+  </si>
+  <si>
+    <t>SELECT equipment_type, cooling_type, minimum_capacity, maximum_capacity, minimum_energy_efficiency_ratio FROM hvac_minimum_requirements_unitary_air_conditioners_90_1 WHERE equipment_type = 'Condensing Units' AND cooling_type = 'AirCooled' AND template IN ('90.1-2004', 'IECC') ORDER BY template</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, assembly_maximum_u_value FROM envelope_requirements_IECC WHERE climate_zone_set LIKE '%7%' AND intended_surface_type LIKE '%Roof%'</t>
+  </si>
+  <si>
+    <t>SELECT template, equipment_type, rating_condition, minimum_capacity, maximum_capacity, minimum_coefficient_of_performance_heating FROM hvac_minimum_requirements_heat_pumps_heating_90_1 WHERE rating_condition = '17F db/15F wb outdoor air' AND equipment_type = 'Heat Pumps' ORDER BY template</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE template = '90.1-2007' AND intended_surface_type LIKE '%Floor%'</t>
+  </si>
+  <si>
+    <t>SELECT equipment_type, cooling_type, minimum_capacity, maximum_capacity, minimum_energy_efficiency_ratio FROM hvac_minimum_requirements_unitary_air_conditioners_90_1 WHERE equipment_type = 'Condensing Units' AND cooling_type = 'WaterCooled' AND template IN ('90.1-2013', 'IECC') ORDER BY template</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%4%' OR climate_zone_set LIKE '%5%' OR climate_zone_set LIKE '%6%') AND intended_surface_type LIKE '%Wall'</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, assembly_maximum_u_value FROM envelope_requirements_IECC WHERE (climate_zone_set LIKE '%7%' OR climate_zone_set LIKE '%8%') AND intended_surface_type LIKE '%Roof'</t>
+  </si>
+  <si>
+    <t>SELECT template, equipment_type, fuel_type, minimum_annual_fuel_utilization_efficiency, minimum_thermal_efficiency FROM hvac_minimum_requirements_furnaces_90_1 WHERE fuel_type = 'Oil' AND minimum_capacity &lt;= 200000 AND maximum_capacity &gt;= 100000 UNION SELECT template, equipment_type, fuel_type, minimum_annual_fuel_utilization_efficiency, minimum_thermal_efficiency FROM hvac_minimum_requirements_furnaces_IECC WHERE fuel_type = 'Oil' AND minimum_capacity &lt;= 200000 AND maximum_capacity &gt;= 100000</t>
+  </si>
+  <si>
+    <t>SELECT ventilation_primary_space_type, ventilation_secondary_space_type, ventilation_rate_occupant, ventilation_rate_area, occupancy_per_area, air_class, annotation FROM level_3_ventilation_62_1_2007 WHERE occupancy_per_area &gt; 100 AND ventilation_rate_occupant &gt; 5 ORDER BY occupancy_per_area DESC, ventilation_rate_occupant DESC;</t>
+  </si>
+  <si>
+    <t>SELECT template, number_of_poles, synchronous_speed, type, minimum_capacity, maximum_capacity, nominal_full_load_efficiency, start_date, annotation FROM hvac_minimum_requirements_motors_90_1 WHERE minimum_capacity &lt;= 40 AND maximum_capacity &gt;= 30 AND number_of_poles IN (2) AND type = 'Enclosed' ORDER BY template, minimum_capacity;</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, building_category, construction, minimum_percent_of_surface, maximum_percent_of_surface, assembly_maximum_u_value, annotation FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%4%' OR climate_zone_set LIKE '%5%' OR climate_zone_set LIKE '%6%') AND intended_surface_type LIKE '%Roof%' AND template = '90.1-2019';</t>
+  </si>
+  <si>
+    <t>SELECT template, climate_zone, design_conditions, percent_oa_30_to_40, percent_oa_40_to_50, percent_oa_50_to_60, percent_oa_60_to_70, percent_oa_70_to_80, percent_oa_greater_than_80, energy_recovery_effectiveness, CASE WHEN climate_zone LIKE '%A' THEN 'Humid' WHEN climate_zone LIKE '%B' THEN 'Dry' ELSE 'Other' END as moisture_regime, annotation FROM system_requirements_energy_recovery_IECC WHERE template = 'IECC-2015' AND climate_zone IN ('1A', '1B', '2A', '2B', '3A', '3B') ORDER BY moisture_regime, climate_zone, design_conditions;</t>
+  </si>
+  <si>
+    <t>SELECT id, template, intended_surface_type, standards_construction_type, building_category, construction, minimum_percent_of_surface, maximum_percent_of_surface, assembly_maximum_u_value, assembly_minimum_visible_transmittance, assembly_minimum_vt_shgc, annotation FROM envelope_requirements_90_1 WHERE intended_surface_type LIKE '%Window%' AND template = '90.1-2016' ORDER BY assembly_minimum_vt_shgc DESC;</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, building_category, assembly_maximum_u_value, annotation FROM envelope_requirements_90_1 WHERE template = '90.1-2013' AND climate_zone_set LIKE '%4%' AND intended_surface_type LIKE '%Wall%' AND standards_construction_type = 'Mass' AND building_category = 'Residential'</t>
+  </si>
+  <si>
+    <t>SELECT template, cooling_type, standard_model, rating_condition, minimum_capacity, maximum_capacity, minimum_scop, annotation FROM hvac_minimum_requirements_computer_room_air_conditioners_90_1 WHERE cooling_type LIKE '%WaterCooled%' AND minimum_capacity &gt;= 100000 AND template = '90.1-2004'</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%4%' OR climate_zone_set LIKE '%5%') AND intended_surface_type LIKE '%Wall%' ORDER BY assembly_maximum_u_value</t>
+  </si>
+  <si>
+    <t>SELECT climate_zone_set, intended_surface_type, assembly_maximum_u_value, minimum_projection_factor FROM envelope_requirements_IECC WHERE intended_surface_type LIKE '%Skylight%' ORDER BY minimum_projection_factor DESC</t>
+  </si>
+  <si>
+    <t>SELECT ventilation_space_type_name, level_3_ventilation_definition_table, level_3_ventilation_definition_id FROM level_2_ventilation_space_types WHERE ventilation_space_type_name LIKE '%Office%' ORDER BY level_3_ventilation_definition_table</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%6%' OR climate_zone_set LIKE '%7%') AND intended_surface_type LIKE '%Floor%' ORDER BY assembly_maximum_u_value</t>
+  </si>
+  <si>
+    <t>SELECT natural_gas_equipment_space_type_name, natural_gas_equipment_average_epd, natural_gas_equipment_median_epd, natural_gas_equipment_fraction_latent, natural_gas_equipment_fraction_radiant FROM level_2_natural_gas_equipment WHERE natural_gas_equipment_average_epd &gt; 10 AND natural_gas_equipment_fraction_latent &gt; 0 ORDER BY natural_gas_equipment_average_epd DESC</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, building_category, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%4%' OR climate_zone_set LIKE '%5%') AND intended_surface_type LIKE '%Wall%'</t>
+  </si>
+  <si>
+    <t>SELECT name, material_type, thickness, resistance, (resistance / thickness) as resistance_per_inch, density FROM support_materials WHERE material_type LIKE '%StandardOpaqueMaterial%' AND resistance &gt; 20 AND thickness &gt; 0 AND density &lt; 1.5 ORDER BY resistance_per_inch DESC</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, building_category, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE template LIKE '%90.1-2007%' AND intended_surface_type LIKE '%Roof%' AND assembly_maximum_u_value &lt;= 0.05</t>
+  </si>
+  <si>
+    <t>SELECT id, lighting_space_type_name, level_3_lighting_code_definition_table, level_3_lighting_code_definition_id, lighting_technology_name, lighting_space_type_target_illuminance_setpoint FROM level_2_lighting_space_types WHERE lighting_space_type_target_illuminance_setpoint &gt; 30</t>
+  </si>
+  <si>
+    <t>SELECT id, space_type_name, lighting_space_type_name, ventilation_space_type_name FROM level_1_space_types WHERE electric_equipment_space_type_name IS NOT NULL AND ventilation_space_type_name LIKE '%Office%'</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type, lighting_secondary_space_type, supplemental_lighting_power_density, automatic_full_off FROM level_3_lighting_90_1_2019 WHERE supplemental_lighting_power_density IS NOT NULL OR automatic_full_off IS NOT NULL</t>
+  </si>
+  <si>
+    <t>SELECT template, climate_zone, data_center, fixed_dry_bulb_high_limit_shutoff_temp, fixed_enthalpy_high_limit_shutoff_enthalpy FROM system_requirements_air_economizer_90_1 WHERE template = '90.1-2010' AND climate_zone LIKE '%4%'</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, assembly_maximum_u_value FROM envelope_requirements_IECC WHERE intended_surface_type LIKE '%Roof%' ORDER BY assembly_maximum_u_value DESC</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type, lighting_power_density, automatic_full_off FROM level_3_lighting_90_1_2019 WHERE (lighting_primary_space_type LIKE '%Laboratory%' OR lighting_primary_space_type LIKE '%Healthcare%') ORDER BY lighting_power_density DESC</t>
+  </si>
+  <si>
+    <t>SELECT template, equipment_type, fan_type, test_fluid, minimum_performance_btu_per_hr_per_hp FROM hvac_minimum_requirements_heat_rejection_90_1 WHERE equipment_type = 'Evaporative Condenser' AND test_fluid = 'R-448A'</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, assembly_maximum_u_value FROM envelope_requirements_IECC WHERE (climate_zone_set LIKE '%7%' OR climate_zone_set LIKE '%8%') AND intended_surface_type LIKE '%Wall'</t>
+  </si>
+  <si>
+    <t>SELECT id, template, intended_surface_type, standards_construction_type, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%4%' OR climate_zone_set LIKE '%5%') AND intended_surface_type LIKE '%Wall'</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type, lighting_secondary_space_type, lighting_power_density, supplemental_lighting_power_density FROM level_3_lighting_90_1_2007 WHERE supplemental_lighting_power_density IS NOT NULL OR automatic_full_off IS NOT NULL</t>
+  </si>
+  <si>
+    <t>SELECT ventilation_primary_space_type, ventilation_secondary_space_type, ventilation_rate_occupant, ventilation_rate_area FROM level_3_ventilation_62_1_1999 WHERE ventilation_primary_space_type = 'Education' ORDER BY ventilation_rate_occupant DESC</t>
+  </si>
+  <si>
+    <t>SELECT id, template, intended_surface_type, standards_construction_type, assembly_maximum_u_value FROM envelope_requirements_IECC WHERE building_category LIKE '%Residential%' OR building_category LIKE '%Commercial'</t>
+  </si>
+  <si>
+    <t>SELECT ventilation_primary_space_type, ventilation_secondary_space_type, air_class, ventilation_rate_occupant FROM level_3_ventilation_62_1_2004 WHERE air_class = 2 ORDER BY ventilation_rate_occupant DESC</t>
+  </si>
+  <si>
+    <t>SELECT id, template, intended_surface_type, standards_construction_type, assembly_maximum_f_factor FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%6%' OR climate_zone_set LIKE '%7%') AND intended_surface_type LIKE '%Roof'</t>
+  </si>
+  <si>
+    <t>SELECT id, lighting_space_type_name, lighting_technology_name, lighting_space_type_target_illuminance_setpoint FROM level_2_lighting_space_types ORDER BY lighting_space_type_target_illuminance_setpoint DESC</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%4%' OR climate_zone_set LIKE '%5%' OR climate_zone_set LIKE '%6%') AND intended_surface_type LIKE '%Wall%' AND template = '90.1-2010'</t>
+  </si>
+  <si>
+    <t>SELECT ventilation_space_type_name, COUNT(*) AS count FROM level_1_space_types WHERE electric_equipment_space_type_name IS NOT NULL GROUP BY ventilation_space_type_name ORDER BY count DESC</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%7%' OR climate_zone_set LIKE '%8%') AND intended_surface_type LIKE '%Wall%' AND template = '90.1-2016'</t>
+  </si>
+  <si>
+    <t>SELECT assembly_maximum_u_value, assembly_maximum_u_value_unit FROM envelope_requirements_IECC WHERE (climate_zone_set LIKE '%4%') AND intended_surface_type = 'ExteriorWall' AND standards_construction_type = 'Mass' AND building_category = 'Residential'</t>
+  </si>
+  <si>
+    <t>SELECT assembly_maximum_u_value, orientation FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%4%' OR climate_zone_set LIKE '%5%') AND intended_surface_type LIKE '%Wall' ORDER BY assembly_maximum_u_value DESC</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type, lighting_power_density FROM level_3_lighting_90_1_2019 WHERE automatic_daylight_responsive_controls_for_sidelighting = 'REQ' AND lighting_power_density &gt; 2.0 ORDER BY lighting_power_density DESC</t>
+  </si>
+  <si>
+    <t>SELECT name, material_type, thickness, resistance, density FROM support_materials WHERE material_type = 'StandardOpaqueMaterial' AND resistance &gt; 10 ORDER BY resistance DESC</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type, lighting_power_density FROM level_3_lighting_90_1_2019 WHERE automatic_partial_off = 'REQ' AND automatic_daylight_responsive_controls_for_sidelighting = 'REQ' ORDER BY lighting_power_density DESC</t>
+  </si>
+  <si>
+    <t>SELECT template, climate_zone_set, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE intended_surface_type LIKE '%Roof%' AND climate_zone_set LIKE '%7%' ORDER BY assembly_maximum_u_value DESC</t>
+  </si>
+  <si>
+    <t>SELECT assembly_maximum_u_value, assembly_maximum_u_value_unit FROM envelope_requirements_IECC WHERE template = 'IECC-2015' AND climate_zone_set LIKE '%3%' AND intended_surface_type LIKE '%Wall%' AND standards_construction_type = 'Mass' AND building_category = 'Residential'</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type, lighting_secondary_space_type, lighting_power_density, supplemental_lighting_power_density, automatic_full_off, scheduled_shutoff, method, annotation FROM level_3_lighting_90_1_2013 WHERE supplemental_lighting_power_density IS NOT NULL OR automatic_full_off IS NOT NULL OR scheduled_shutoff IS NOT NULL</t>
+  </si>
+  <si>
+    <t>SELECT name, intended_surface_type, standards_construction_type, insulation_layer FROM support_constructions WHERE insulation_layer IS NOT NULL</t>
+  </si>
+  <si>
+    <t>SELECT assembly_maximum_u_value, assembly_maximum_u_value_unit FROM envelope_requirements_IECC WHERE template = 'IECC-2012' AND climate_zone_set LIKE '%4%' AND intended_surface_type LIKE '%Roof%' AND building_category LIKE '%Residential%'</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type, automatic_daylight_responsive_controls_for_sidelighting, automatic_daylight_responsive_controls_for_toplighting, method, annotation FROM level_3_lighting_90_1_2016 WHERE automatic_daylight_responsive_controls_for_sidelighting IS NOT NULL OR automatic_daylight_responsive_controls_for_toplighting IS NOT NULL</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%4%' OR climate_zone_set LIKE '%5%') AND intended_surface_type LIKE '%Wall' ORDER BY assembly_maximum_u_value</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type, lighting_power_density, automatic_daylight_responsive_controls_for_sidelighting FROM level_3_lighting_90_1_2019 WHERE automatic_daylight_responsive_controls_for_sidelighting = 'REQ' ORDER BY lighting_power_density DESC</t>
+  </si>
+  <si>
+    <t>SELECT template, cooling_type, compressor_type, minimum_capacity, maximum_capacity, start_date, end_date, minimum_integrated_part_load_value FROM hvac_minimum_requirements_chillers_IECC WHERE template = 'IECC-2006' AND cooling_type = 'WaterCooled' AND compressor_type = 'Rotary Screw' AND minimum_capacity &lt;= 200 AND maximum_capacity &gt;= 100</t>
+  </si>
+  <si>
+    <t>SELECT ventilation_primary_space_type, ventilation_rate_occupant, ventilation_rate_area FROM level_3_ventilation_62_1_1999 WHERE ventilation_rate_occupant = 0 AND ventilation_rate_area &gt; 0.5 ORDER BY ventilation_rate_area DESC</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, assembly_maximum_solar_heat_gain_coefficient FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%6%' OR climate_zone_set LIKE '%7%') AND intended_surface_type LIKE '%Skylight' ORDER BY assembly_maximum_solar_heat_gain_coefficient</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type, rcr_threshold, automatic_partial_off FROM level_3_lighting_90_1_2019 WHERE automatic_partial_off = 'REQ' AND rcr_threshold &lt;= 4 ORDER BY rcr_threshold</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, assembly_minimum_visible_transmittance FROM envelope_requirements_IECC WHERE (climate_zone_set LIKE '%3%' OR climate_zone_set LIKE '%4%') AND intended_surface_type LIKE '%Window' ORDER BY assembly_minimum_visible_transmittance</t>
+  </si>
+  <si>
+    <t>SELECT equipment_type, subcategory, rating_condition, minimum_coefficient_of_performance_heating FROM hvac_minimum_requirements_heat_pumps_heating_90_1 ORDER BY minimum_coefficient_of_performance_heating DESC</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%5%' OR climate_zone_set LIKE '%6%') AND intended_surface_type LIKE '%Floor' ORDER BY assembly_maximum_u_value</t>
+  </si>
+  <si>
+    <t>SELECT template, equipment_type, cooling_type, heating_type, subcategory, minimum_capacity, maximum_capacity, minimum_energy_efficiency_ratio AS eer, minimum_integrated_energy_efficiency_ratio AS ieer FROM hvac_minimum_requirements_unitary_air_conditioners_90_1 WHERE equipment_type = 'Air Conditioners' AND subcategory = 'Single Package' AND (cooling_type LIKE '%AirCooled%' OR cooling_type LIKE '%WaterCooled%') AND minimum_capacity &lt;= 300000 AND maximum_capacity &gt;= 150000 AND start_date &gt; '2015-01-01'</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type, lighting_secondary_space_type, lighting_power_density, method FROM level_3_lighting_IECC_2006 WHERE (lighting_primary_space_type LIKE '%Retail%' OR lighting_secondary_space_type LIKE '%Store%') ORDER BY lighting_power_density DESC</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, assembly_maximum_solar_heat_gain_coefficient FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%6%' OR climate_zone_set LIKE '%7%') AND intended_surface_type LIKE '%Window'</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, building_category FROM envelope_requirements_IECC WHERE template = 'IECC-2012' AND climate_zone_set LIKE '%4%' AND intended_surface_type LIKE '%Wall%' AND building_category LIKE '%Residential'</t>
+  </si>
+  <si>
+    <t>SELECT template, equipment_type, fuel_type, minimum_annual_fuel_utilization_efficiency FROM hvac_minimum_requirements_furnaces_90_1 WHERE template = '90.1-2016' AND (fuel_type = 'NaturalGas' OR fuel_type = 'Electric')</t>
+  </si>
+  <si>
+    <t>SELECT template, equipment_type, fuel_type, minimum_annual_fuel_utilization_efficiency FROM hvac_minimum_requirements_furnaces_90_1 WHERE template = '90.1-2016' AND equipment_type LIKE '%Furnace%' AND fuel_type = 'NaturalGas' AND (minimum_capacity &lt;= 150000 AND maximum_capacity &gt;= 150000)</t>
+  </si>
+  <si>
+    <t>SELECT template, climate_zone_set, intended_surface_type, standards_construction_type FROM envelope_requirements_IECC WHERE template = 'IECC-2012' AND climate_zone_set LIKE '%4%' AND intended_surface_type LIKE '%Wall%' AND building_category LIKE '%Residential' UNION SELECT template, climate_zone_set, intended_surface_type, standards_construction_type FROM envelope_requirements_90_1 WHERE template = '90.1-2010' AND climate_zone_set LIKE '%4%' AND intended_surface_type LIKE '%Wall%' AND building_category LIKE '%Residential'</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%3%' OR climate_zone_set LIKE '%4%') AND intended_surface_type LIKE '%Wall'</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type, lighting_power_density, method FROM level_3_lighting_IECC_2006 WHERE lighting_primary_space_type LIKE '%Retail%' UNION SELECT lighting_primary_space_type, lighting_power_density, method FROM level_3_lighting_90_1_2010 WHERE lighting_primary_space_type LIKE '%Retail'</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, assembly_maximum_u_value FROM envelope_requirements_IECC WHERE (climate_zone_set LIKE '%5%' OR climate_zone_set LIKE '%6%') AND building_category LIKE '%Residential' AND intended_surface_type LIKE '%Roof'</t>
+  </si>
+  <si>
+    <t>SELECT name, intended_surface_type, standards_construction_type, insulation_layer, material_1, material_2, material_3 FROM support_constructions ORDER BY insulation_layer DESC LIMIT 5</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, assembly_minimum_visible_transmittance FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%1%' OR climate_zone_set LIKE '%2%') AND building_category NOT LIKE '%Residential' AND intended_surface_type LIKE '%Window'</t>
+  </si>
+  <si>
+    <t>SELECT id, space_type_name, lighting_space_type_name, ventilation_space_type_name FROM level_1_space_types ORDER BY lighting_space_type_name DESC LIMIT 5</t>
+  </si>
+  <si>
+    <t>SELECT template, equipment_type, cooling_type, minimum_capacity, maximum_capacity, minimum_energy_efficiency_ratio as eer, minimum_integrated_part_load_value as iplv FROM hvac_minimum_requirements_unitary_air_conditioners_90_1 WHERE template LIKE '%90.1-2010%' AND equipment_type = 'Condensing Units' AND (cooling_type = 'AirCooled' OR cooling_type = 'WaterCooled') AND start_date &gt; '2010-01-01'</t>
+  </si>
+  <si>
+    <t>SELECT intended_surface_type, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE template LIKE '%90.1-2007%' AND (climate_zone_set LIKE '%4%' OR climate_zone_set LIKE '%5%') AND intended_surface_type LIKE '%Roof%'</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type, COUNT(*) as count FROM level_3_lighting_90_1_2022 WHERE rcr_threshold &gt; 6 GROUP BY lighting_primary_space_type ORDER BY count DESC LIMIT 5</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type, method, lighting_power_density FROM level_3_lighting_90_1_2004 WHERE lighting_primary_space_type LIKE '%Office%' UNION ALL SELECT lighting_primary_space_type, method, lighting_power_density FROM level_3_lighting_90_1_2010 WHERE lighting_primary_space_type LIKE '%Office%'</t>
+  </si>
+  <si>
+    <t>SELECT template, number_of_poles, synchronous_speed, type, minimum_capacity, maximum_capacity, nominal_full_load_efficiency FROM hvac_minimum_requirements_motors_90_1 WHERE minimum_capacity &lt;= 30 AND maximum_capacity &gt;= 20 AND number_of_poles IN (2, 4) ORDER BY nominal_full_load_efficiency DESC</t>
+  </si>
+  <si>
+    <t>SELECT assembly_maximum_u_value, assembly_maximum_u_value_unit FROM envelope_requirements_IECC WHERE template = 'IECC-2012' AND climate_zone_set LIKE '%3%' AND intended_surface_type LIKE '%Wall%' AND building_category LIKE '%Residential'</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, building_category, assembly_maximum_u_value FROM envelope_requirements_IECC WHERE template = 'IECC-2009' AND climate_zone_set LIKE '%7%' AND intended_surface_type LIKE '%Roof'</t>
+  </si>
+  <si>
+    <t>SELECT assembly_maximum_u_value, assembly_maximum_u_value_unit FROM envelope_requirements_90_1 WHERE template = '90.1-2010' AND climate_zone_set LIKE '%5%' AND intended_surface_type LIKE '%Wall'</t>
+  </si>
+  <si>
+    <t>SELECT ventilation_primary_space_type, ventilation_secondary_space_type, ventilation_rate_occupant, ventilation_rate_area FROM level_3_ventilation_62_1_1999 WHERE ventilation_primary_space_type LIKE '%Education%' ORDER BY ventilation_rate_occupant DESC</t>
+  </si>
+  <si>
+    <t>SELECT lighting_zone, allowance_type, allowance, allowance_unit FROM exterior_lighting_90_1 WHERE template = '90.1-2013' AND allowance_type LIKE '%parking%'</t>
+  </si>
+  <si>
+    <t>SELECT assembly_minimum_visible_transmittance FROM envelope_requirements_IECC WHERE climate_zone_set LIKE '%4%' AND intended_surface_type LIKE '%Skylight%'</t>
+  </si>
+  <si>
+    <t>SELECT template, climate_zone, design_conditions, under_8000_hours FROM system_requirements_energy_recovery_90_1 WHERE (climate_zone LIKE '%6%' OR climate_zone LIKE '%7%' OR climate_zone LIKE '%8%') AND template = '90.1-2007' ORDER BY climate_zone</t>
+  </si>
+  <si>
+    <t>SELECT assembly_maximum_u_value, assembly_maximum_u_value_unit FROM envelope_requirements_90_1 WHERE template = '90.1-2004' AND climate_zone_set LIKE '%3A%' AND building_category LIKE '%Residential%'</t>
+  </si>
+  <si>
+    <t>SELECT level_2_lighting_space_types.lighting_space_type_name, level_3_lighting_code_definition_table, lighting_space_type_target_illuminance_setpoint FROM level_2_lighting_space_types WHERE lighting_space_type_name LIKE '%office%' ORDER BY lighting_space_type_target_illuminance_setpoint DESC</t>
+  </si>
+  <si>
+    <t>SELECT id, template, intended_surface_type, standards_construction_type, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%3%' OR climate_zone_set LIKE '%4%') AND intended_surface_type LIKE '%Roof%' AND template = '90.1-2010'</t>
+  </si>
+  <si>
+    <t>SELECT name, material_type, thickness, resistance, density FROM support_materials WHERE resistance &gt; 20 AND density &lt; 2.0</t>
+  </si>
+  <si>
+    <t>SELECT DISTINCT lighting_space_type_name, MAX(lighting_space_type_target_illuminance_setpoint) as max_illuminance FROM level_2_lighting_space_types WHERE lighting_space_type_target_illuminance_setpoint &gt; 300 GROUP BY lighting_space_type_name ORDER BY max_illuminance DESC</t>
+  </si>
+  <si>
+    <t>SELECT id, template, intended_surface_type, standards_construction_type, assembly_maximum_solar_heat_gain_coefficient FROM envelope_requirements_IECC WHERE (climate_zone_set LIKE '%5%' OR climate_zone_set LIKE '%6%') AND intended_surface_type LIKE '%Window%'</t>
+  </si>
+  <si>
+    <t>SELECT id, template, intended_surface_type, standards_construction_type, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%7%' OR climate_zone_set LIKE '%8%') AND intended_surface_type LIKE '%Wall%' AND template = '90.1-2010'</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type, lighting_secondary_space_type, lighting_power_density, automatic_partial_off, scheduled_shutoff, annotation FROM level_3_lighting_90_1_2013 WHERE (lighting_primary_space_type LIKE '%Office%' OR lighting_secondary_space_type LIKE '%Residential%') AND lighting_power_density IS NOT NULL ORDER BY lighting_power_density DESC</t>
+  </si>
+  <si>
+    <t>SELECT template, equipment_type, fan_type, minimum_performance_gpm_per_hp, annotation FROM hvac_minimum_requirements_heat_rejection_90_1 WHERE equipment_type LIKE '%Cooling Tower%' AND minimum_performance_gpm_per_hp IS NOT NULL AND (template = '90.1-2013' OR template = '90.1-2019') ORDER BY fan_type, template</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, building_category, construction FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%4%' OR climate_zone_set LIKE '%5%') AND intended_surface_type LIKE '%Wall'</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type, lighting_secondary_space_type, lighting_power_density, annotation FROM level_3_lighting_90_1_2010_prm WHERE lighting_primary_space_type LIKE '%Retail%' OR lighting_primary_space_type LIKE '%Office%' ORDER BY lighting_power_density DESC</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, assembly_maximum_u_value FROM envelope_requirements_IECC WHERE (climate_zone_set LIKE '%6%' OR climate_zone_set LIKE '%7%') AND intended_surface_type LIKE '%Roof'</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, building_category FROM envelope_requirements_90_1_prm WHERE (climate_zone_set LIKE '%3%' OR climate_zone_set LIKE '%4%') AND intended_surface_type LIKE '%Floor'</t>
+  </si>
+  <si>
+    <t>SELECT ventilation_primary_space_type, ventilation_secondary_space_type, ventilation_rate_occupant, ventilation_rate_area FROM level_3_ventilation_62_1_2007 ORDER BY ventilation_rate_area DESC</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, assembly_maximum_solar_heat_gain_coefficient FROM envelope_requirements_IECC WHERE (climate_zone_set LIKE '%5%' OR climate_zone_set LIKE '%6%') AND intended_surface_type LIKE '%Window'</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%4%' OR climate_zone_set LIKE '%5%') AND intended_surface_type LIKE '%Wall' ORDER BY climate_zone_set</t>
+  </si>
+  <si>
+    <t>SELECT template, equipment_type, cooling_type, subcategory, minimum_energy_efficiency_ratio as eer, start_date FROM hvac_minimum_requirements_heat_pumps_cooling_IECC WHERE equipment_type = 'Heat Pumps' AND cooling_type = 'AirCooled' AND minimum_capacity &gt;= 120000 AND maximum_capacity &lt;= 240000 AND start_date &gt; '2015-01-01'</t>
+  </si>
+  <si>
+    <t>SELECT template, equipment_type, region, subcategory, minimum_seasonal_energy_efficiency_ratio, off_mode_power FROM hvac_minimum_requirements_heat_pumps_cooling_90_1 WHERE region = 'Southwestern' AND (equipment_type = 'Small Duct High Velocity' OR (equipment_type = 'Heat Pumps' AND subcategory = 'Single Package')) ORDER BY equipment_type, template</t>
+  </si>
+  <si>
+    <t>SELECT DISTINCT natural_gas_equipment_space_type_name, MAX(natural_gas_equipment_average_epd) as max_epd, natural_gas_equipment_fraction_lost FROM level_2_natural_gas_equipment GROUP BY natural_gas_equipment_space_type_name, natural_gas_equipment_fraction_lost ORDER BY max_epd DESC</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, assembly_maximum_solar_heat_gain_coefficient FROM envelope_requirements_IECC WHERE (climate_zone_set LIKE '%3%' OR climate_zone_set LIKE '%4%') AND intended_surface_type LIKE '%Window' ORDER BY climate_zone_set</t>
+  </si>
+  <si>
+    <t>SELECT template, equipment_type, cooling_type, subcategory, minimum_seasonal_energy_efficiency_ratio_2 as seer, start_date FROM hvac_minimum_requirements_heat_pumps_cooling_90_1 WHERE equipment_type = 'Heat Pumps' AND cooling_type = 'AirCooled' AND minimum_capacity &gt;= 120000 AND maximum_capacity &lt;= 240000 AND start_date &gt; '2010-01-01'</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%5%' OR climate_zone_set LIKE '%6%') AND (intended_surface_type LIKE '%Wall' OR intended_surface_type LIKE '%Roof') ORDER BY climate_zone_set, intended_surface_type</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE intended_surface_type LIKE '%Roof%' AND template = '90.1-2013'</t>
+  </si>
+  <si>
+    <t>SELECT template, equipment_type, rating_condition, minimum_capacity, maximum_capacity, minimum_coefficient_of_performance_heating FROM hvac_minimum_requirements_heat_pumps_heating_90_1 WHERE rating_condition LIKE '%17F%' AND minimum_capacity &gt;= 135000 ORDER BY template</t>
+  </si>
+  <si>
+    <t>SELECT template, equipment_type, fan_type, test_fluid, minimum_performance_btu_per_hr_per_hp FROM hvac_minimum_requirements_heat_rejection_IECC WHERE equipment_type = 'Evaporative Condenser' AND fan_type = 'Propeller or Axial' ORDER BY test_fluid</t>
+  </si>
+  <si>
+    <t>SELECT template, equipment_type, subcategory, rating_condition, minimum_capacity, maximum_capacity, minimum_coefficient_of_performance_heating FROM hvac_minimum_requirements_heat_pumps_heating_90_1 WHERE ((equipment_type = 'SPVHP' AND subcategory LIKE '%Nonweatherized%') OR (equipment_type = 'Heat Pumps')) AND minimum_capacity &lt;= 30000 AND maximum_capacity &gt;= 10000 ORDER BY equipment_type, rating_condition</t>
+  </si>
+  <si>
+    <t>SELECT template, intended_surface_type, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE intended_surface_type LIKE '%Window%' AND building_category = 'Residential' ORDER BY template</t>
+  </si>
+  <si>
+    <t>SELECT DISTINCT lighting_space_type_name, MAX(lighting_space_type_target_illuminance_setpoint) AS max_illuminance, lighting_technology_name FROM level_2_lighting_space_types WHERE lighting_space_type_target_illuminance_setpoint &gt; 300 GROUP BY lighting_space_type_name, lighting_technology_name ORDER BY max_illuminance DESC</t>
+  </si>
+  <si>
+    <t>SELECT DISTINCT template, equipment_type, MIN(minimum_capacity) AS min_cap, MAX(maximum_capacity) AS max_cap FROM hvac_minimum_requirements_unitary_air_conditioners_IECC GROUP BY template, equipment_type ORDER BY equipment_type</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, assembly_maximum_u_value FROM envelope_requirements_IECC WHERE (climate_zone_set LIKE '%6%' OR climate_zone_set LIKE '%7%') AND intended_surface_type LIKE '%Floor%' GROUP BY building_category ORDER BY building_category</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%4%' OR climate_zone_set LIKE '%5%' OR climate_zone_set LIKE '%6%') AND intended_surface_type LIKE '%Wall' AND template = '90.1-2019'</t>
+  </si>
+  <si>
+    <t>SELECT DISTINCT climate_zone_set, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE intended_surface_type LIKE '%Skylight%' AND template = '90.1-2022' ORDER BY assembly_maximum_u_value ASC</t>
+  </si>
+  <si>
+    <t>SELECT id, climate_zone_set, intended_surface_type, building_category, assembly_maximum_u_value FROM envelope_requirements_IECC WHERE intended_surface_type LIKE '%Roof%' AND (building_category LIKE '%Residential%' OR building_category LIKE '%Commercial%') ORDER BY assembly_maximum_u_value ASC</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, assembly_minimum_vt_shgc FROM envelope_requirements_90_1 WHERE intended_surface_type LIKE '%Skylight%' AND (climate_zone_set LIKE '%4%' OR climate_zone_set LIKE '%5%') AND template = '90.1-2019' ORDER BY assembly_minimum_vt_shgc ASC</t>
+  </si>
+  <si>
+    <t>SELECT template, equipment_type, fuel_type, minimum_capacity, maximum_capacity, minimum_annual_fuel_utilization_efficiency FROM hvac_minimum_requirements_furnaces_IECC WHERE (fuel_type = 'Gas' OR fuel_type = 'Oil') AND minimum_capacity &lt;= 200000 ORDER BY minimum_annual_fuel_utilization_efficiency DESC</t>
+  </si>
+  <si>
+    <t>SELECT intended_surface_type, assembly_maximum_u_value, assembly_maximum_solar_heat_gain_coefficient FROM envelope_requirements_90_1 WHERE intended_surface_type LIKE '%Roof%' ORDER BY assembly_maximum_u_value DESC</t>
+  </si>
+  <si>
+    <t>SELECT intended_surface_type, assembly_maximum_u_value FROM envelope_requirements_IECC WHERE intended_surface_type LIKE '%Wall%' ORDER BY assembly_maximum_u_value</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type, rcr_threshold, automatic_full_off FROM level_3_lighting_90_1_2022 WHERE rcr_threshold &lt;= 4 AND (automatic_full_off = 'ADD2' OR scheduled_shutoff = 'ADD2') ORDER BY rcr_threshold</t>
+  </si>
+  <si>
+    <t>SELECT intended_surface_type, assembly_maximum_u_value FROM envelope_requirements_IECC WHERE (climate_zone_set LIKE '%6%' OR climate_zone_set LIKE '%7%') AND intended_surface_type LIKE '%Floor%' ORDER BY assembly_maximum_u_value</t>
+  </si>
+  <si>
+    <t>SELECT electric_equipment_space_type_name, electric_equipment_average_epd, electric_equipment_median_epd FROM level_2_electric_equipment ORDER BY electric_equipment_average_epd DESC</t>
+  </si>
+  <si>
+    <t>SELECT name, intended_surface_type, insulation_layer FROM support_constructions WHERE (intended_surface_type LIKE '%Roof%' OR intended_surface_type LIKE '%Wall%') ORDER BY name</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, assembly_maximum_u_value, annotation FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%4%' OR climate_zone_set LIKE '%5%') AND intended_surface_type LIKE '%Wall%' AND template = '90.1-2022'</t>
+  </si>
+  <si>
+    <t>SELECT template, climate_zone_set, intended_surface_type, assembly_maximum_solar_heat_gain_coefficient, annotation FROM envelope_requirements_IECC WHERE intended_surface_type LIKE '%Window%' AND (template = 'IECC-2018' OR template = 'IECC-2021') ORDER BY template</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, assembly_maximum_u_value, annotation FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%3%' OR climate_zone_set LIKE '%4%') AND intended_surface_type LIKE '%Roof%' AND template = '90.1-2022'</t>
+  </si>
+  <si>
+    <t>SELECT template, equipment_type, subcategory, minimum_energy_efficiency_ratio, start_date, end_date, annotation FROM hvac_minimum_requirements_variable_refrigerant_flow_systems_90_1 WHERE (equipment_type LIKE '%WaterSource%' OR equipment_type LIKE '%GroundSource%') AND template = '90.1-2016'</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, assembly_maximum_u_value, annotation FROM envelope_requirements_IECC WHERE climate_zone_set LIKE '%5%' AND intended_surface_type LIKE '%Floor%' AND template = 'IECC-2021'</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, assembly_maximum_u_value, assembly_maximum_solar_heat_gain_coefficient FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%4%' OR climate_zone_set LIKE '%5%' OR climate_zone_set LIKE '%6%') AND template LIKE '%2010%' AND intended_surface_type LIKE '%Window%' ORDER BY assembly_maximum_u_value</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, assembly_maximum_u_value FROM envelope_requirements_IECC WHERE climate_zone_set LIKE '%7%' AND intended_surface_type LIKE '%Roof%' ORDER BY assembly_maximum_u_value</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%6%' OR climate_zone_set LIKE '%7%') AND intended_surface_type LIKE '%Roof'</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type, lighting_power_density, automatic_daylight_responsive_controls_for_toplighting FROM level_3_lighting_90_1_2019 WHERE automatic_daylight_responsive_controls_for_toplighting = 'REQ' AND lighting_power_density &gt; 1.5 ORDER BY lighting_power_density DESC</t>
+  </si>
+  <si>
+    <t>SELECT template, intended_surface_type, assembly_maximum_u_value FROM envelope_requirements_IECC WHERE (climate_zone_set LIKE '%3%' OR climate_zone_set LIKE '%4%' OR climate_zone_set LIKE '%5%') AND intended_surface_type LIKE '%Roof%' AND template = 'IECC-2021'</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%7%' OR climate_zone_set LIKE '%8%') AND intended_surface_type LIKE '%Floor'</t>
+  </si>
+  <si>
+    <t>SELECT template, equipment_type, fuel_type, minimum_capacity, maximum_capacity, minimum_annual_fuel_utilization_efficiency, annotation FROM hvac_minimum_requirements_furnaces_90_1 WHERE equipment_type LIKE '%Warm Air Furnace%' AND fuel_type = 'NaturalGas' ORDER BY template, minimum_annual_fuel_utilization_efficiency DESC</t>
+  </si>
+  <si>
+    <t>SELECT id, space_type_name, lighting_space_type_name, ventilation_space_type_name, electric_equipment_space_type_name FROM level_1_space_types WHERE electric_equipment_space_type_name LIKE '%Office%'</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE climate_zone_set LIKE '%4%' AND intended_surface_type LIKE '%Roof%' AND (template LIKE '%90.1-2019%' OR template LIKE '%IECC%')</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, assembly_maximum_solar_heat_gain_coefficient FROM envelope_requirements_90_1 WHERE template LIKE '%90.1-2016%' ORDER BY assembly_maximum_solar_heat_gain_coefficient DESC</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%4%') AND intended_surface_type LIKE '%Wall'</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type, lighting_secondary_space_type, method, lighting_power_density, automatic_daylight_responsive_controls_for_sidelighting FROM level_3_lighting_90_1_2010_prm WHERE lighting_power_density &gt; 1.2 AND (automatic_daylight_responsive_controls_for_sidelighting = 'REQ' OR automatic_daylight_responsive_controls_for_toplighting = 'REQ')</t>
+  </si>
+  <si>
+    <t>SELECT template, equipment_type, fuel_type, minimum_capacity, maximum_capacity, minimum_annual_fuel_utilization_efficiency FROM hvac_minimum_requirements_furnaces_IECC WHERE fuel_type = 'NaturalGas' AND minimum_capacity &lt;= 200000 AND (maximum_capacity &gt;= 100000 OR maximum_capacity IS NULL)</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%7%') AND intended_surface_type LIKE '%Roof%' UNION SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, assembly_maximum_u_value FROM envelope_requirements_IECC WHERE (climate_zone_set LIKE '%7%') AND intended_surface_type LIKE '%Roof'</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, assembly_maximum_u_value FROM envelope_requirements_IECC WHERE (climate_zone_set LIKE '%5%') AND intended_surface_type LIKE '%Floor'</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, building_category, construction, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%4%' OR climate_zone_set LIKE '%5%') AND intended_surface_type LIKE '%Wall' ORDER BY climate_zone_set</t>
+  </si>
+  <si>
+    <t>SELECT name, material_type, thickness, resistance, (resistance / thickness) as resistance_per_inch, density FROM support_materials WHERE material_type = 'StandardOpaqueMaterial' AND resistance &gt; 20 AND thickness &gt; 0 ORDER BY resistance_per_inch DESC LIMIT 10</t>
+  </si>
+  <si>
+    <t>SELECT template, climate_zone, under_8000_hours, design_conditions, percent_oa_70_to_80, percent_oa_greater_than_80, energy_recovery_effectiveness FROM system_requirements_energy_recovery_90_1 WHERE percent_oa_greater_than_80 IS NOT NULL AND percent_oa_greater_than_80 &lt; 5000 ORDER BY percent_oa_greater_than_80, climate_zone</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, building_category, construction, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%6%' OR climate_zone_set LIKE '%7%' OR climate_zone_set LIKE '%8%') AND intended_surface_type LIKE '%Roof' ORDER BY climate_zone_set</t>
+  </si>
+  <si>
+    <t>SELECT ventilation_primary_space_type, ventilation_secondary_space_type, air_class, ventilation_rate_occupant, ventilation_rate_area FROM level_3_ventilation_62_1_2004 WHERE air_class = 2 ORDER BY ventilation_rate_area DESC, ventilation_rate_occupant DESC</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, building_category, construction, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE intended_surface_type LIKE '%Wall' UNION SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, building_category, construction, assembly_maximum_u_value FROM envelope_requirements_IECC WHERE intended_surface_type LIKE '%Wall'</t>
+  </si>
+  <si>
+    <t>SELECT ventilation_primary_space_type, ventilation_secondary_space_type, air_class, ventilation_rate_occupant, ventilation_rate_area FROM level_3_ventilation_62_1_2004 WHERE ventilation_rate_occupant &gt; 10 ORDER BY ventilation_rate_occupant DESC</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, assembly_maximum_u_value FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%3%' OR climate_zone_set LIKE '%4%') AND intended_surface_type LIKE '%Wall'</t>
+  </si>
+  <si>
+    <t>SELECT natural_gas_equipment_space_type_name, natural_gas_equipment_minimum_epd, natural_gas_equipment_median_epd, natural_gas_equipment_maximum_epd FROM level_2_natural_gas_equipment WHERE (natural_gas_equipment_space_type_name LIKE '%kitchen%' OR natural_gas_equipment_space_type_name LIKE '%deli%')</t>
+  </si>
+  <si>
+    <t>SELECT template, climate_zone, under_8000_hours, design_conditions, percent_oa_70_to_80, percent_oa_greater_than_80, energy_recovery_effectiveness FROM system_requirements_energy_recovery_90_1 WHERE percent_oa_greater_than_80 IS NOT NULL ORDER BY percent_oa_greater_than_80, climate_zone</t>
+  </si>
+  <si>
+    <t>SELECT ventilation_primary_space_type, ventilation_secondary_space_type, ventilation_rate_occupant, ventilation_rate_area, occupancy_per_area FROM level_3_ventilation_62_1_2004 WHERE ventilation_primary_space_type LIKE '%Food and Beverage Service%' ORDER BY ventilation_rate_occupant DESC</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, assembly_maximum_u_value FROM envelope_requirements_IECC WHERE intended_surface_type LIKE '%Roof%' ORDER BY climate_zone_set</t>
+  </si>
+  <si>
+    <t>SELECT id, lighting_space_type_name, level_3_lighting_code_definition_table, level_3_lighting_code_definition_id FROM level_2_lighting_space_types WHERE lighting_space_type_name LIKE '%Office%'</t>
+  </si>
+  <si>
+    <t>SELECT name, intended_surface_type, standards_construction_type, insulation_layer FROM support_constructions WHERE intended_surface_type LIKE '%Wall%'</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type, building_category FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%4%' OR climate_zone_set LIKE '%5%') AND intended_surface_type LIKE '%Roof'</t>
+  </si>
+  <si>
+    <t>SELECT template, equipment_type, fan_type, minimum_performance_btu_per_hr_per_hp FROM hvac_minimum_requirements_heat_rejection_IECC WHERE equipment_type = 'Evaporative Condenser' AND template LIKE '%IECC-2021%'</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%3%' OR climate_zone_set LIKE '%4%') AND intended_surface_type LIKE '%Wall'</t>
+  </si>
+  <si>
+    <t>SELECT ventilation_primary_space_type, ventilation_rate_occupant, occupancy_per_area FROM level_3_ventilation_62_1_2007 WHERE occupancy_per_area &gt; 100 AND ventilation_rate_occupant &gt; 5</t>
+  </si>
+  <si>
+    <t>SELECT lighting_primary_space_type, method, automatic_daylight_responsive_controls_for_sidelighting FROM level_3_lighting_90_1_2010_prm WHERE method = 'BA' AND (automatic_daylight_responsive_controls_for_sidelighting = 'REQ')</t>
+  </si>
+  <si>
+    <t>SELECT id, template, climate_zone_set, intended_surface_type, standards_construction_type FROM envelope_requirements_90_1 WHERE (climate_zone_set LIKE '%5%' OR climate_zone_set LIKE '%6%') AND intended_surface_type LIKE '%Roof'</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1081,12 +3670,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1124,11 +3707,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1142,11 +3722,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1194,8 +3774,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0C8568FE-6704-4958-8B79-579C6A959B01}" name="Table1" displayName="Table1" ref="B1:C64" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2">
-  <autoFilter ref="B1:C64" xr:uid="{0C8568FE-6704-4958-8B79-579C6A959B01}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0C8568FE-6704-4958-8B79-579C6A959B01}" name="Table1" displayName="Table1" ref="B1:C514" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2">
+  <autoFilter ref="B1:C514" xr:uid="{0C8568FE-6704-4958-8B79-579C6A959B01}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{0458D18D-3D29-4D20-8D9F-298C1BBCB325}" name="answer" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{2CB46501-370C-4514-802F-F7A4E1E87BAA}" name="question" dataDxfId="0"/>
@@ -1521,7 +4101,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CDBA05A-EE27-4D14-81B9-A7E66315CCFE}">
-  <dimension ref="B1:M80"/>
+  <dimension ref="B1:M514"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="8.83984375" customWidth="1"/>
@@ -1531,593 +4111,4128 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="2:3" ht="115.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="1" t="s">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" ht="115.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="2:3" ht="144" x14ac:dyDescent="0.55000000000000004">
-      <c r="B3" s="1" t="s">
+    </row>
+    <row r="4" spans="2:3" ht="144" x14ac:dyDescent="0.55000000000000004">
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="2:3" ht="115.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B4" s="1" t="s">
+    </row>
+    <row r="5" spans="2:3" ht="115.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="2:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B5" s="1" t="s">
+    </row>
+    <row r="6" spans="2:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="2:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="1" t="s">
+    </row>
+    <row r="7" spans="2:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="2:3" ht="72" x14ac:dyDescent="0.55000000000000004">
-      <c r="B7" s="1" t="s">
+    </row>
+    <row r="8" spans="2:3" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="2:3" ht="144" x14ac:dyDescent="0.55000000000000004">
-      <c r="B8" s="1" t="s">
+    </row>
+    <row r="9" spans="2:3" ht="129.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="1" t="s">
+    </row>
+    <row r="10" spans="2:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="2:3" ht="216" x14ac:dyDescent="0.55000000000000004">
-      <c r="B10" s="1" t="s">
+    </row>
+    <row r="11" spans="2:3" ht="216" x14ac:dyDescent="0.55000000000000004">
+      <c r="B11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="2:3" ht="230.4" x14ac:dyDescent="0.55000000000000004">
-      <c r="B11" s="1" t="s">
+    </row>
+    <row r="12" spans="2:3" ht="230.4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="2:3" ht="201.6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="1" t="s">
+    </row>
+    <row r="13" spans="2:3" ht="201.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="2:3" ht="244.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B13" s="1" t="s">
+    </row>
+    <row r="14" spans="2:3" ht="244.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="2:3" ht="244.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B14" s="1" t="s">
+    </row>
+    <row r="15" spans="2:3" ht="230.4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" spans="2:3" ht="273.60000000000002" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="1" t="s">
+    </row>
+    <row r="16" spans="2:3" ht="244.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="16" spans="2:3" ht="244.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B16" s="1" t="s">
+    </row>
+    <row r="17" spans="2:13" ht="216" x14ac:dyDescent="0.55000000000000004">
+      <c r="B17" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="2:13" ht="302.39999999999998" x14ac:dyDescent="0.55000000000000004">
-      <c r="B17" s="1" t="s">
+    </row>
+    <row r="18" spans="2:13" ht="259.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B18" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18" spans="2:13" ht="201.6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18" s="1" t="s">
+    </row>
+    <row r="19" spans="2:13" ht="201.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B19" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="19" spans="2:13" ht="158.4" x14ac:dyDescent="0.55000000000000004">
-      <c r="B19" s="1" t="s">
+    </row>
+    <row r="20" spans="2:13" ht="158.4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" spans="2:13" ht="201.6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B20" s="1" t="s">
+    </row>
+    <row r="21" spans="2:13" ht="201.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="21" spans="2:13" ht="216" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="1" t="s">
+    </row>
+    <row r="22" spans="2:13" ht="216" x14ac:dyDescent="0.55000000000000004">
+      <c r="B22" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="22" spans="2:13" ht="288" x14ac:dyDescent="0.55000000000000004">
-      <c r="B22" s="1" t="s">
+    </row>
+    <row r="23" spans="2:13" ht="288" x14ac:dyDescent="0.55000000000000004">
+      <c r="B23" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="23" spans="2:13" ht="230.4" x14ac:dyDescent="0.55000000000000004">
-      <c r="B23" s="1" t="s">
+    </row>
+    <row r="24" spans="2:13" ht="230.4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B24" t="s">
+        <v>44</v>
+      </c>
+      <c r="C24" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="24" spans="2:13" ht="259.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B24" s="1" t="s">
+    </row>
+    <row r="25" spans="2:13" ht="259.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B25" t="s">
+        <v>46</v>
+      </c>
+      <c r="C25" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="25" spans="2:13" ht="129.6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B25" s="1" t="s">
+    </row>
+    <row r="26" spans="2:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C26" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="26" spans="2:13" ht="216" x14ac:dyDescent="0.55000000000000004">
-      <c r="B26" s="1" t="s">
+    </row>
+    <row r="27" spans="2:13" ht="216" x14ac:dyDescent="0.55000000000000004">
+      <c r="B27" t="s">
+        <v>51</v>
+      </c>
+      <c r="C27" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="27" spans="2:13" ht="172.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B27" s="1" t="s">
+    </row>
+    <row r="28" spans="2:13" ht="172.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B28" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="3"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+    </row>
+    <row r="29" spans="2:13" ht="129.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B29" t="s">
+        <v>127</v>
+      </c>
+      <c r="C29" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="28" spans="2:13" ht="129.6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B28" s="1" t="s">
+    </row>
+    <row r="30" spans="2:13" ht="201.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B30" t="s">
         <v>55</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C30" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="5"/>
+      <c r="K30" s="4"/>
+      <c r="L30" s="4"/>
+    </row>
+    <row r="31" spans="2:13" ht="144" x14ac:dyDescent="0.55000000000000004">
+      <c r="B31" t="s">
+        <v>56</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="32" spans="2:13" ht="129.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B32" t="s">
+        <v>60</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" ht="273.60000000000002" x14ac:dyDescent="0.55000000000000004">
+      <c r="B33" t="s">
+        <v>61</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" ht="144" x14ac:dyDescent="0.55000000000000004">
+      <c r="B34" t="s">
+        <v>63</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3" ht="144" x14ac:dyDescent="0.55000000000000004">
+      <c r="B35" t="s">
+        <v>66</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3" ht="216" x14ac:dyDescent="0.55000000000000004">
+      <c r="B36" t="s">
+        <v>67</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3" ht="187.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B37" t="s">
+        <v>69</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="38" spans="2:3" ht="201.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B38" t="s">
+        <v>72</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3" ht="187.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B39" t="s">
+        <v>128</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3" ht="172.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B40" t="s">
+        <v>74</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="41" spans="2:3" ht="302.39999999999998" x14ac:dyDescent="0.55000000000000004">
+      <c r="B41" t="s">
+        <v>75</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="42" spans="2:3" ht="187.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B42" t="s">
+        <v>78</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="43" spans="2:3" ht="244.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B43" t="s">
+        <v>79</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="44" spans="2:3" ht="187.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B44" t="s">
+        <v>82</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="45" spans="2:3" ht="172.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B45" t="s">
+        <v>84</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="46" spans="2:3" ht="172.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B46" t="s">
+        <v>124</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="47" spans="2:3" ht="259.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B47" t="s">
+        <v>87</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="48" spans="2:3" ht="129.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B48" t="s">
+        <v>89</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="49" spans="2:9" ht="158.4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B49" t="s">
+        <v>91</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="50" spans="2:9" ht="144" x14ac:dyDescent="0.55000000000000004">
+      <c r="B50" t="s">
+        <v>129</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="51" spans="2:9" ht="144" x14ac:dyDescent="0.55000000000000004">
+      <c r="B51" t="s">
+        <v>94</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="52" spans="2:9" ht="158.4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B52" t="s">
+        <v>96</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="53" spans="2:9" ht="172.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B53" t="s">
+        <v>98</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="54" spans="2:9" ht="172.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B54" t="s">
+        <v>130</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="55" spans="2:9" ht="172.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B55" t="s">
+        <v>101</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="56" spans="2:9" ht="187.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B56" t="s">
+        <v>103</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="57" spans="2:9" ht="158.4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B57" t="s">
+        <v>106</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="58" spans="2:9" ht="201.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B58" t="s">
+        <v>107</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="59" spans="2:9" ht="172.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B59" t="s">
+        <v>109</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="60" spans="2:9" ht="201.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B60" t="s">
+        <v>112</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="61" spans="2:9" ht="187.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B61" t="s">
+        <v>113</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="I61" s="6"/>
+    </row>
+    <row r="62" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="B62" t="s">
+        <v>115</v>
+      </c>
+      <c r="C62" t="s">
+        <v>116</v>
+      </c>
+      <c r="I62" s="6"/>
+    </row>
+    <row r="63" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="B63" t="s">
+        <v>117</v>
+      </c>
+      <c r="C63" t="s">
+        <v>118</v>
+      </c>
+      <c r="I63" s="6"/>
+    </row>
+    <row r="64" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="B64" t="s">
+        <v>119</v>
+      </c>
+      <c r="C64" t="s">
+        <v>120</v>
+      </c>
+      <c r="I64" s="6"/>
+    </row>
+    <row r="65" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B65" t="s">
+        <v>121</v>
+      </c>
+      <c r="C65" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="66" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B66" t="s">
+        <v>131</v>
+      </c>
+      <c r="C66" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="67" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B67" t="s">
+        <v>132</v>
+      </c>
+      <c r="C67" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="68" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B68" t="s">
+        <v>133</v>
+      </c>
+      <c r="C68" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="69" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B69" t="s">
+        <v>134</v>
+      </c>
+      <c r="C69" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="70" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B70" t="s">
+        <v>135</v>
+      </c>
+      <c r="C70" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="71" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B71" t="s">
+        <v>136</v>
+      </c>
+      <c r="C71" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="72" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B72" t="s">
+        <v>137</v>
+      </c>
+      <c r="C72" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="73" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B73" t="s">
+        <v>138</v>
+      </c>
+      <c r="C73" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="74" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B74" t="s">
+        <v>139</v>
+      </c>
+      <c r="C74" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="75" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B75" t="s">
+        <v>140</v>
+      </c>
+      <c r="C75" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="76" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B76" t="s">
+        <v>141</v>
+      </c>
+      <c r="C76" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="77" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B77" t="s">
+        <v>142</v>
+      </c>
+      <c r="C77" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="78" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B78" t="s">
+        <v>143</v>
+      </c>
+      <c r="C78" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="79" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B79" t="s">
+        <v>144</v>
+      </c>
+      <c r="C79" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="80" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B80" t="s">
+        <v>145</v>
+      </c>
+      <c r="C80" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="81" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B81" t="s">
+        <v>146</v>
+      </c>
+      <c r="C81" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="82" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B82" t="s">
+        <v>147</v>
+      </c>
+      <c r="C82" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="83" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B83" t="s">
+        <v>148</v>
+      </c>
+      <c r="C83" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="84" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B84" t="s">
+        <v>149</v>
+      </c>
+      <c r="C84" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="85" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B85" t="s">
+        <v>150</v>
+      </c>
+      <c r="C85" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="86" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B86" t="s">
+        <v>151</v>
+      </c>
+      <c r="C86" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="87" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B87" t="s">
+        <v>152</v>
+      </c>
+      <c r="C87" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="88" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B88" t="s">
+        <v>153</v>
+      </c>
+      <c r="C88" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="89" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B89" t="s">
+        <v>154</v>
+      </c>
+      <c r="C89" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="90" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B90" t="s">
+        <v>155</v>
+      </c>
+      <c r="C90" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="91" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B91" t="s">
+        <v>156</v>
+      </c>
+      <c r="C91" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="92" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B92" t="s">
+        <v>157</v>
+      </c>
+      <c r="C92" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="93" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B93" t="s">
+        <v>158</v>
+      </c>
+      <c r="C93" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="94" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B94" t="s">
+        <v>159</v>
+      </c>
+      <c r="C94" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="95" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B95" t="s">
+        <v>160</v>
+      </c>
+      <c r="C95" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="96" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B96" t="s">
+        <v>161</v>
+      </c>
+      <c r="C96" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="97" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B97" t="s">
+        <v>162</v>
+      </c>
+      <c r="C97" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="98" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B98" t="s">
+        <v>163</v>
+      </c>
+      <c r="C98" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="99" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B99" t="s">
+        <v>164</v>
+      </c>
+      <c r="C99" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="100" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B100" t="s">
+        <v>165</v>
+      </c>
+      <c r="C100" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="101" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B101" t="s">
+        <v>166</v>
+      </c>
+      <c r="C101" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="102" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B102" t="s">
+        <v>167</v>
+      </c>
+      <c r="C102" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="103" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B103" t="s">
+        <v>168</v>
+      </c>
+      <c r="C103" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="104" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B104" t="s">
+        <v>169</v>
+      </c>
+      <c r="C104" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="105" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B105" t="s">
+        <v>170</v>
+      </c>
+      <c r="C105" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="106" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B106" t="s">
+        <v>171</v>
+      </c>
+      <c r="C106" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="107" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B107" t="s">
+        <v>172</v>
+      </c>
+      <c r="C107" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="108" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B108" t="s">
+        <v>173</v>
+      </c>
+      <c r="C108" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="109" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B109" t="s">
+        <v>174</v>
+      </c>
+      <c r="C109" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="110" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B110" t="s">
+        <v>175</v>
+      </c>
+      <c r="C110" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="111" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B111" t="s">
+        <v>176</v>
+      </c>
+      <c r="C111" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="112" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B112" t="s">
+        <v>177</v>
+      </c>
+      <c r="C112" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="113" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B113" t="s">
+        <v>178</v>
+      </c>
+      <c r="C113" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="114" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B114" t="s">
+        <v>179</v>
+      </c>
+      <c r="C114" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="115" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B115" t="s">
+        <v>180</v>
+      </c>
+      <c r="C115" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="116" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B116" t="s">
+        <v>181</v>
+      </c>
+      <c r="C116" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="117" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B117" t="s">
+        <v>182</v>
+      </c>
+      <c r="C117" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="118" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B118" t="s">
+        <v>183</v>
+      </c>
+      <c r="C118" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="119" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B119" t="s">
+        <v>184</v>
+      </c>
+      <c r="C119" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="120" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B120" t="s">
+        <v>185</v>
+      </c>
+      <c r="C120" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="121" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B121" t="s">
+        <v>186</v>
+      </c>
+      <c r="C121" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="122" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B122" t="s">
+        <v>187</v>
+      </c>
+      <c r="C122" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="123" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B123" t="s">
+        <v>188</v>
+      </c>
+      <c r="C123" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="124" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B124" t="s">
+        <v>189</v>
+      </c>
+      <c r="C124" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="125" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B125" t="s">
+        <v>190</v>
+      </c>
+      <c r="C125" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="126" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B126" t="s">
+        <v>191</v>
+      </c>
+      <c r="C126" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="127" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B127" t="s">
+        <v>192</v>
+      </c>
+      <c r="C127" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="128" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B128" t="s">
+        <v>193</v>
+      </c>
+      <c r="C128" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="129" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B129" t="s">
+        <v>194</v>
+      </c>
+      <c r="C129" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="130" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B130" t="s">
+        <v>195</v>
+      </c>
+      <c r="C130" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="131" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B131" t="s">
+        <v>196</v>
+      </c>
+      <c r="C131" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="132" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B132" t="s">
+        <v>197</v>
+      </c>
+      <c r="C132" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="133" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B133" t="s">
+        <v>198</v>
+      </c>
+      <c r="C133" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="134" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B134" t="s">
+        <v>199</v>
+      </c>
+      <c r="C134" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="135" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B135" t="s">
+        <v>200</v>
+      </c>
+      <c r="C135" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="136" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B136" t="s">
+        <v>201</v>
+      </c>
+      <c r="C136" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="137" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B137" t="s">
+        <v>202</v>
+      </c>
+      <c r="C137" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="138" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B138" t="s">
+        <v>203</v>
+      </c>
+      <c r="C138" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="139" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B139" t="s">
+        <v>204</v>
+      </c>
+      <c r="C139" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="140" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B140" t="s">
+        <v>205</v>
+      </c>
+      <c r="C140" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="141" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B141" t="s">
+        <v>206</v>
+      </c>
+      <c r="C141" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="142" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B142" t="s">
+        <v>207</v>
+      </c>
+      <c r="C142" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="143" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B143" t="s">
+        <v>208</v>
+      </c>
+      <c r="C143" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="144" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B144" t="s">
+        <v>209</v>
+      </c>
+      <c r="C144" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="145" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B145" t="s">
+        <v>210</v>
+      </c>
+      <c r="C145" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="146" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B146" t="s">
+        <v>211</v>
+      </c>
+      <c r="C146" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="147" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B147" t="s">
+        <v>212</v>
+      </c>
+      <c r="C147" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="148" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B148" t="s">
+        <v>213</v>
+      </c>
+      <c r="C148" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="149" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B149" t="s">
+        <v>214</v>
+      </c>
+      <c r="C149" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="150" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B150" t="s">
+        <v>215</v>
+      </c>
+      <c r="C150" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="151" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B151" t="s">
+        <v>216</v>
+      </c>
+      <c r="C151" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="152" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B152" t="s">
+        <v>217</v>
+      </c>
+      <c r="C152" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="153" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B153" t="s">
+        <v>218</v>
+      </c>
+      <c r="C153" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="154" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B154" t="s">
+        <v>219</v>
+      </c>
+      <c r="C154" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="155" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B155" t="s">
+        <v>220</v>
+      </c>
+      <c r="C155" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="156" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B156" t="s">
+        <v>221</v>
+      </c>
+      <c r="C156" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="157" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B157" t="s">
+        <v>222</v>
+      </c>
+      <c r="C157" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="158" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B158" t="s">
+        <v>223</v>
+      </c>
+      <c r="C158" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="159" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B159" t="s">
+        <v>224</v>
+      </c>
+      <c r="C159" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="160" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B160" t="s">
+        <v>225</v>
+      </c>
+      <c r="C160" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="161" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B161" t="s">
+        <v>226</v>
+      </c>
+      <c r="C161" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="162" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B162" t="s">
+        <v>227</v>
+      </c>
+      <c r="C162" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="163" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B163" t="s">
+        <v>228</v>
+      </c>
+      <c r="C163" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="164" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B164" t="s">
+        <v>229</v>
+      </c>
+      <c r="C164" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="165" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B165" t="s">
+        <v>230</v>
+      </c>
+      <c r="C165" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="166" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B166" t="s">
+        <v>231</v>
+      </c>
+      <c r="C166" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="167" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B167" t="s">
+        <v>232</v>
+      </c>
+      <c r="C167" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="168" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B168" t="s">
+        <v>233</v>
+      </c>
+      <c r="C168" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="169" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B169" t="s">
+        <v>234</v>
+      </c>
+      <c r="C169" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="170" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B170" t="s">
+        <v>235</v>
+      </c>
+      <c r="C170" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="171" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B171" t="s">
+        <v>236</v>
+      </c>
+      <c r="C171" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="172" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B172" t="s">
+        <v>237</v>
+      </c>
+      <c r="C172" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="173" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B173" t="s">
+        <v>238</v>
+      </c>
+      <c r="C173" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="174" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B174" t="s">
+        <v>239</v>
+      </c>
+      <c r="C174" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="175" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B175" t="s">
+        <v>240</v>
+      </c>
+      <c r="C175" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="176" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B176" t="s">
+        <v>241</v>
+      </c>
+      <c r="C176" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="177" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B177" t="s">
+        <v>242</v>
+      </c>
+      <c r="C177" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="178" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B178" t="s">
+        <v>243</v>
+      </c>
+      <c r="C178" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="179" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B179" t="s">
+        <v>244</v>
+      </c>
+      <c r="C179" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="180" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B180" t="s">
+        <v>245</v>
+      </c>
+      <c r="C180" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="181" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B181" t="s">
+        <v>246</v>
+      </c>
+      <c r="C181" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="182" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B182" t="s">
+        <v>247</v>
+      </c>
+      <c r="C182" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="183" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B183" t="s">
+        <v>248</v>
+      </c>
+      <c r="C183" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="184" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B184" t="s">
+        <v>249</v>
+      </c>
+      <c r="C184" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="185" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B185" t="s">
+        <v>250</v>
+      </c>
+      <c r="C185" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="186" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B186" t="s">
+        <v>251</v>
+      </c>
+      <c r="C186" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="187" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B187" t="s">
+        <v>252</v>
+      </c>
+      <c r="C187" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="188" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B188" t="s">
+        <v>253</v>
+      </c>
+      <c r="C188" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="189" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B189" t="s">
+        <v>254</v>
+      </c>
+      <c r="C189" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="190" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B190" t="s">
+        <v>255</v>
+      </c>
+      <c r="C190" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="191" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B191" t="s">
+        <v>256</v>
+      </c>
+      <c r="C191" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="192" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B192" t="s">
+        <v>257</v>
+      </c>
+      <c r="C192" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="193" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B193" t="s">
+        <v>258</v>
+      </c>
+      <c r="C193" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="194" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B194" t="s">
+        <v>259</v>
+      </c>
+      <c r="C194" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="195" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B195" t="s">
+        <v>260</v>
+      </c>
+      <c r="C195" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="196" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B196" t="s">
+        <v>261</v>
+      </c>
+      <c r="C196" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="197" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B197" t="s">
+        <v>262</v>
+      </c>
+      <c r="C197" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="198" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B198" t="s">
+        <v>263</v>
+      </c>
+      <c r="C198" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="199" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B199" t="s">
+        <v>264</v>
+      </c>
+      <c r="C199" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="200" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B200" t="s">
+        <v>265</v>
+      </c>
+      <c r="C200" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="201" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B201" t="s">
+        <v>266</v>
+      </c>
+      <c r="C201" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="202" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B202" t="s">
+        <v>267</v>
+      </c>
+      <c r="C202" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="203" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B203" t="s">
+        <v>268</v>
+      </c>
+      <c r="C203" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="204" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B204" t="s">
+        <v>269</v>
+      </c>
+      <c r="C204" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="205" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B205" t="s">
+        <v>270</v>
+      </c>
+      <c r="C205" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="206" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B206" t="s">
+        <v>271</v>
+      </c>
+      <c r="C206" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="207" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B207" t="s">
+        <v>272</v>
+      </c>
+      <c r="C207" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="208" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B208" t="s">
+        <v>273</v>
+      </c>
+      <c r="C208" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="209" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B209" t="s">
+        <v>274</v>
+      </c>
+      <c r="C209" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="210" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B210" t="s">
+        <v>275</v>
+      </c>
+      <c r="C210" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="211" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B211" t="s">
+        <v>276</v>
+      </c>
+      <c r="C211" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="212" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B212" t="s">
+        <v>277</v>
+      </c>
+      <c r="C212" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="213" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B213" t="s">
+        <v>278</v>
+      </c>
+      <c r="C213" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="214" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B214" t="s">
+        <v>279</v>
+      </c>
+      <c r="C214" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="215" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B215" t="s">
+        <v>280</v>
+      </c>
+      <c r="C215" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="216" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B216" t="s">
+        <v>281</v>
+      </c>
+      <c r="C216" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="217" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B217" t="s">
+        <v>282</v>
+      </c>
+      <c r="C217" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="218" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B218" t="s">
+        <v>283</v>
+      </c>
+      <c r="C218" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="219" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B219" t="s">
+        <v>106</v>
+      </c>
+      <c r="C219" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="220" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B220" t="s">
+        <v>284</v>
+      </c>
+      <c r="C220" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="221" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B221" t="s">
+        <v>285</v>
+      </c>
+      <c r="C221" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="222" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B222" t="s">
+        <v>286</v>
+      </c>
+      <c r="C222" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="223" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B223" t="s">
+        <v>287</v>
+      </c>
+      <c r="C223" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="224" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B224" t="s">
+        <v>288</v>
+      </c>
+      <c r="C224" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="225" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B225" t="s">
+        <v>289</v>
+      </c>
+      <c r="C225" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="226" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B226" t="s">
+        <v>290</v>
+      </c>
+      <c r="C226" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="227" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B227" t="s">
+        <v>291</v>
+      </c>
+      <c r="C227" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="228" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B228" t="s">
+        <v>292</v>
+      </c>
+      <c r="C228" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="229" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B229" t="s">
+        <v>293</v>
+      </c>
+      <c r="C229" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="230" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B230" t="s">
+        <v>294</v>
+      </c>
+      <c r="C230" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="231" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B231" t="s">
+        <v>295</v>
+      </c>
+      <c r="C231" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="232" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B232" t="s">
+        <v>296</v>
+      </c>
+      <c r="C232" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="233" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B233" t="s">
+        <v>297</v>
+      </c>
+      <c r="C233" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="234" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B234" t="s">
+        <v>298</v>
+      </c>
+      <c r="C234" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="235" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B235" t="s">
+        <v>299</v>
+      </c>
+      <c r="C235" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="236" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B236" t="s">
+        <v>300</v>
+      </c>
+      <c r="C236" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="237" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B237" t="s">
+        <v>301</v>
+      </c>
+      <c r="C237" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="238" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B238" t="s">
+        <v>302</v>
+      </c>
+      <c r="C238" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="239" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B239" t="s">
+        <v>303</v>
+      </c>
+      <c r="C239" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="240" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B240" t="s">
+        <v>304</v>
+      </c>
+      <c r="C240" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="241" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B241" t="s">
+        <v>305</v>
+      </c>
+      <c r="C241" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="242" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B242" t="s">
+        <v>306</v>
+      </c>
+      <c r="C242" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="243" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B243" t="s">
+        <v>307</v>
+      </c>
+      <c r="C243" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="244" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B244" t="s">
+        <v>308</v>
+      </c>
+      <c r="C244" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="245" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B245" t="s">
+        <v>309</v>
+      </c>
+      <c r="C245" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="246" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B246" t="s">
+        <v>310</v>
+      </c>
+      <c r="C246" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="247" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B247" t="s">
+        <v>311</v>
+      </c>
+      <c r="C247" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="248" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B248" t="s">
+        <v>312</v>
+      </c>
+      <c r="C248" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="249" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B249" t="s">
+        <v>313</v>
+      </c>
+      <c r="C249" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="250" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B250" t="s">
+        <v>314</v>
+      </c>
+      <c r="C250" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="251" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B251" t="s">
+        <v>315</v>
+      </c>
+      <c r="C251" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="252" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B252" t="s">
+        <v>316</v>
+      </c>
+      <c r="C252" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="253" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B253" t="s">
+        <v>317</v>
+      </c>
+      <c r="C253" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="254" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B254" t="s">
+        <v>318</v>
+      </c>
+      <c r="C254" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="255" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B255" t="s">
+        <v>319</v>
+      </c>
+      <c r="C255" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="256" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B256" t="s">
+        <v>320</v>
+      </c>
+      <c r="C256" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="257" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B257" t="s">
+        <v>321</v>
+      </c>
+      <c r="C257" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="258" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B258" t="s">
+        <v>322</v>
+      </c>
+      <c r="C258" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="259" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B259" t="s">
+        <v>323</v>
+      </c>
+      <c r="C259" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="260" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B260" t="s">
+        <v>324</v>
+      </c>
+      <c r="C260" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="261" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B261" t="s">
+        <v>325</v>
+      </c>
+      <c r="C261" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="262" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B262" t="s">
+        <v>326</v>
+      </c>
+      <c r="C262" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="263" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B263" t="s">
+        <v>327</v>
+      </c>
+      <c r="C263" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="264" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B264" t="s">
+        <v>328</v>
+      </c>
+      <c r="C264" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="265" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B265" t="s">
+        <v>329</v>
+      </c>
+      <c r="C265" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="266" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B266" t="s">
+        <v>330</v>
+      </c>
+      <c r="C266" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="267" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B267" t="s">
+        <v>331</v>
+      </c>
+      <c r="C267" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="268" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B268" t="s">
+        <v>332</v>
+      </c>
+      <c r="C268" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="269" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B269" t="s">
+        <v>333</v>
+      </c>
+      <c r="C269" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="270" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B270" t="s">
+        <v>334</v>
+      </c>
+      <c r="C270" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="271" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B271" t="s">
+        <v>335</v>
+      </c>
+      <c r="C271" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="272" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B272" t="s">
+        <v>336</v>
+      </c>
+      <c r="C272" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="273" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B273" t="s">
+        <v>150</v>
+      </c>
+      <c r="C273" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="274" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B274" t="s">
+        <v>337</v>
+      </c>
+      <c r="C274" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="275" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B275" t="s">
+        <v>338</v>
+      </c>
+      <c r="C275" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="276" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B276" t="s">
+        <v>339</v>
+      </c>
+      <c r="C276" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="277" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B277" t="s">
+        <v>340</v>
+      </c>
+      <c r="C277" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="278" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B278" t="s">
+        <v>341</v>
+      </c>
+      <c r="C278" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="279" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B279" t="s">
+        <v>342</v>
+      </c>
+      <c r="C279" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="280" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B280" t="s">
+        <v>343</v>
+      </c>
+      <c r="C280" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="281" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B281" t="s">
+        <v>344</v>
+      </c>
+      <c r="C281" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="282" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B282" t="s">
+        <v>345</v>
+      </c>
+      <c r="C282" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="283" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B283" t="s">
+        <v>346</v>
+      </c>
+      <c r="C283" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="284" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B284" t="s">
+        <v>347</v>
+      </c>
+      <c r="C284" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="285" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B285" t="s">
+        <v>348</v>
+      </c>
+      <c r="C285" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="286" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B286" t="s">
+        <v>349</v>
+      </c>
+      <c r="C286" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="287" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B287" t="s">
+        <v>350</v>
+      </c>
+      <c r="C287" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="288" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B288" t="s">
+        <v>351</v>
+      </c>
+      <c r="C288" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="289" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B289" t="s">
+        <v>352</v>
+      </c>
+      <c r="C289" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="290" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B290" t="s">
+        <v>353</v>
+      </c>
+      <c r="C290" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="291" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B291" t="s">
+        <v>354</v>
+      </c>
+      <c r="C291" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="292" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B292" t="s">
+        <v>355</v>
+      </c>
+      <c r="C292" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="293" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B293" t="s">
+        <v>356</v>
+      </c>
+      <c r="C293" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="294" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B294" t="s">
+        <v>357</v>
+      </c>
+      <c r="C294" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="295" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B295" t="s">
+        <v>358</v>
+      </c>
+      <c r="C295" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="296" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B296" t="s">
+        <v>359</v>
+      </c>
+      <c r="C296" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="297" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B297" t="s">
+        <v>360</v>
+      </c>
+      <c r="C297" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="298" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B298" t="s">
+        <v>361</v>
+      </c>
+      <c r="C298" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="299" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B299" t="s">
+        <v>362</v>
+      </c>
+      <c r="C299" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="300" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B300" t="s">
+        <v>363</v>
+      </c>
+      <c r="C300" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="301" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B301" t="s">
+        <v>364</v>
+      </c>
+      <c r="C301" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="302" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B302" t="s">
+        <v>365</v>
+      </c>
+      <c r="C302" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="303" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B303" t="s">
+        <v>366</v>
+      </c>
+      <c r="C303" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="304" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B304" t="s">
+        <v>367</v>
+      </c>
+      <c r="C304" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="305" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B305" t="s">
+        <v>368</v>
+      </c>
+      <c r="C305" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="306" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B306" t="s">
+        <v>369</v>
+      </c>
+      <c r="C306" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="307" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B307" t="s">
+        <v>370</v>
+      </c>
+      <c r="C307" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="308" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B308" t="s">
+        <v>371</v>
+      </c>
+      <c r="C308" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="309" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B309" t="s">
+        <v>372</v>
+      </c>
+      <c r="C309" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="310" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B310" t="s">
+        <v>373</v>
+      </c>
+      <c r="C310" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="311" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B311" t="s">
+        <v>374</v>
+      </c>
+      <c r="C311" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="312" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B312" t="s">
+        <v>375</v>
+      </c>
+      <c r="C312" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="313" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B313" t="s">
+        <v>376</v>
+      </c>
+      <c r="C313" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="314" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B314" t="s">
+        <v>377</v>
+      </c>
+      <c r="C314" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="315" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B315" t="s">
+        <v>378</v>
+      </c>
+      <c r="C315" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="316" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B316" t="s">
+        <v>379</v>
+      </c>
+      <c r="C316" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="317" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B317" t="s">
+        <v>380</v>
+      </c>
+      <c r="C317" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="318" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B318" t="s">
+        <v>381</v>
+      </c>
+      <c r="C318" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="319" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B319" t="s">
+        <v>382</v>
+      </c>
+      <c r="C319" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="320" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B320" t="s">
+        <v>383</v>
+      </c>
+      <c r="C320" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="321" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B321" t="s">
+        <v>384</v>
+      </c>
+      <c r="C321" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="322" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B322" t="s">
+        <v>385</v>
+      </c>
+      <c r="C322" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="323" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B323" t="s">
+        <v>386</v>
+      </c>
+      <c r="C323" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="324" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B324" t="s">
+        <v>387</v>
+      </c>
+      <c r="C324" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="325" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B325" t="s">
+        <v>388</v>
+      </c>
+      <c r="C325" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="326" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B326" t="s">
+        <v>389</v>
+      </c>
+      <c r="C326" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="327" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B327" t="s">
+        <v>390</v>
+      </c>
+      <c r="C327" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="328" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B328" t="s">
+        <v>106</v>
+      </c>
+      <c r="C328" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="329" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B329" t="s">
+        <v>391</v>
+      </c>
+      <c r="C329" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="330" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B330" t="s">
+        <v>392</v>
+      </c>
+      <c r="C330" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="331" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B331" t="s">
+        <v>393</v>
+      </c>
+      <c r="C331" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="332" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B332" t="s">
+        <v>394</v>
+      </c>
+      <c r="C332" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="333" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B333" t="s">
+        <v>395</v>
+      </c>
+      <c r="C333" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="334" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B334" t="s">
         <v>52</v>
       </c>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
-      <c r="J28" s="3"/>
-      <c r="K28" s="4"/>
-      <c r="L28" s="3"/>
-      <c r="M28" s="3"/>
-    </row>
-    <row r="29" spans="2:13" ht="201.6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B29" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="30" spans="2:13" ht="158.4" x14ac:dyDescent="0.55000000000000004">
-      <c r="B30" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="G30" s="5"/>
-      <c r="H30" s="5"/>
-      <c r="I30" s="5"/>
-      <c r="J30" s="6"/>
-      <c r="K30" s="5"/>
-      <c r="L30" s="5"/>
-    </row>
-    <row r="31" spans="2:13" ht="144" x14ac:dyDescent="0.55000000000000004">
-      <c r="B31" s="1" t="s">
+      <c r="C334" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="335" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B335" t="s">
+        <v>396</v>
+      </c>
+      <c r="C335" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="336" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B336" t="s">
+        <v>397</v>
+      </c>
+      <c r="C336" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="337" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B337" t="s">
+        <v>398</v>
+      </c>
+      <c r="C337" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="338" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B338" t="s">
+        <v>399</v>
+      </c>
+      <c r="C338" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="339" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B339" t="s">
+        <v>400</v>
+      </c>
+      <c r="C339" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="340" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B340" t="s">
+        <v>401</v>
+      </c>
+      <c r="C340" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="341" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B341" t="s">
+        <v>402</v>
+      </c>
+      <c r="C341" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="342" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B342" t="s">
+        <v>403</v>
+      </c>
+      <c r="C342" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="343" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B343" t="s">
+        <v>404</v>
+      </c>
+      <c r="C343" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="344" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B344" t="s">
+        <v>405</v>
+      </c>
+      <c r="C344" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="345" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B345" t="s">
+        <v>406</v>
+      </c>
+      <c r="C345" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="346" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B346" t="s">
+        <v>407</v>
+      </c>
+      <c r="C346" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="347" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B347" t="s">
+        <v>125</v>
+      </c>
+      <c r="C347" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="348" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B348" t="s">
+        <v>408</v>
+      </c>
+      <c r="C348" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="349" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B349" t="s">
+        <v>409</v>
+      </c>
+      <c r="C349" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="350" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B350" t="s">
+        <v>410</v>
+      </c>
+      <c r="C350" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="351" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B351" t="s">
+        <v>411</v>
+      </c>
+      <c r="C351" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="352" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B352" t="s">
+        <v>412</v>
+      </c>
+      <c r="C352" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="353" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B353" t="s">
+        <v>413</v>
+      </c>
+      <c r="C353" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="354" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B354" t="s">
+        <v>414</v>
+      </c>
+      <c r="C354" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="355" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B355" t="s">
+        <v>399</v>
+      </c>
+      <c r="C355" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="356" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B356" t="s">
+        <v>415</v>
+      </c>
+      <c r="C356" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="357" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B357" t="s">
+        <v>416</v>
+      </c>
+      <c r="C357" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="358" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B358" t="s">
+        <v>417</v>
+      </c>
+      <c r="C358" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="359" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B359" t="s">
+        <v>418</v>
+      </c>
+      <c r="C359" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="360" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B360" t="s">
+        <v>222</v>
+      </c>
+      <c r="C360" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="361" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B361" t="s">
+        <v>419</v>
+      </c>
+      <c r="C361" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="362" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B362" t="s">
+        <v>420</v>
+      </c>
+      <c r="C362" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="363" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B363" t="s">
+        <v>421</v>
+      </c>
+      <c r="C363" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="364" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B364" t="s">
+        <v>422</v>
+      </c>
+      <c r="C364" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="365" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B365" t="s">
+        <v>423</v>
+      </c>
+      <c r="C365" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="366" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B366" t="s">
+        <v>424</v>
+      </c>
+      <c r="C366" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="367" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B367" t="s">
+        <v>425</v>
+      </c>
+      <c r="C367" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="368" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B368" t="s">
+        <v>426</v>
+      </c>
+      <c r="C368" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="369" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B369" t="s">
+        <v>427</v>
+      </c>
+      <c r="C369" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="370" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B370" t="s">
+        <v>428</v>
+      </c>
+      <c r="C370" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="371" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B371" t="s">
+        <v>429</v>
+      </c>
+      <c r="C371" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="372" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B372" t="s">
+        <v>430</v>
+      </c>
+      <c r="C372" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="373" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B373" t="s">
+        <v>431</v>
+      </c>
+      <c r="C373" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="374" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B374" t="s">
+        <v>432</v>
+      </c>
+      <c r="C374" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="375" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B375" t="s">
+        <v>433</v>
+      </c>
+      <c r="C375" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="376" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B376" t="s">
+        <v>434</v>
+      </c>
+      <c r="C376" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="377" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B377" t="s">
+        <v>96</v>
+      </c>
+      <c r="C377" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="378" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B378" t="s">
+        <v>435</v>
+      </c>
+      <c r="C378" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="379" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B379" t="s">
+        <v>436</v>
+      </c>
+      <c r="C379" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="380" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B380" t="s">
+        <v>437</v>
+      </c>
+      <c r="C380" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="381" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B381" t="s">
+        <v>438</v>
+      </c>
+      <c r="C381" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="382" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B382" t="s">
+        <v>439</v>
+      </c>
+      <c r="C382" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="383" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B383" t="s">
+        <v>440</v>
+      </c>
+      <c r="C383" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="384" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B384" t="s">
+        <v>441</v>
+      </c>
+      <c r="C384" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="385" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B385" t="s">
+        <v>442</v>
+      </c>
+      <c r="C385" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="386" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B386" t="s">
+        <v>443</v>
+      </c>
+      <c r="C386" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="387" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B387" t="s">
+        <v>444</v>
+      </c>
+      <c r="C387" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="388" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B388" t="s">
+        <v>445</v>
+      </c>
+      <c r="C388" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="389" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B389" t="s">
         <v>60</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="32" spans="2:13" ht="288" x14ac:dyDescent="0.55000000000000004">
-      <c r="B32" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="33" spans="2:3" ht="144" x14ac:dyDescent="0.55000000000000004">
-      <c r="B33" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="34" spans="2:3" ht="144" x14ac:dyDescent="0.55000000000000004">
-      <c r="B34" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="35" spans="2:3" ht="216" x14ac:dyDescent="0.55000000000000004">
-      <c r="B35" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="36" spans="2:3" ht="187.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B36" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="37" spans="2:3" ht="201.6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B37" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="38" spans="2:3" ht="187.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B38" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="39" spans="2:3" ht="172.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B39" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="40" spans="2:3" ht="316.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B40" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="41" spans="2:3" ht="187.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B41" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="42" spans="2:3" ht="244.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B42" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="43" spans="2:3" ht="187.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B43" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="44" spans="2:3" ht="172.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B44" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="45" spans="2:3" ht="187.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B45" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="46" spans="2:3" ht="273.60000000000002" x14ac:dyDescent="0.55000000000000004">
-      <c r="B46" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="47" spans="2:3" ht="129.6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B47" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="48" spans="2:3" ht="158.4" x14ac:dyDescent="0.55000000000000004">
-      <c r="B48" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="49" spans="2:9" ht="144" x14ac:dyDescent="0.55000000000000004">
-      <c r="B49" s="1" t="s">
+      <c r="C389" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="390" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B390" t="s">
+        <v>446</v>
+      </c>
+      <c r="C390" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="391" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B391" t="s">
+        <v>447</v>
+      </c>
+      <c r="C391" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="392" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B392" t="s">
+        <v>448</v>
+      </c>
+      <c r="C392" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="393" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B393" t="s">
+        <v>449</v>
+      </c>
+      <c r="C393" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="394" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B394" t="s">
+        <v>450</v>
+      </c>
+      <c r="C394" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="395" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B395" t="s">
+        <v>451</v>
+      </c>
+      <c r="C395" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="396" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B396" t="s">
+        <v>452</v>
+      </c>
+      <c r="C396" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="397" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B397" t="s">
+        <v>453</v>
+      </c>
+      <c r="C397" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="398" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B398" t="s">
+        <v>454</v>
+      </c>
+      <c r="C398" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="399" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B399" t="s">
+        <v>455</v>
+      </c>
+      <c r="C399" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="400" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B400" t="s">
+        <v>456</v>
+      </c>
+      <c r="C400" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="401" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B401" t="s">
+        <v>457</v>
+      </c>
+      <c r="C401" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="402" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B402" t="s">
+        <v>458</v>
+      </c>
+      <c r="C402" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="403" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B403" t="s">
+        <v>459</v>
+      </c>
+      <c r="C403" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="404" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B404" t="s">
+        <v>460</v>
+      </c>
+      <c r="C404" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="405" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B405" t="s">
+        <v>461</v>
+      </c>
+      <c r="C405" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="406" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B406" t="s">
+        <v>462</v>
+      </c>
+      <c r="C406" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="407" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B407" t="s">
+        <v>463</v>
+      </c>
+      <c r="C407" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="408" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B408" t="s">
+        <v>464</v>
+      </c>
+      <c r="C408" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="409" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B409" t="s">
+        <v>465</v>
+      </c>
+      <c r="C409" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="410" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B410" t="s">
+        <v>466</v>
+      </c>
+      <c r="C410" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="411" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B411" t="s">
+        <v>467</v>
+      </c>
+      <c r="C411" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="412" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B412" t="s">
+        <v>468</v>
+      </c>
+      <c r="C412" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="413" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B413" t="s">
+        <v>469</v>
+      </c>
+      <c r="C413" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="414" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B414" t="s">
+        <v>470</v>
+      </c>
+      <c r="C414" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="415" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B415" t="s">
+        <v>471</v>
+      </c>
+      <c r="C415" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="416" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B416" t="s">
+        <v>472</v>
+      </c>
+      <c r="C416" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="417" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B417" t="s">
+        <v>473</v>
+      </c>
+      <c r="C417" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="418" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B418" t="s">
+        <v>474</v>
+      </c>
+      <c r="C418" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="419" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B419" t="s">
+        <v>475</v>
+      </c>
+      <c r="C419" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="420" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B420" t="s">
+        <v>476</v>
+      </c>
+      <c r="C420" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="421" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B421" t="s">
+        <v>477</v>
+      </c>
+      <c r="C421" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="422" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B422" t="s">
+        <v>478</v>
+      </c>
+      <c r="C422" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="423" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B423" t="s">
+        <v>479</v>
+      </c>
+      <c r="C423" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="424" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B424" t="s">
+        <v>480</v>
+      </c>
+      <c r="C424" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="425" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B425" t="s">
+        <v>481</v>
+      </c>
+      <c r="C425" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="426" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B426" t="s">
+        <v>482</v>
+      </c>
+      <c r="C426" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="427" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B427" t="s">
+        <v>483</v>
+      </c>
+      <c r="C427" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="428" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B428" t="s">
+        <v>484</v>
+      </c>
+      <c r="C428" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="429" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B429" t="s">
+        <v>485</v>
+      </c>
+      <c r="C429" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="430" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B430" t="s">
+        <v>486</v>
+      </c>
+      <c r="C430" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="431" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B431" t="s">
+        <v>487</v>
+      </c>
+      <c r="C431" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="432" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B432" t="s">
+        <v>488</v>
+      </c>
+      <c r="C432" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="433" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B433" t="s">
+        <v>489</v>
+      </c>
+      <c r="C433" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="434" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B434" t="s">
+        <v>490</v>
+      </c>
+      <c r="C434" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="435" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B435" t="s">
+        <v>491</v>
+      </c>
+      <c r="C435" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="436" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B436" t="s">
+        <v>492</v>
+      </c>
+      <c r="C436" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="437" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B437" t="s">
+        <v>493</v>
+      </c>
+      <c r="C437" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="438" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B438" t="s">
+        <v>494</v>
+      </c>
+      <c r="C438" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="439" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B439" t="s">
+        <v>150</v>
+      </c>
+      <c r="C439" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="440" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B440" t="s">
+        <v>495</v>
+      </c>
+      <c r="C440" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="441" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B441" t="s">
+        <v>496</v>
+      </c>
+      <c r="C441" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="442" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B442" t="s">
+        <v>497</v>
+      </c>
+      <c r="C442" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="443" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B443" t="s">
+        <v>498</v>
+      </c>
+      <c r="C443" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="444" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B444" t="s">
+        <v>491</v>
+      </c>
+      <c r="C444" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="445" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B445" t="s">
+        <v>499</v>
+      </c>
+      <c r="C445" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="446" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B446" t="s">
+        <v>500</v>
+      </c>
+      <c r="C446" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="447" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B447" t="s">
+        <v>501</v>
+      </c>
+      <c r="C447" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="448" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B448" t="s">
+        <v>126</v>
+      </c>
+      <c r="C448" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="449" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B449" t="s">
+        <v>502</v>
+      </c>
+      <c r="C449" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="450" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B450" t="s">
+        <v>503</v>
+      </c>
+      <c r="C450" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="451" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B451" t="s">
+        <v>504</v>
+      </c>
+      <c r="C451" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="452" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B452" t="s">
+        <v>505</v>
+      </c>
+      <c r="C452" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="453" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B453" t="s">
+        <v>347</v>
+      </c>
+      <c r="C453" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="454" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B454" t="s">
+        <v>506</v>
+      </c>
+      <c r="C454" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="455" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B455" t="s">
+        <v>507</v>
+      </c>
+      <c r="C455" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="456" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B456" t="s">
+        <v>508</v>
+      </c>
+      <c r="C456" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="457" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B457" t="s">
+        <v>509</v>
+      </c>
+      <c r="C457" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="458" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B458" t="s">
+        <v>510</v>
+      </c>
+      <c r="C458" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="459" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B459" t="s">
+        <v>511</v>
+      </c>
+      <c r="C459" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="460" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B460" t="s">
+        <v>512</v>
+      </c>
+      <c r="C460" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="461" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B461" t="s">
+        <v>513</v>
+      </c>
+      <c r="C461" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="462" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B462" t="s">
+        <v>514</v>
+      </c>
+      <c r="C462" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="463" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B463" t="s">
+        <v>426</v>
+      </c>
+      <c r="C463" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="464" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B464" t="s">
+        <v>515</v>
+      </c>
+      <c r="C464" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="465" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B465" t="s">
+        <v>516</v>
+      </c>
+      <c r="C465" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="466" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B466" t="s">
+        <v>517</v>
+      </c>
+      <c r="C466" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="467" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B467" t="s">
+        <v>518</v>
+      </c>
+      <c r="C467" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="468" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B468" t="s">
+        <v>519</v>
+      </c>
+      <c r="C468" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="469" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B469" t="s">
+        <v>520</v>
+      </c>
+      <c r="C469" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="470" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B470" t="s">
+        <v>521</v>
+      </c>
+      <c r="C470" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="471" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B471" t="s">
+        <v>522</v>
+      </c>
+      <c r="C471" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="472" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B472" t="s">
+        <v>523</v>
+      </c>
+      <c r="C472" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="473" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B473" t="s">
+        <v>524</v>
+      </c>
+      <c r="C473" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="474" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B474" t="s">
+        <v>525</v>
+      </c>
+      <c r="C474" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="475" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B475" t="s">
+        <v>526</v>
+      </c>
+      <c r="C475" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="476" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B476" t="s">
+        <v>527</v>
+      </c>
+      <c r="C476" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="477" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B477" t="s">
+        <v>528</v>
+      </c>
+      <c r="C477" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="478" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B478" t="s">
+        <v>529</v>
+      </c>
+      <c r="C478" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="479" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B479" t="s">
+        <v>530</v>
+      </c>
+      <c r="C479" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="480" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B480" t="s">
+        <v>531</v>
+      </c>
+      <c r="C480" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="481" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B481" t="s">
+        <v>532</v>
+      </c>
+      <c r="C481" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="482" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B482" t="s">
+        <v>533</v>
+      </c>
+      <c r="C482" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="483" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B483" t="s">
+        <v>534</v>
+      </c>
+      <c r="C483" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="484" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B484" t="s">
+        <v>535</v>
+      </c>
+      <c r="C484" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="485" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B485" t="s">
+        <v>536</v>
+      </c>
+      <c r="C485" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="486" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B486" t="s">
+        <v>537</v>
+      </c>
+      <c r="C486" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="487" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B487" t="s">
+        <v>538</v>
+      </c>
+      <c r="C487" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="488" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B488" t="s">
+        <v>539</v>
+      </c>
+      <c r="C488" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="489" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B489" t="s">
+        <v>540</v>
+      </c>
+      <c r="C489" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="490" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B490" t="s">
+        <v>541</v>
+      </c>
+      <c r="C490" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="491" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B491" t="s">
+        <v>542</v>
+      </c>
+      <c r="C491" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="492" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B492" t="s">
+        <v>543</v>
+      </c>
+      <c r="C492" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="493" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B493" t="s">
+        <v>544</v>
+      </c>
+      <c r="C493" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="494" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B494" t="s">
+        <v>545</v>
+      </c>
+      <c r="C494" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="495" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B495" t="s">
+        <v>103</v>
+      </c>
+      <c r="C495" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="496" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B496" t="s">
+        <v>112</v>
+      </c>
+      <c r="C496" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="497" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B497" t="s">
+        <v>546</v>
+      </c>
+      <c r="C497" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="498" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B498" t="s">
         <v>96</v>
       </c>
-      <c r="C49" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="50" spans="2:9" ht="144" x14ac:dyDescent="0.55000000000000004">
-      <c r="B50" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="51" spans="2:9" ht="158.4" x14ac:dyDescent="0.55000000000000004">
-      <c r="B51" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="52" spans="2:9" ht="172.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B52" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="53" spans="2:9" ht="172.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B53" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="54" spans="2:9" ht="172.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B54" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="55" spans="2:9" ht="187.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B55" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="56" spans="2:9" ht="158.4" x14ac:dyDescent="0.55000000000000004">
-      <c r="B56" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="57" spans="2:9" ht="201.6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B57" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="58" spans="2:9" ht="172.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B58" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="59" spans="2:9" ht="201.6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B59" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="C59" s="7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="60" spans="2:9" ht="187.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B60" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="C60" s="7" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="61" spans="2:9" ht="158.4" x14ac:dyDescent="0.55000000000000004">
-      <c r="B61" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="I61" s="8"/>
-    </row>
-    <row r="62" spans="2:9" ht="129.6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B62" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="I62" s="8"/>
-    </row>
-    <row r="63" spans="2:9" ht="100.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B63" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="C63" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="I63" s="8"/>
-    </row>
-    <row r="64" spans="2:9" ht="115.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B64" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="C64" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="I64" s="8"/>
-    </row>
-    <row r="65" spans="2:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="B65" s="1"/>
-      <c r="C65" s="1"/>
-    </row>
-    <row r="66" spans="2:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="B66" s="1"/>
-      <c r="C66" s="1"/>
-    </row>
-    <row r="67" spans="2:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="B67" s="1"/>
-      <c r="C67" s="1"/>
-    </row>
-    <row r="68" spans="2:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="B68" s="1"/>
-      <c r="C68" s="1"/>
-    </row>
-    <row r="69" spans="2:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="B69" s="1"/>
-      <c r="C69" s="1"/>
-    </row>
-    <row r="70" spans="2:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="B70" s="1"/>
-      <c r="C70" s="1"/>
-    </row>
-    <row r="71" spans="2:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="B71" s="1"/>
-      <c r="C71" s="1"/>
-    </row>
-    <row r="72" spans="2:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="B72" s="1"/>
-      <c r="C72" s="1"/>
-    </row>
-    <row r="73" spans="2:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="B73" s="1"/>
-      <c r="C73" s="1"/>
-    </row>
-    <row r="74" spans="2:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="B74" s="1"/>
-      <c r="C74" s="1"/>
-    </row>
-    <row r="75" spans="2:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="B75" s="1"/>
-      <c r="C75" s="1"/>
-    </row>
-    <row r="76" spans="2:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="B76" s="1"/>
-      <c r="C76" s="1"/>
-    </row>
-    <row r="77" spans="2:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="C77" s="1"/>
-    </row>
-    <row r="78" spans="2:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="C78" s="1"/>
-    </row>
-    <row r="79" spans="2:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="C79" s="1"/>
-    </row>
-    <row r="80" spans="2:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="C80" s="1"/>
+      <c r="C498" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="499" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B499" t="s">
+        <v>547</v>
+      </c>
+      <c r="C499" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="500" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B500" t="s">
+        <v>548</v>
+      </c>
+      <c r="C500" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="501" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B501" t="s">
+        <v>295</v>
+      </c>
+      <c r="C501" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="502" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B502" t="s">
+        <v>549</v>
+      </c>
+      <c r="C502" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="503" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B503" t="s">
+        <v>550</v>
+      </c>
+      <c r="C503" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="504" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B504" t="s">
+        <v>362</v>
+      </c>
+      <c r="C504" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="505" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B505" t="s">
+        <v>551</v>
+      </c>
+      <c r="C505" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="506" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B506" t="s">
+        <v>552</v>
+      </c>
+      <c r="C506" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="507" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B507" t="s">
+        <v>553</v>
+      </c>
+      <c r="C507" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="508" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B508" t="s">
+        <v>554</v>
+      </c>
+      <c r="C508" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="509" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B509" t="s">
+        <v>555</v>
+      </c>
+      <c r="C509" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="510" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B510" t="s">
+        <v>556</v>
+      </c>
+      <c r="C510" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="511" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B511" t="s">
+        <v>557</v>
+      </c>
+      <c r="C511" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="512" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B512" t="s">
+        <v>558</v>
+      </c>
+      <c r="C512" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="513" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B513" t="s">
+        <v>559</v>
+      </c>
+      <c r="C513" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="514" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="C514" s="7"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="E28:F35">
